--- a/covarianants.xlsx
+++ b/covarianants.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ковенанты" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Ковенанты'!$A$1:$N$261</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Ковенанты'!$A$1:$N$271</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -476,7 +476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N266"/>
+  <dimension ref="A1:N276"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -2290,8 +2290,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Информационный (отчётность эмитента) +
-Раскрытие отчётности эмитента</t>
+          <t>Раскрытие отчётности</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -2339,8 +2338,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>Информационный (отчётность эмитента) +
-Раскрытие отчётности эмитента</t>
+          <t>Раскрытие отчётности</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -2398,8 +2396,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>Информационный (отчётность эмитента) +
-Раскрытие отчётности эмитента</t>
+          <t>Раскрытие отчётности</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -2457,8 +2454,7 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>Информационный (отчётность эмитента) +
-Раскрытие отчётности эмитента</t>
+          <t>Раскрытие отчётности</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -4315,8 +4311,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Информационный (отчётность эмитента) +
-Раскрытие отчётности эмитента</t>
+          <t>Раскрытие отчётности</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -4374,8 +4369,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Информационный (отчётность эмитента) +
-Раскрытие отчётности эмитента</t>
+          <t>Раскрытие отчётности</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -4583,8 +4577,7 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>Информационный (отчётность эмитента) +
-Раскрытие отчётности эмитента</t>
+          <t>Раскрытие отчётности</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -4632,8 +4625,7 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>Информационный (отчётность эмитента) +
-Раскрытие отчётности эмитента</t>
+          <t>Раскрытие отчётности</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -4691,8 +4683,7 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>Информационный (отчётность эмитента) +
-Раскрытие отчётности эмитента</t>
+          <t>Раскрытие отчётности</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
@@ -4740,8 +4731,7 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>Информационный (отчётность эмитента) +
-Раскрытие отчётности эмитента</t>
+          <t>Раскрытие отчётности</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -4789,8 +4779,7 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>Информационный (отчётность эмитента) +
-Раскрытие отчётности эмитента</t>
+          <t>Долговая нагрузка</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
@@ -4848,8 +4837,7 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>Информационный (отчётность эмитента) +
-Раскрытие отчётности эмитента</t>
+          <t>Раскрытие отчётности</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -4897,8 +4885,7 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>Информационный (отчётность эмитента) +
-Раскрытие отчётности эмитента</t>
+          <t>Раскрытие отчётности</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -4956,8 +4943,7 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>Информационный (отчётность эмитента) +
-Раскрытие отчётности эмитента</t>
+          <t>Раскрытие отчётности</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -5005,8 +4991,7 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>Информационный (отчётность эмитента) +
-Раскрытие отчётности эмитента</t>
+          <t>Раскрытие отчётности</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
@@ -5064,8 +5049,7 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>Информационный (отчётность эмитента) +
-Раскрытие отчётности эмитента</t>
+          <t>Раскрытие отчётности</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
@@ -5113,8 +5097,7 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>Информационный (отчётность эмитента) +
-Раскрытие отчётности эмитента</t>
+          <t>Раскрытие отчётности</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
@@ -5172,8 +5155,7 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>Информационный (отчётность эмитента) +
-Раскрытие отчётности эмитента</t>
+          <t>Раскрытие отчётности</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
@@ -5221,8 +5203,7 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>Информационный (отчётность эмитента) +
-Раскрытие отчётности эмитента</t>
+          <t>Раскрытие отчётности</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
@@ -5280,8 +5261,7 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>Информационный (отчётность эмитента) +
-Раскрытие отчётности эмитента</t>
+          <t>Раскрытие отчётности</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -5329,8 +5309,7 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>Информационный (отчётность эмитента) +
-Раскрытие отчётности эмитента</t>
+          <t>Раскрытие отчётности</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
@@ -5388,8 +5367,7 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>Информационный (отчётность эмитента) +
-Раскрытие отчётности эмитента</t>
+          <t>Раскрытие отчётности</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
@@ -5437,8 +5415,7 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>Информационный (отчётность эмитента) +
-Раскрытие отчётности эмитента</t>
+          <t>Раскрытие отчётности</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -5496,8 +5473,7 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>Информационный (отчётность эмитента) +
-Раскрытие отчётности эмитента</t>
+          <t>Раскрытие отчётности</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
@@ -5545,8 +5521,7 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>Информационный (отчётность эмитента) +
-Раскрытие отчётности эмитента</t>
+          <t>Раскрытие отчётности</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
@@ -5604,8 +5579,7 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>Информационный (отчётность эмитента) +
-Раскрытие отчётности эмитента</t>
+          <t>Раскрытие отчётности</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
@@ -5653,8 +5627,7 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>Информационный (отчётность эмитента) +
-Раскрытие отчётности эмитента</t>
+          <t>Раскрытие отчётности</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
@@ -5702,8 +5675,7 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>Информационный (отчётность эмитента) +
-Раскрытие отчётности эмитента</t>
+          <t>Долговая нагрузка</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
@@ -5761,8 +5733,7 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>Информационный (отчётность эмитента) +
-Раскрытие отчётности эмитента</t>
+          <t>Раскрытие отчётности</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
@@ -5810,8 +5781,7 @@
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>Информационный (отчётность эмитента) +
-Раскрытие отчётности эмитента</t>
+          <t>Раскрытие отчётности</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
@@ -5859,8 +5829,7 @@
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>Информационный (отчётность эмитента) +
-Раскрытие отчётности эмитента</t>
+          <t>Долговая нагрузка</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
@@ -5918,8 +5887,7 @@
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>Информационный (отчётность эмитента) +
-Раскрытие отчётности эмитента</t>
+          <t>Раскрытие отчётности</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
@@ -5967,8 +5935,7 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>Информационный (отчётность эмитента) +
-Раскрытие отчётности эмитента</t>
+          <t>Раскрытие отчётности</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
@@ -6016,8 +5983,7 @@
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>Информационный (отчётность эмитента) +
-Раскрытие отчётности эмитента</t>
+          <t>Долговая нагрузка</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
@@ -6075,8 +6041,7 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>Информационный (отчётность эмитента) +
-Раскрытие отчётности эмитента</t>
+          <t>Раскрытие отчётности</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
@@ -6124,8 +6089,7 @@
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>Информационный (отчётность эмитента) +
-Раскрытие отчётности эмитента</t>
+          <t>Раскрытие отчётности</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
@@ -6173,8 +6137,7 @@
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>Информационный (отчётность эмитента) +
-Раскрытие отчётности эмитента</t>
+          <t>Долговая нагрузка</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
@@ -6232,8 +6195,7 @@
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>Информационный (отчётность эмитента) +
-Раскрытие отчётности эмитента</t>
+          <t>Раскрытие отчётности</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
@@ -6281,8 +6243,7 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>Информационный (отчётность эмитента) +
-Раскрытие отчётности эмитента</t>
+          <t>Раскрытие отчётности</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
@@ -6330,8 +6291,7 @@
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>Информационный (отчётность эмитента) +
-Раскрытие отчётности эмитента</t>
+          <t>Долговая нагрузка</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
@@ -6389,8 +6349,7 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>Информационный (отчётность эмитента) +
-Раскрытие отчётности эмитента</t>
+          <t>Утрата контроля</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
@@ -7178,8 +7137,7 @@
       </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>Информационный (отчётность эмитента) +
-Раскрытие отчётности эмитента</t>
+          <t>Раскрытие отчётности</t>
         </is>
       </c>
       <c r="H129" s="2" t="inlineStr">
@@ -7287,8 +7245,7 @@
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>Информационный (отчётность эмитента) +
-Раскрытие отчётности эмитента</t>
+          <t>Раскрытие отчётности</t>
         </is>
       </c>
       <c r="H131" s="2" t="inlineStr">
@@ -7328,62 +7285,52 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="7" t="inlineStr">
+      <c r="A132" s="2" t="inlineStr">
         <is>
           <t>МВ ФИНАНС-001Р-06</t>
         </is>
       </c>
-      <c r="B132" s="7" t="inlineStr"/>
-      <c r="C132" s="7" t="inlineStr">
+      <c r="B132" s="2" t="inlineStr"/>
+      <c r="C132" s="2" t="inlineStr">
         <is>
           <t>RU000A10BFP3</t>
         </is>
       </c>
-      <c r="D132" s="7" t="inlineStr"/>
-      <c r="E132" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F132" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G132" s="7" t="inlineStr">
-        <is>
-          <t>Информационный (отчётность эмитента) +
-Раскрытие отчётности эмитента</t>
-        </is>
-      </c>
-      <c r="H132" s="7" t="inlineStr">
-        <is>
-          <t>6.5.1 Программы),
-в порядке и сроки, предусмотренные Решением о выпуске ценных бумаг. (из Программы)</t>
-        </is>
-      </c>
-      <c r="I132" s="7" t="inlineStr">
-        <is>
-          <t>Программа облигаций (e-disclosure)</t>
-        </is>
-      </c>
-      <c r="J132" s="7" t="inlineStr">
-        <is>
-          <t>п. 6.5.1</t>
-        </is>
-      </c>
-      <c r="K132" s="7" t="n">
+      <c r="D132" s="2" t="inlineStr"/>
+      <c r="E132" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="L132" s="7" t="inlineStr">
-        <is>
-          <t>files.aspx</t>
-        </is>
-      </c>
-      <c r="M132" s="7" t="inlineStr">
-        <is>
-          <t>6.5.1 Программы), в порядке и сроки, предусмотренные Решением о выпуске ценных бумаг. Владелец Биржевой облигации имеет право на получение дохода (процента), размер или порядок определения размера, а также сроки выплаты которого будут указаны в соответствующем Решении о выпуске. Владелец Биржевых облигаций имеет право требовать досрочного погашения Биржевых облигаций и выплаты ему накопленного купонного дохода по Биржевым облигациям, рассчитанного на дату исполнения обязательств по досрочному по</t>
-        </is>
-      </c>
-      <c r="N132" s="8" t="inlineStr">
-        <is>
-          <t>https://e-disclosure.ru/portal/files.aspx?id=38369&amp;type=7</t>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>Положения о досрочном погашении</t>
+        </is>
+      </c>
+      <c r="H132" s="2" t="inlineStr">
+        <is>
+          <t>Put-опция у владельцев отсутствует</t>
+        </is>
+      </c>
+      <c r="I132" s="2" t="inlineStr">
+        <is>
+          <t>Решение о выпуске</t>
+        </is>
+      </c>
+      <c r="J132" s="2" t="inlineStr"/>
+      <c r="K132" s="2" t="inlineStr"/>
+      <c r="L132" s="2" t="inlineStr">
+        <is>
+          <t>15550_0_Решение о выпуске_001Р-06.pdf</t>
+        </is>
+      </c>
+      <c r="M132" s="2" t="inlineStr"/>
+      <c r="N132" s="3" t="inlineStr">
+        <is>
+          <t>https://st.finam.ru/ipo/genconditions/15550_0_Решение о выпуске_001Р-06.pdf</t>
         </is>
       </c>
     </row>
@@ -7508,8 +7455,7 @@
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>Информационный (отчётность эмитента) +
-Раскрытие отчётности эмитента</t>
+          <t>Кросс-дефолт</t>
         </is>
       </c>
       <c r="H135" s="2" t="inlineStr">
@@ -7557,8 +7503,7 @@
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>Информационный (отчётность эмитента) +
-Раскрытие отчётности эмитента</t>
+          <t>Раскрытие отчётности</t>
         </is>
       </c>
       <c r="H136" s="2" t="inlineStr">
@@ -7606,8 +7551,7 @@
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>Информационный (отчётность эмитента) +
-Раскрытие отчётности эмитента</t>
+          <t>Раскрытие отчётности</t>
         </is>
       </c>
       <c r="H137" s="2" t="inlineStr">
@@ -7665,8 +7609,7 @@
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>Информационный (отчётность эмитента) +
-Раскрытие отчётности эмитента</t>
+          <t>Кросс-дефолт</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr">
@@ -7714,8 +7657,7 @@
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>Информационный (отчётность эмитента) +
-Раскрытие отчётности эмитента</t>
+          <t>Раскрытие отчётности</t>
         </is>
       </c>
       <c r="H139" s="2" t="inlineStr">
@@ -7763,8 +7705,7 @@
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>Информационный (отчётность эмитента) +
-Раскрытие отчётности эмитента</t>
+          <t>Раскрытие отчётности</t>
         </is>
       </c>
       <c r="H140" s="2" t="inlineStr">
@@ -7822,8 +7763,7 @@
       </c>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>Информационный (отчётность эмитента) +
-Раскрытие отчётности эмитента</t>
+          <t>Кросс-дефолт</t>
         </is>
       </c>
       <c r="H141" s="2" t="inlineStr">
@@ -7871,8 +7811,7 @@
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>Информационный (отчётность эмитента) +
-Раскрытие отчётности эмитента</t>
+          <t>Раскрытие отчётности</t>
         </is>
       </c>
       <c r="H142" s="2" t="inlineStr">
@@ -7920,8 +7859,7 @@
       </c>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t>Информационный (отчётность эмитента) +
-Раскрытие отчётности эмитента</t>
+          <t>Раскрытие отчётности</t>
         </is>
       </c>
       <c r="H143" s="2" t="inlineStr">
@@ -7979,8 +7917,7 @@
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>Информационный (отчётность эмитента) +
-Раскрытие отчётности эмитента</t>
+          <t>Кросс-дефолт</t>
         </is>
       </c>
       <c r="H144" s="2" t="inlineStr">
@@ -8028,8 +7965,7 @@
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>Информационный (отчётность эмитента) +
-Раскрытие отчётности эмитента</t>
+          <t>Раскрытие отчётности</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
@@ -8077,8 +8013,7 @@
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>Информационный (отчётность эмитента) +
-Раскрытие отчётности эмитента</t>
+          <t>Раскрытие отчётности</t>
         </is>
       </c>
       <c r="H146" s="2" t="inlineStr">
@@ -8136,8 +8071,7 @@
       </c>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>Информационный (отчётность эмитента) +
-Раскрытие отчётности эмитента</t>
+          <t>Кросс-дефолт</t>
         </is>
       </c>
       <c r="H147" s="2" t="inlineStr">
@@ -8185,8 +8119,7 @@
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>Информационный (отчётность эмитента) +
-Раскрытие отчётности эмитента</t>
+          <t>Раскрытие отчётности</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr">
@@ -8234,8 +8167,7 @@
       </c>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>Информационный (отчётность эмитента) +
-Раскрытие отчётности эмитента</t>
+          <t>Раскрытие отчётности</t>
         </is>
       </c>
       <c r="H149" s="2" t="inlineStr">
@@ -8293,8 +8225,7 @@
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>Информационный (отчётность эмитента) +
-Раскрытие отчётности эмитента</t>
+          <t>Кросс-дефолт</t>
         </is>
       </c>
       <c r="H150" s="2" t="inlineStr">
@@ -8342,8 +8273,7 @@
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>Информационный (отчётность эмитента) +
-Раскрытие отчётности эмитента</t>
+          <t>Раскрытие отчётности</t>
         </is>
       </c>
       <c r="H151" s="2" t="inlineStr">
@@ -8391,8 +8321,7 @@
       </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>Информационный (отчётность эмитента) +
-Раскрытие отчётности эмитента</t>
+          <t>Раскрытие отчётности</t>
         </is>
       </c>
       <c r="H152" s="2" t="inlineStr">
@@ -8500,8 +8429,7 @@
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>Информационный (отчётность эмитента) +
-Раскрытие отчётности эмитента</t>
+          <t>Иное</t>
         </is>
       </c>
       <c r="H154" s="2" t="inlineStr">
@@ -8551,8 +8479,7 @@
       </c>
       <c r="G155" s="7" t="inlineStr">
         <is>
-          <t>Информационный (отчётность эмитента) +
-Раскрытие отчётности эмитента</t>
+          <t>Делистинг</t>
         </is>
       </c>
       <c r="H155" s="7" t="inlineStr">
@@ -8610,8 +8537,7 @@
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>Информационный (отчётность эмитента) +
-Раскрытие отчётности эмитента</t>
+          <t>Раскрытие отчётности</t>
         </is>
       </c>
       <c r="H156" s="2" t="inlineStr">
@@ -8669,8 +8595,7 @@
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>Информационный (отчётность эмитента) +
-Раскрытие отчётности эмитента</t>
+          <t>Раскрытие отчётности</t>
         </is>
       </c>
       <c r="H157" s="2" t="inlineStr">
@@ -8728,8 +8653,7 @@
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>Информационный (отчётность эмитента) +
-Раскрытие отчётности эмитента</t>
+          <t>Раскрытие отчётности</t>
         </is>
       </c>
       <c r="H158" s="2" t="inlineStr">
@@ -8777,8 +8701,7 @@
       </c>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>Информационный (отчётность эмитента) +
-Раскрытие отчётности эмитента</t>
+          <t>Раскрытие отчётности</t>
         </is>
       </c>
       <c r="H159" s="2" t="inlineStr">
@@ -8826,8 +8749,7 @@
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>Информационный (отчётность эмитента) +
-Раскрытие отчётности эмитента</t>
+          <t>Раскрытие отчётности</t>
         </is>
       </c>
       <c r="H160" s="2" t="inlineStr">
@@ -8875,8 +8797,7 @@
       </c>
       <c r="G161" s="2" t="inlineStr">
         <is>
-          <t>Информационный (отчётность эмитента) +
-Раскрытие отчётности эмитента</t>
+          <t>Утрата контроля</t>
         </is>
       </c>
       <c r="H161" s="2" t="inlineStr">
@@ -8934,8 +8855,7 @@
       </c>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>Информационный (отчётность эмитента) +
-Раскрытие отчётности эмитента</t>
+          <t>Раскрытие отчётности</t>
         </is>
       </c>
       <c r="H162" s="2" t="inlineStr">
@@ -8983,8 +8903,7 @@
       </c>
       <c r="G163" s="2" t="inlineStr">
         <is>
-          <t>Информационный (отчётность эмитента) +
-Раскрытие отчётности эмитента</t>
+          <t>Раскрытие отчётности</t>
         </is>
       </c>
       <c r="H163" s="2" t="inlineStr">
@@ -9032,8 +8951,7 @@
       </c>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>Информационный (отчётность эмитента) +
-Раскрытие отчётности эмитента</t>
+          <t>Раскрытие отчётности</t>
         </is>
       </c>
       <c r="H164" s="2" t="inlineStr">
@@ -9081,8 +8999,7 @@
       </c>
       <c r="G165" s="2" t="inlineStr">
         <is>
-          <t>Информационный (отчётность эмитента) +
-Раскрытие отчётности эмитента</t>
+          <t>Утрата контроля</t>
         </is>
       </c>
       <c r="H165" s="2" t="inlineStr">
@@ -9140,8 +9057,7 @@
       </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>Информационный (отчётность эмитента) +
-Раскрытие отчётности эмитента</t>
+          <t>Иное</t>
         </is>
       </c>
       <c r="H166" s="2" t="inlineStr">
@@ -9201,8 +9117,7 @@
       </c>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>Информационный (отчётность эмитента) +
-Раскрытие отчётности эмитента</t>
+          <t>Иное</t>
         </is>
       </c>
       <c r="H167" s="2" t="inlineStr">
@@ -9403,15 +9318,14 @@
       </c>
       <c r="D171" s="2" t="inlineStr"/>
       <c r="E171" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F171" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G171" s="2" t="inlineStr">
         <is>
-          <t>Информационный (отчётность эмитента) +
-Раскрытие отчётности эмитента</t>
+          <t>Раскрытие отчётности</t>
         </is>
       </c>
       <c r="H171" s="2" t="inlineStr">
@@ -9459,8 +9373,7 @@
       </c>
       <c r="G172" s="2" t="inlineStr">
         <is>
-          <t>Информационный (отчётность эмитента) +
-Раскрытие отчётности эмитента</t>
+          <t>Раскрытие отчётности</t>
         </is>
       </c>
       <c r="H172" s="2" t="inlineStr">
@@ -9498,379 +9411,384 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="7" t="inlineStr"/>
-      <c r="B173" s="7" t="inlineStr"/>
-      <c r="C173" s="7" t="inlineStr"/>
-      <c r="D173" s="7" t="inlineStr"/>
-      <c r="E173" s="7" t="inlineStr"/>
-      <c r="F173" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="G173" s="7" t="inlineStr">
-        <is>
-          <t>Информационный (отчётность эмитента) +
-Раскрытие отчётности эмитента</t>
-        </is>
-      </c>
-      <c r="H173" s="7" t="inlineStr">
-        <is>
-          <t>9.5. (из Программы)</t>
-        </is>
-      </c>
-      <c r="I173" s="7" t="inlineStr">
-        <is>
-          <t>Программа облигаций (e-disclosure)</t>
-        </is>
-      </c>
-      <c r="J173" s="7" t="inlineStr">
-        <is>
-          <t>п. 9.5</t>
-        </is>
-      </c>
-      <c r="K173" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L173" s="7" t="inlineStr">
-        <is>
-          <t>files.aspx</t>
-        </is>
-      </c>
-      <c r="M173" s="7" t="inlineStr">
-        <is>
-          <t>9.5. Программы). В случае принятия Эмитентом в соответствии с п. 9.5 Программы решения о частичном досрочном погашении Биржевых облигаций, владелец Биржевой облигации имеет право также на получение каждой досрочно погашаемой части номинальной стоимости Биржевой облигации. В случаях и в сроки, предусмотренные Программой и Условиями выпуска, владелец Биржевой облигации имеет право на получение дохода, порядок определения размера которого указан в п.9.3 Программы, а сроки выплаты (выплат) - в п. 9.</t>
-        </is>
-      </c>
-      <c r="N173" s="8" t="inlineStr">
-        <is>
-          <t>https://e-disclosure.ru/portal/files.aspx?id=37631&amp;type=7</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" s="4" t="inlineStr">
+      <c r="A173" s="4" t="inlineStr">
         <is>
           <t>ЭКОНОМЛИЗИНГ-001Р-06</t>
         </is>
       </c>
-      <c r="B174" s="4" t="inlineStr"/>
-      <c r="C174" s="4" t="inlineStr">
+      <c r="B173" s="4" t="inlineStr"/>
+      <c r="C173" s="4" t="inlineStr">
         <is>
           <t>RU000A1078Y6</t>
         </is>
       </c>
-      <c r="D174" s="4" t="inlineStr"/>
-      <c r="E174" s="4" t="inlineStr">
+      <c r="D173" s="4" t="inlineStr"/>
+      <c r="E173" s="4" t="inlineStr">
         <is>
           <t>Требует
 ручной проверки</t>
         </is>
       </c>
-      <c r="F174" s="5" t="inlineStr">
+      <c r="F173" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G174" s="5" t="inlineStr">
+      <c r="G173" s="5" t="inlineStr">
         <is>
           <t>⚠ ОШИБКА ПАРСИНГА</t>
         </is>
       </c>
-      <c r="H174" s="4" t="inlineStr">
+      <c r="H173" s="4" t="inlineStr">
         <is>
           <t>Не удалось извлечь ковенанты: Failed to download decision PDF for RU000A1078Y6</t>
         </is>
       </c>
-      <c r="I174" s="4" t="inlineStr">
-        <is>
-          <t>Решение о выпуске</t>
-        </is>
-      </c>
-      <c r="J174" s="4" t="inlineStr"/>
-      <c r="K174" s="4" t="inlineStr"/>
-      <c r="L174" s="4" t="inlineStr"/>
-      <c r="M174" s="5" t="inlineStr">
+      <c r="I173" s="4" t="inlineStr">
+        <is>
+          <t>Решение о выпуске</t>
+        </is>
+      </c>
+      <c r="J173" s="4" t="inlineStr"/>
+      <c r="K173" s="4" t="inlineStr"/>
+      <c r="L173" s="4" t="inlineStr"/>
+      <c r="M173" s="5" t="inlineStr">
         <is>
           <t>Требует ручной проверки</t>
         </is>
       </c>
-      <c r="N174" s="4" t="inlineStr"/>
+      <c r="N173" s="4" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>ЭКОНОМЛИЗИНГ-001Р-07</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr"/>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>RU000A107SX3</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr"/>
+      <c r="E174" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F174" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G174" s="2" t="inlineStr">
+        <is>
+          <t>Иное</t>
+        </is>
+      </c>
+      <c r="H174" s="2" t="inlineStr">
+        <is>
+          <t>5.6.1.</t>
+        </is>
+      </c>
+      <c r="I174" s="2" t="inlineStr">
+        <is>
+          <t>Решение о выпуске</t>
+        </is>
+      </c>
+      <c r="J174" s="2" t="inlineStr">
+        <is>
+          <t>п. 5.6.1, 1</t>
+        </is>
+      </c>
+      <c r="K174" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="L174" s="2" t="inlineStr">
+        <is>
+          <t>14989_0_Решение о выпуске 001Р-07.pdf</t>
+        </is>
+      </c>
+      <c r="M174" s="2" t="inlineStr">
+        <is>
+          <t>5.6.1. Досрочное погашение облигаций по требованию их владельцев. Предусмотрена возможность досрочного погашения Биржевых облигаций по требованию их владельцев в порядке и на условиях, установленных п. 9.5.1 Программы. Досрочное погашение Биржевых облигаций по требованию их владельцев производится денежными средствами в безналичном порядке в рублях Российской Федерации. Требование (заявление) о досрочном погашении Биржевых облигаций направляется в соответствии с действующим законодательством Рос</t>
+        </is>
+      </c>
+      <c r="N174" s="3" t="inlineStr">
+        <is>
+          <t>https://st.finam.ru/ipo/genconditions/14989_0_Решение о выпуске 001Р-07.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="175">
-      <c r="A175" s="2" t="inlineStr">
-        <is>
-          <t>ЭКОНОМЛИЗИНГ-001Р-07</t>
-        </is>
-      </c>
-      <c r="B175" s="2" t="inlineStr"/>
-      <c r="C175" s="2" t="inlineStr">
-        <is>
-          <t>RU000A107SX3</t>
-        </is>
-      </c>
-      <c r="D175" s="2" t="inlineStr"/>
-      <c r="E175" s="2" t="n">
+      <c r="A175" s="7" t="inlineStr"/>
+      <c r="B175" s="7" t="inlineStr"/>
+      <c r="C175" s="7" t="inlineStr"/>
+      <c r="D175" s="7" t="inlineStr"/>
+      <c r="E175" s="7" t="inlineStr"/>
+      <c r="F175" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="F175" s="2" t="n">
+      <c r="G175" s="7" t="inlineStr">
+        <is>
+          <t>Делистинг</t>
+        </is>
+      </c>
+      <c r="H175" s="7" t="inlineStr">
+        <is>
+          <t>Досрочное погашение в случае делистинга (из Программы)</t>
+        </is>
+      </c>
+      <c r="I175" s="7" t="inlineStr">
+        <is>
+          <t>Программа облигаций</t>
+        </is>
+      </c>
+      <c r="J175" s="7" t="inlineStr">
+        <is>
+          <t>п. 9.5.1</t>
+        </is>
+      </c>
+      <c r="K175" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L175" s="7" t="inlineStr">
+        <is>
+          <t>14989_0_Программа.pdf</t>
+        </is>
+      </c>
+      <c r="M175" s="7" t="inlineStr">
+        <is>
+          <t>азанным в настоящем пункте Программы, случаи досрочного погашения Биржевых облигаций по требованию их владельцев. В этом случае Условия выпуска должны содержать порядок и условия такого досрочного погашения Биржевых облигаций. Владельцы Биржевых облигаций вправе предъявить их к досрочному погашению в случае делистинга Биржевых облигаций на всех биржах, осуществивших их допуск к организованным торгам. Стоимость (порядок определения стоимости) досрочного погашения: Досрочное погашение Биржевых обл</t>
+        </is>
+      </c>
+      <c r="N175" s="8" t="inlineStr">
+        <is>
+          <t>https://st.finam.ru/ipo/decision/14989_0_Программа.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>ЭКОНОМЛИЗИНГ-001Р-08</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr"/>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>RU000A10B081</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr"/>
+      <c r="E176" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F176" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="G175" s="2" t="inlineStr">
-        <is>
-          <t>Информационный (отчётность эмитента) +
-Раскрытие отчётности эмитента</t>
-        </is>
-      </c>
-      <c r="H175" s="2" t="inlineStr">
+      <c r="G176" s="2" t="inlineStr">
+        <is>
+          <t>Иное</t>
+        </is>
+      </c>
+      <c r="H176" s="2" t="inlineStr">
         <is>
           <t>5.6.1.</t>
         </is>
       </c>
-      <c r="I175" s="2" t="inlineStr">
-        <is>
-          <t>Решение о выпуске</t>
-        </is>
-      </c>
-      <c r="J175" s="2" t="inlineStr">
+      <c r="I176" s="2" t="inlineStr">
+        <is>
+          <t>Решение о выпуске</t>
+        </is>
+      </c>
+      <c r="J176" s="2" t="inlineStr">
         <is>
           <t>п. 5.6.1, 1</t>
         </is>
       </c>
-      <c r="K175" s="2" t="n">
+      <c r="K176" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="L175" s="2" t="inlineStr">
-        <is>
-          <t>14989_0_Решение о выпуске 001Р-07.pdf</t>
-        </is>
-      </c>
-      <c r="M175" s="2" t="inlineStr">
+      <c r="L176" s="2" t="inlineStr">
+        <is>
+          <t>16252_0_Решение о выпуске 001Р-08.pdf</t>
+        </is>
+      </c>
+      <c r="M176" s="2" t="inlineStr">
         <is>
           <t>5.6.1. Досрочное погашение облигаций по требованию их владельцев. Предусмотрена возможность досрочного погашения Биржевых облигаций по требованию их владельцев в порядке и на условиях, установленных п. 9.5.1 Программы. Досрочное погашение Биржевых облигаций по требованию их владельцев производится денежными средствами в безналичном порядке в рублях Российской Федерации. Требование (заявление) о досрочном погашении Биржевых облигаций направляется в соответствии с действующим законодательством Рос</t>
         </is>
       </c>
-      <c r="N175" s="3" t="inlineStr">
-        <is>
-          <t>https://st.finam.ru/ipo/genconditions/14989_0_Решение о выпуске 001Р-07.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" s="7" t="inlineStr"/>
-      <c r="B176" s="7" t="inlineStr"/>
-      <c r="C176" s="7" t="inlineStr"/>
-      <c r="D176" s="7" t="inlineStr"/>
-      <c r="E176" s="7" t="inlineStr"/>
-      <c r="F176" s="7" t="n">
+      <c r="N176" s="3" t="inlineStr">
+        <is>
+          <t>https://st.finam.ru/ipo/genconditions/16252_0_Решение о выпуске 001Р-08.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="7" t="inlineStr"/>
+      <c r="B177" s="7" t="inlineStr"/>
+      <c r="C177" s="7" t="inlineStr"/>
+      <c r="D177" s="7" t="inlineStr"/>
+      <c r="E177" s="7" t="inlineStr"/>
+      <c r="F177" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="G176" s="7" t="inlineStr">
-        <is>
-          <t>Информационный (отчётность эмитента) +
-Раскрытие отчётности эмитента</t>
-        </is>
-      </c>
-      <c r="H176" s="7" t="inlineStr">
-        <is>
-          <t>Досрочное погашение в случае делистинга (из Программы)</t>
-        </is>
-      </c>
-      <c r="I176" s="7" t="inlineStr">
-        <is>
-          <t>Программа облигаций</t>
-        </is>
-      </c>
-      <c r="J176" s="7" t="inlineStr">
+      <c r="G177" s="7" t="inlineStr">
+        <is>
+          <t>Делистинг</t>
+        </is>
+      </c>
+      <c r="H177" s="7" t="inlineStr">
+        <is>
+          <t>в случае делистинга Биржевых облигаций на всех биржах, осуществивших их допуск к организованным торгам. (из Программы)</t>
+        </is>
+      </c>
+      <c r="I177" s="7" t="inlineStr">
+        <is>
+          <t>Программа облигаций (e-disclosure)</t>
+        </is>
+      </c>
+      <c r="J177" s="7" t="inlineStr">
         <is>
           <t>п. 9.5.1</t>
         </is>
       </c>
-      <c r="K176" s="7" t="n">
+      <c r="K177" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="L176" s="7" t="inlineStr">
-        <is>
-          <t>14989_0_Программа.pdf</t>
-        </is>
-      </c>
-      <c r="M176" s="7" t="inlineStr">
+      <c r="L177" s="7" t="inlineStr">
+        <is>
+          <t>files.aspx</t>
+        </is>
+      </c>
+      <c r="M177" s="7" t="inlineStr">
         <is>
           <t>азанным в настоящем пункте Программы, случаи досрочного погашения Биржевых облигаций по требованию их владельцев. В этом случае Условия выпуска должны содержать порядок и условия такого досрочного погашения Биржевых облигаций. Владельцы Биржевых облигаций вправе предъявить их к досрочному погашению в случае делистинга Биржевых облигаций на всех биржах, осуществивших их допуск к организованным торгам. Стоимость (порядок определения стоимости) досрочного погашения: Досрочное погашение Биржевых обл</t>
         </is>
       </c>
-      <c r="N176" s="8" t="inlineStr">
-        <is>
-          <t>https://st.finam.ru/ipo/decision/14989_0_Программа.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" s="2" t="inlineStr">
-        <is>
-          <t>ЭКОНОМЛИЗИНГ-001Р-08</t>
-        </is>
-      </c>
-      <c r="B177" s="2" t="inlineStr"/>
-      <c r="C177" s="2" t="inlineStr">
-        <is>
-          <t>RU000A10B081</t>
-        </is>
-      </c>
-      <c r="D177" s="2" t="inlineStr"/>
-      <c r="E177" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="F177" s="2" t="n">
+      <c r="N177" s="8" t="inlineStr">
+        <is>
+          <t>https://e-disclosure.ru/portal/files.aspx?id=37873&amp;type=7</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>ЭКОНОМЛИЗИНГ-002Р-01</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="inlineStr"/>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>RU000A10CDX0</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr"/>
+      <c r="E178" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F178" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G178" s="2" t="inlineStr">
+        <is>
+          <t>Положения о досрочном погашении</t>
+        </is>
+      </c>
+      <c r="H178" s="2" t="inlineStr">
+        <is>
+          <t>Put-опция у владельцев отсутствует</t>
+        </is>
+      </c>
+      <c r="I178" s="2" t="inlineStr">
+        <is>
+          <t>Решение о выпуске</t>
+        </is>
+      </c>
+      <c r="J178" s="2" t="inlineStr"/>
+      <c r="K178" s="2" t="inlineStr"/>
+      <c r="L178" s="2" t="inlineStr">
+        <is>
+          <t>17045_0_Решение о выпуске 002Р-01.pdf</t>
+        </is>
+      </c>
+      <c r="M178" s="2" t="inlineStr"/>
+      <c r="N178" s="3" t="inlineStr">
+        <is>
+          <t>https://st.finam.ru/ipo/genconditions/17045_0_Решение о выпуске 002Р-01.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="7" t="inlineStr">
+        <is>
+          <t>ЭКОНОМЛИЗИНГ-002Р-02</t>
+        </is>
+      </c>
+      <c r="B179" s="7" t="inlineStr"/>
+      <c r="C179" s="7" t="inlineStr">
+        <is>
+          <t>RU000A10ERA4</t>
+        </is>
+      </c>
+      <c r="D179" s="7" t="inlineStr"/>
+      <c r="E179" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="G177" s="2" t="inlineStr">
-        <is>
-          <t>Информационный (отчётность эмитента) +
-Раскрытие отчётности эмитента</t>
-        </is>
-      </c>
-      <c r="H177" s="2" t="inlineStr">
-        <is>
-          <t>5.6.1.</t>
-        </is>
-      </c>
-      <c r="I177" s="2" t="inlineStr">
-        <is>
-          <t>Решение о выпуске</t>
-        </is>
-      </c>
-      <c r="J177" s="2" t="inlineStr">
-        <is>
-          <t>п. 5.6.1, 1</t>
-        </is>
-      </c>
-      <c r="K177" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="L177" s="2" t="inlineStr">
-        <is>
-          <t>16252_0_Решение о выпуске 001Р-08.pdf</t>
-        </is>
-      </c>
-      <c r="M177" s="2" t="inlineStr">
-        <is>
-          <t>5.6.1. Досрочное погашение облигаций по требованию их владельцев. Предусмотрена возможность досрочного погашения Биржевых облигаций по требованию их владельцев в порядке и на условиях, установленных п. 9.5.1 Программы. Досрочное погашение Биржевых облигаций по требованию их владельцев производится денежными средствами в безналичном порядке в рублях Российской Федерации. Требование (заявление) о досрочном погашении Биржевых облигаций направляется в соответствии с действующим законодательством Рос</t>
-        </is>
-      </c>
-      <c r="N177" s="3" t="inlineStr">
-        <is>
-          <t>https://st.finam.ru/ipo/genconditions/16252_0_Решение о выпуске 001Р-08.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" s="7" t="inlineStr"/>
-      <c r="B178" s="7" t="inlineStr"/>
-      <c r="C178" s="7" t="inlineStr"/>
-      <c r="D178" s="7" t="inlineStr"/>
-      <c r="E178" s="7" t="inlineStr"/>
-      <c r="F178" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G178" s="7" t="inlineStr">
-        <is>
-          <t>Информационный (отчётность эмитента) +
-Раскрытие отчётности эмитента</t>
-        </is>
-      </c>
-      <c r="H178" s="7" t="inlineStr">
-        <is>
-          <t>Досрочное погашение в случае делистинга (из Программы)</t>
-        </is>
-      </c>
-      <c r="I178" s="7" t="inlineStr">
+      <c r="F179" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G179" s="7" t="inlineStr">
+        <is>
+          <t>Делистинг</t>
+        </is>
+      </c>
+      <c r="H179" s="7" t="inlineStr">
+        <is>
+          <t>в случае делистинга Биржевых облигаций на всех биржах, осуществивших их допуск к организованным торгам. (из Программы)</t>
+        </is>
+      </c>
+      <c r="I179" s="7" t="inlineStr">
         <is>
           <t>Программа облигаций (e-disclosure)</t>
         </is>
       </c>
-      <c r="J178" s="7" t="inlineStr">
+      <c r="J179" s="7" t="inlineStr">
         <is>
           <t>п. 9.5.1</t>
         </is>
       </c>
-      <c r="K178" s="7" t="n">
+      <c r="K179" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="L178" s="7" t="inlineStr">
+      <c r="L179" s="7" t="inlineStr">
         <is>
           <t>files.aspx</t>
         </is>
       </c>
-      <c r="M178" s="7" t="inlineStr">
+      <c r="M179" s="7" t="inlineStr">
         <is>
           <t>азанным в настоящем пункте Программы, случаи досрочного погашения Биржевых облигаций по требованию их владельцев. В этом случае Условия выпуска должны содержать порядок и условия такого досрочного погашения Биржевых облигаций. Владельцы Биржевых облигаций вправе предъявить их к досрочному погашению в случае делистинга Биржевых облигаций на всех биржах, осуществивших их допуск к организованным торгам. Стоимость (порядок определения стоимости) досрочного погашения: Досрочное погашение Биржевых обл</t>
         </is>
       </c>
-      <c r="N178" s="8" t="inlineStr">
+      <c r="N179" s="8" t="inlineStr">
         <is>
           <t>https://e-disclosure.ru/portal/files.aspx?id=37873&amp;type=7</t>
-        </is>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" s="2" t="inlineStr">
-        <is>
-          <t>ЭКОНОМЛИЗИНГ-002Р-01</t>
-        </is>
-      </c>
-      <c r="B179" s="2" t="inlineStr"/>
-      <c r="C179" s="2" t="inlineStr">
-        <is>
-          <t>RU000A10CDX0</t>
-        </is>
-      </c>
-      <c r="D179" s="2" t="inlineStr"/>
-      <c r="E179" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F179" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G179" s="2" t="inlineStr">
-        <is>
-          <t>Положения о досрочном погашении</t>
-        </is>
-      </c>
-      <c r="H179" s="2" t="inlineStr">
-        <is>
-          <t>Put-опция у владельцев отсутствует</t>
-        </is>
-      </c>
-      <c r="I179" s="2" t="inlineStr">
-        <is>
-          <t>Решение о выпуске</t>
-        </is>
-      </c>
-      <c r="J179" s="2" t="inlineStr"/>
-      <c r="K179" s="2" t="inlineStr"/>
-      <c r="L179" s="2" t="inlineStr">
-        <is>
-          <t>17045_0_Решение о выпуске 002Р-01.pdf</t>
-        </is>
-      </c>
-      <c r="M179" s="2" t="inlineStr"/>
-      <c r="N179" s="3" t="inlineStr">
-        <is>
-          <t>https://st.finam.ru/ipo/genconditions/17045_0_Решение о выпуске 002Р-01.pdf</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="7" t="inlineStr">
         <is>
-          <t>ЭКОНОМЛИЗИНГ-002Р-02</t>
+          <t>ЭКОНОМЛИЗИНГ-002Р-03</t>
         </is>
       </c>
       <c r="B180" s="7" t="inlineStr"/>
       <c r="C180" s="7" t="inlineStr">
         <is>
-          <t>RU000A10ERA4</t>
+          <t>RU000A10FSV5</t>
         </is>
       </c>
       <c r="D180" s="7" t="inlineStr"/>
@@ -9882,13 +9800,12 @@
       </c>
       <c r="G180" s="7" t="inlineStr">
         <is>
-          <t>Информационный (отчётность эмитента) +
-Раскрытие отчётности эмитента</t>
+          <t>Делистинг</t>
         </is>
       </c>
       <c r="H180" s="7" t="inlineStr">
         <is>
-          <t>Досрочное погашение в случае делистинга (из Программы)</t>
+          <t>в случае делистинга Биржевых облигаций на всех биржах, осуществивших их допуск к организованным торгам. (из Программы)</t>
         </is>
       </c>
       <c r="I180" s="7" t="inlineStr">
@@ -9921,74 +9838,65 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="7" t="inlineStr">
-        <is>
-          <t>ЭКОНОМЛИЗИНГ-002Р-03</t>
-        </is>
-      </c>
-      <c r="B181" s="7" t="inlineStr"/>
-      <c r="C181" s="7" t="inlineStr">
-        <is>
-          <t>RU000A10FSV5</t>
-        </is>
-      </c>
-      <c r="D181" s="7" t="inlineStr"/>
-      <c r="E181" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F181" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G181" s="7" t="inlineStr">
-        <is>
-          <t>Информационный (отчётность эмитента) +
-Раскрытие отчётности эмитента</t>
-        </is>
-      </c>
-      <c r="H181" s="7" t="inlineStr">
-        <is>
-          <t>Досрочное погашение в случае делистинга (из Программы)</t>
-        </is>
-      </c>
-      <c r="I181" s="7" t="inlineStr">
-        <is>
-          <t>Программа облигаций (e-disclosure)</t>
-        </is>
-      </c>
-      <c r="J181" s="7" t="inlineStr">
-        <is>
-          <t>п. 9.5.1</t>
-        </is>
-      </c>
-      <c r="K181" s="7" t="n">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>ЭЛИТ СТРОЙ-БО-01</t>
+        </is>
+      </c>
+      <c r="B181" s="2" t="inlineStr"/>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>RU000A10BP46</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr"/>
+      <c r="E181" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="L181" s="7" t="inlineStr">
-        <is>
-          <t>files.aspx</t>
-        </is>
-      </c>
-      <c r="M181" s="7" t="inlineStr">
-        <is>
-          <t>азанным в настоящем пункте Программы, случаи досрочного погашения Биржевых облигаций по требованию их владельцев. В этом случае Условия выпуска должны содержать порядок и условия такого досрочного погашения Биржевых облигаций. Владельцы Биржевых облигаций вправе предъявить их к досрочному погашению в случае делистинга Биржевых облигаций на всех биржах, осуществивших их допуск к организованным торгам. Стоимость (порядок определения стоимости) досрочного погашения: Досрочное погашение Биржевых обл</t>
-        </is>
-      </c>
-      <c r="N181" s="8" t="inlineStr">
-        <is>
-          <t>https://e-disclosure.ru/portal/files.aspx?id=37873&amp;type=7</t>
+      <c r="F181" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G181" s="2" t="inlineStr">
+        <is>
+          <t>Положения о досрочном погашении</t>
+        </is>
+      </c>
+      <c r="H181" s="2" t="inlineStr">
+        <is>
+          <t>Put-опция у владельцев отсутствует</t>
+        </is>
+      </c>
+      <c r="I181" s="2" t="inlineStr">
+        <is>
+          <t>Решение о выпуске</t>
+        </is>
+      </c>
+      <c r="J181" s="2" t="inlineStr"/>
+      <c r="K181" s="2" t="inlineStr"/>
+      <c r="L181" s="2" t="inlineStr">
+        <is>
+          <t>11776_0_Решение о выпуске БО-01.pdf</t>
+        </is>
+      </c>
+      <c r="M181" s="2" t="inlineStr"/>
+      <c r="N181" s="3" t="inlineStr">
+        <is>
+          <t>https://st.finam.ru/ipo/genconditions/11776_0_Решение о выпуске БО-01.pdf</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>ЭЛИТ СТРОЙ-БО-01</t>
+          <t>ЭЛИТ СТРОЙ-002P-02</t>
         </is>
       </c>
       <c r="B182" s="2" t="inlineStr"/>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>RU000A10BP46</t>
+          <t>RU000A10E6J7</t>
         </is>
       </c>
       <c r="D182" s="2" t="inlineStr"/>
@@ -10019,26 +9927,26 @@
       <c r="K182" s="2" t="inlineStr"/>
       <c r="L182" s="2" t="inlineStr">
         <is>
-          <t>11776_0_Решение о выпуске БО-01.pdf</t>
+          <t>17745_0_Решение о выпуске 002Р-02.pdf</t>
         </is>
       </c>
       <c r="M182" s="2" t="inlineStr"/>
       <c r="N182" s="3" t="inlineStr">
         <is>
-          <t>https://st.finam.ru/ipo/genconditions/11776_0_Решение о выпуске БО-01.pdf</t>
+          <t>https://st.finam.ru/ipo/genconditions/17745_0_Решение о выпуске 002Р-02.pdf</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>ЭЛИТ СТРОЙ-002P-02</t>
+          <t>ЭЛИТ СТРОЙ-002P-03</t>
         </is>
       </c>
       <c r="B183" s="2" t="inlineStr"/>
       <c r="C183" s="2" t="inlineStr">
         <is>
-          <t>RU000A10E6J7</t>
+          <t>RU000A10FLJ5</t>
         </is>
       </c>
       <c r="D183" s="2" t="inlineStr"/>
@@ -10069,45 +9977,43 @@
       <c r="K183" s="2" t="inlineStr"/>
       <c r="L183" s="2" t="inlineStr">
         <is>
-          <t>17745_0_Решение о выпуске 002Р-02.pdf</t>
+          <t>18435_0_Решение_о_выпуске_002Р-03.pdf</t>
         </is>
       </c>
       <c r="M183" s="2" t="inlineStr"/>
       <c r="N183" s="3" t="inlineStr">
         <is>
-          <t>https://st.finam.ru/ipo/genconditions/17745_0_Решение о выпуске 002Р-02.pdf</t>
+          <t>https://st.finam.ru/ipo/genconditions/18435_0_Решение_о_выпуске_002Р-03.pdf</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>ЭЛИТ СТРОЙ-002P-03</t>
+          <t>ПКО ЮРИДИЧЕСКАЯ СЛУЖБА ВЗЫСКАНИЯ-001Р-01</t>
         </is>
       </c>
       <c r="B184" s="2" t="inlineStr"/>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>RU000A10FLJ5</t>
+          <t>RU000A10CN62</t>
         </is>
       </c>
       <c r="D184" s="2" t="inlineStr"/>
       <c r="E184" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F184" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="F184" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="G184" s="2" t="inlineStr">
         <is>
-          <t>Положения о досрочном погашении</t>
+          <t>Раскрытие отчётности</t>
         </is>
       </c>
       <c r="H184" s="2" t="inlineStr">
         <is>
-          <t>Put-опция у владельцев отсутствует</t>
+          <t>Нераскрытие Эмитентом на Странице в сети Интернет промежуточной бухгалтерской (финансовой) отчетности Эмитента, составленной в соответствии с Федеральным законом от 06</t>
         </is>
       </c>
       <c r="I184" s="2" t="inlineStr">
@@ -10115,48 +10021,47 @@
           <t>Решение о выпуске</t>
         </is>
       </c>
-      <c r="J184" s="2" t="inlineStr"/>
-      <c r="K184" s="2" t="inlineStr"/>
+      <c r="J184" s="2" t="inlineStr">
+        <is>
+          <t>п. 5.6.1, 1</t>
+        </is>
+      </c>
+      <c r="K184" s="2" t="n">
+        <v>7</v>
+      </c>
       <c r="L184" s="2" t="inlineStr">
         <is>
-          <t>18435_0_Решение_о_выпуске_002Р-03.pdf</t>
-        </is>
-      </c>
-      <c r="M184" s="2" t="inlineStr"/>
+          <t>17143_0_Решение_о_выпуске_001Р-01.pdf</t>
+        </is>
+      </c>
+      <c r="M184" s="2" t="inlineStr">
+        <is>
+          <t>Нераскрытие Эмитентом на Странице в сети Интернет промежуточной бухгалтерской (финансовой) отчетности Эмитента, составленной в соответствии с Федеральным законом от 06.12.2011 №402-ФЗ «О бухгалтерском учете» и Российскими стандартами бухгалтерского учета, за отчетные периоды, состоящие из 3, 6, и 9 месяцев отчетного года (далее – промежуточная бухгалтерская (финансовая) отчетность Эмитента), в течение 60 дней после даты окончания отчетного периода, за который составлена отчетность. 7 Моментом на</t>
+        </is>
+      </c>
       <c r="N184" s="3" t="inlineStr">
         <is>
-          <t>https://st.finam.ru/ipo/genconditions/18435_0_Решение_о_выпуске_002Р-03.pdf</t>
+          <t>https://st.finam.ru/ipo/genconditions/17143_0_Решение_о_выпуске_001Р-01.pdf</t>
         </is>
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="2" t="inlineStr">
-        <is>
-          <t>ПКО ЮРИДИЧЕСКАЯ СЛУЖБА ВЗЫСКАНИЯ-001Р-01</t>
-        </is>
-      </c>
+      <c r="A185" s="2" t="inlineStr"/>
       <c r="B185" s="2" t="inlineStr"/>
-      <c r="C185" s="2" t="inlineStr">
-        <is>
-          <t>RU000A10CN62</t>
-        </is>
-      </c>
+      <c r="C185" s="2" t="inlineStr"/>
       <c r="D185" s="2" t="inlineStr"/>
-      <c r="E185" s="2" t="n">
-        <v>3</v>
-      </c>
+      <c r="E185" s="2" t="inlineStr"/>
       <c r="F185" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>Информационный (отчётность эмитента) +
-Раскрытие отчётности эмитента</t>
+          <t>Раскрытие отчётности</t>
         </is>
       </c>
       <c r="H185" s="2" t="inlineStr">
         <is>
-          <t>Нераскрытие Эмитентом на Странице в сети Интернет промежуточной бухгалтерской (финансовой) отчетности Эмитента, составленной в соответствии с Федеральным законом от 06</t>
+          <t>Нераскрытие Эмитентом на Странице в сети Интернет промежуточной бухгалтерской (финансовой) отчетности Поручителя, составленной в соответствии с Федеральным законом от 06</t>
         </is>
       </c>
       <c r="I185" s="2" t="inlineStr">
@@ -10166,7 +10071,7 @@
       </c>
       <c r="J185" s="2" t="inlineStr">
         <is>
-          <t>п. 5.6.1, 1</t>
+          <t>п. 5.6.1, 2</t>
         </is>
       </c>
       <c r="K185" s="2" t="n">
@@ -10179,7 +10084,7 @@
       </c>
       <c r="M185" s="2" t="inlineStr">
         <is>
-          <t>Нераскрытие Эмитентом на Странице в сети Интернет промежуточной бухгалтерской (финансовой) отчетности Эмитента, составленной в соответствии с Федеральным законом от 06.12.2011 №402-ФЗ «О бухгалтерском учете» и Российскими стандартами бухгалтерского учета, за отчетные периоды, состоящие из 3, 6, и 9 месяцев отчетного года (далее – промежуточная бухгалтерская (финансовая) отчетность Эмитента), в течение 60 дней после даты окончания отчетного периода, за который составлена отчетность. 7 Моментом на</t>
+          <t xml:space="preserve">Нераскрытие Эмитентом на Странице в сети Интернет промежуточной бухгалтерской (финансовой) отчетности Поручителя, составленной в соответствии с Федеральным законом от 06.12.2011 №402-ФЗ «О бухгалтерском учете» и Российскими стандартами бухгалтерского учета, за отчетные периоды, состоящие из 3, 6, и 9 месяцев отчетного года (далее – промежуточная бухгалтерская (финансовая) отчетность Поручителя), в течение 60 дней после даты окончания отчетного периода, за который составлена отчетность. Моментом </t>
         </is>
       </c>
       <c r="N185" s="3" t="inlineStr">
@@ -10195,17 +10100,16 @@
       <c r="D186" s="2" t="inlineStr"/>
       <c r="E186" s="2" t="inlineStr"/>
       <c r="F186" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G186" s="2" t="inlineStr">
         <is>
-          <t>Информационный (отчётность эмитента) +
-Раскрытие отчётности эмитента</t>
+          <t>Раскрытие отчётности</t>
         </is>
       </c>
       <c r="H186" s="2" t="inlineStr">
         <is>
-          <t>Нераскрытие Эмитентом на Странице в сети Интернет промежуточной бухгалтерской (финансовой) отчетности Поручителя, составленной в соответствии с Федеральным законом от 06</t>
+          <t>Нераскрытие Эмитентом на Странице в сети Интернет годовой консолидированной финансовой отчетности Поручителя, составленной в соответствии с Международными стандартами финансовой отчетности, с приложен…</t>
         </is>
       </c>
       <c r="I186" s="2" t="inlineStr">
@@ -10215,7 +10119,7 @@
       </c>
       <c r="J186" s="2" t="inlineStr">
         <is>
-          <t>п. 5.6.1, 2</t>
+          <t>п. 5.6.1, 3</t>
         </is>
       </c>
       <c r="K186" s="2" t="n">
@@ -10228,7 +10132,7 @@
       </c>
       <c r="M186" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Нераскрытие Эмитентом на Странице в сети Интернет промежуточной бухгалтерской (финансовой) отчетности Поручителя, составленной в соответствии с Федеральным законом от 06.12.2011 №402-ФЗ «О бухгалтерском учете» и Российскими стандартами бухгалтерского учета, за отчетные периоды, состоящие из 3, 6, и 9 месяцев отчетного года (далее – промежуточная бухгалтерская (финансовая) отчетность Поручителя), в течение 60 дней после даты окончания отчетного периода, за который составлена отчетность. Моментом </t>
+          <t>Нераскрытие Эмитентом на Странице в сети Интернет годовой консолидированной финансовой отчетности Поручителя, составленной в соответствии с Международными стандартами финансовой отчетности, с приложением аудиторского заключения в отношении указанной отчетности, в срок не позднее 120 дней после даты окончания отчетного года. Моментом наступления данного События досрочного погашения по требованию владельцев Биржевых облигаций является первый рабочий день после истечения срока, указанного выше, для</t>
         </is>
       </c>
       <c r="N186" s="3" t="inlineStr">
@@ -10238,23 +10142,34 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="2" t="inlineStr"/>
+      <c r="A187" s="2" t="inlineStr">
+        <is>
+          <t>АКБ ДЕРЖАВА-03</t>
+        </is>
+      </c>
       <c r="B187" s="2" t="inlineStr"/>
-      <c r="C187" s="2" t="inlineStr"/>
+      <c r="C187" s="2" t="inlineStr">
+        <is>
+          <t>RU000A0JWB59</t>
+        </is>
+      </c>
       <c r="D187" s="2" t="inlineStr"/>
-      <c r="E187" s="2" t="inlineStr"/>
-      <c r="F187" s="2" t="n">
-        <v>3</v>
+      <c r="E187" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F187" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="G187" s="2" t="inlineStr">
         <is>
-          <t>Информационный (отчётность эмитента) +
-Раскрытие отчётности эмитента</t>
+          <t>Положения о досрочном погашении</t>
         </is>
       </c>
       <c r="H187" s="2" t="inlineStr">
         <is>
-          <t>Нераскрытие Эмитентом на Странице в сети Интернет годовой консолидированной финансовой отчетности Поручителя, составленной в соответствии с Международными стандартами финансовой отчетности, с приложен…</t>
+          <t>Put-опция у владельцев отсутствует</t>
         </is>
       </c>
       <c r="I187" s="2" t="inlineStr">
@@ -10262,59 +10177,47 @@
           <t>Решение о выпуске</t>
         </is>
       </c>
-      <c r="J187" s="2" t="inlineStr">
-        <is>
-          <t>п. 5.6.1, 3</t>
-        </is>
-      </c>
-      <c r="K187" s="2" t="n">
-        <v>7</v>
-      </c>
+      <c r="J187" s="2" t="inlineStr"/>
+      <c r="K187" s="2" t="inlineStr"/>
       <c r="L187" s="2" t="inlineStr">
         <is>
-          <t>17143_0_Решение_о_выпуске_001Р-01.pdf</t>
-        </is>
-      </c>
-      <c r="M187" s="2" t="inlineStr">
-        <is>
-          <t>Нераскрытие Эмитентом на Странице в сети Интернет годовой консолидированной финансовой отчетности Поручителя, составленной в соответствии с Международными стандартами финансовой отчетности, с приложением аудиторского заключения в отношении указанной отчетности, в срок не позднее 120 дней после даты окончания отчетного года. Моментом наступления данного События досрочного погашения по требованию владельцев Биржевых облигаций является первый рабочий день после истечения срока, указанного выше, для</t>
-        </is>
-      </c>
+          <t>6936_0_Решение.pdf</t>
+        </is>
+      </c>
+      <c r="M187" s="2" t="inlineStr"/>
       <c r="N187" s="3" t="inlineStr">
         <is>
-          <t>https://st.finam.ru/ipo/genconditions/17143_0_Решение_о_выпуске_001Р-01.pdf</t>
+          <t>https://st.finam.ru/ipo/decision/6936_0_Решение.pdf</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>АКБ ДЕРЖАВА-03</t>
+          <t>АЛТИМЕЙТ ЭДЬЮКЕЙШН-БО-П01</t>
         </is>
       </c>
       <c r="B188" s="2" t="inlineStr"/>
       <c r="C188" s="2" t="inlineStr">
         <is>
-          <t>RU000A0JWB59</t>
+          <t>RU000A10C7C2</t>
         </is>
       </c>
       <c r="D188" s="2" t="inlineStr"/>
       <c r="E188" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F188" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="F188" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="G188" s="2" t="inlineStr">
         <is>
-          <t>Положения о досрочном погашении</t>
+          <t>Раскрытие отчётности</t>
         </is>
       </c>
       <c r="H188" s="2" t="inlineStr">
         <is>
-          <t>Put-опция у владельцев отсутствует</t>
+          <t>5.6.1.</t>
         </is>
       </c>
       <c r="I188" s="2" t="inlineStr">
@@ -10322,30 +10225,40 @@
           <t>Решение о выпуске</t>
         </is>
       </c>
-      <c r="J188" s="2" t="inlineStr"/>
-      <c r="K188" s="2" t="inlineStr"/>
+      <c r="J188" s="2" t="inlineStr">
+        <is>
+          <t>п. 5.6.1, 1</t>
+        </is>
+      </c>
+      <c r="K188" s="2" t="n">
+        <v>6</v>
+      </c>
       <c r="L188" s="2" t="inlineStr">
         <is>
-          <t>6936_0_Решение.pdf</t>
-        </is>
-      </c>
-      <c r="M188" s="2" t="inlineStr"/>
+          <t>16927_0_Решение о выпуске БО-П01.pdf</t>
+        </is>
+      </c>
+      <c r="M188" s="2" t="inlineStr">
+        <is>
+          <t>5.6.1. Досрочное погашение облигаций по требованию их владельцев: Владельцы Биржевых облигаций имеют право требовать досрочного погашения Биржевых облигаций в случае наступления События досрочного погашения по требованию владельцев Биржевых облигаций (далее– «Событие»): Нарушение Эмитентом, сроков публикации годовой аудированной консолидированной финансовой отчетности АО «АЭ Холдинг» (ОГРН 1247700208337), составленной в соответствии с Международными стандартами финансовой отчетности (далее - МСФ</t>
+        </is>
+      </c>
       <c r="N188" s="3" t="inlineStr">
         <is>
-          <t>https://st.finam.ru/ipo/decision/6936_0_Решение.pdf</t>
+          <t>https://st.finam.ru/ipo/genconditions/16927_0_Решение о выпуске БО-П01.pdf</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>АЛТИМЕЙТ ЭДЬЮКЕЙШН-БО-П01</t>
+          <t>ГЕЛЬТЕК-МЕДИКА-БО-01</t>
         </is>
       </c>
       <c r="B189" s="2" t="inlineStr"/>
       <c r="C189" s="2" t="inlineStr">
         <is>
-          <t>RU000A10C7C2</t>
+          <t>RU000A10D3G1</t>
         </is>
       </c>
       <c r="D189" s="2" t="inlineStr"/>
@@ -10357,13 +10270,13 @@
       </c>
       <c r="G189" s="2" t="inlineStr">
         <is>
-          <t>Информационный (отчётность эмитента) +
-Раскрытие отчётности эмитента</t>
+          <t>Иное</t>
         </is>
       </c>
       <c r="H189" s="2" t="inlineStr">
         <is>
-          <t>5.6.1.</t>
+          <t>5.6.1 Решения, а также
+действующим законодательством Российской Федерации.</t>
         </is>
       </c>
       <c r="I189" s="2" t="inlineStr">
@@ -10377,53 +10290,51 @@
         </is>
       </c>
       <c r="K189" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L189" s="2" t="inlineStr">
         <is>
-          <t>16927_0_Решение о выпуске БО-П01.pdf</t>
+          <t>17268_0_Решение о выпуске БО-01.pdf</t>
         </is>
       </c>
       <c r="M189" s="2" t="inlineStr">
         <is>
-          <t>5.6.1. Досрочное погашение облигаций по требованию их владельцев: Владельцы Биржевых облигаций имеют право требовать досрочного погашения Биржевых облигаций в случае наступления События досрочного погашения по требованию владельцев Биржевых облигаций (далее– «Событие»): Нарушение Эмитентом, сроков публикации годовой аудированной консолидированной финансовой отчетности АО «АЭ Холдинг» (ОГРН 1247700208337), составленной в соответствии с Международными стандартами финансовой отчетности (далее - МСФ</t>
+          <t>5.6.1 Решения, а также действующим законодательством Российской Федерации.</t>
         </is>
       </c>
       <c r="N189" s="3" t="inlineStr">
         <is>
-          <t>https://st.finam.ru/ipo/genconditions/16927_0_Решение о выпуске БО-П01.pdf</t>
+          <t>https://st.finam.ru/ipo/genconditions/17268_0_Решение о выпуске БО-01.pdf</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>ГЕЛЬТЕК-МЕДИКА-БО-01</t>
+          <t>ТАЛЬВЕН-БО-П01</t>
         </is>
       </c>
       <c r="B190" s="2" t="inlineStr"/>
       <c r="C190" s="2" t="inlineStr">
         <is>
-          <t>RU000A10D3G1</t>
+          <t>RU000A10DSX6</t>
         </is>
       </c>
       <c r="D190" s="2" t="inlineStr"/>
       <c r="E190" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F190" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G190" s="2" t="inlineStr">
         <is>
-          <t>Информационный (отчётность эмитента) +
-Раскрытие отчётности эмитента</t>
+          <t>Раскрытие отчётности</t>
         </is>
       </c>
       <c r="H190" s="2" t="inlineStr">
         <is>
-          <t>5.6.1 Решения, а также
-действующим законодательством Российской Федерации.</t>
+          <t>Нарушение Эмитентом сроков публикации годовой аудированной консолидированной финансовой отчетности, составленной в соответствии с Международными стандартами финансовой отчетности (далее - МСФО) с прил…</t>
         </is>
       </c>
       <c r="I190" s="2" t="inlineStr">
@@ -10437,52 +10348,41 @@
         </is>
       </c>
       <c r="K190" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L190" s="2" t="inlineStr">
         <is>
-          <t>17268_0_Решение о выпуске БО-01.pdf</t>
+          <t>17569_0_Решение о выпуске_БО-П01.pdf</t>
         </is>
       </c>
       <c r="M190" s="2" t="inlineStr">
         <is>
-          <t>5.6.1 Решения, а также действующим законодательством Российской Федерации.</t>
+          <t xml:space="preserve">Нарушение Эмитентом сроков публикации годовой аудированной консолидированной финансовой отчетности, составленной в соответствии с Международными стандартами финансовой отчетности (далее - МСФО) с приложением аудиторского заключения в отношении такой отчетности (далее - Финансовая отчетность), а именно неопубликование такой отчётности в указанный ниже срок. Для целей выполнения обязательства, предусмотренного настоящим подпунктом, Эмитент в течение срока обращения Биржевых облигаций принимает на </t>
         </is>
       </c>
       <c r="N190" s="3" t="inlineStr">
         <is>
-          <t>https://st.finam.ru/ipo/genconditions/17268_0_Решение о выпуске БО-01.pdf</t>
+          <t>https://st.finam.ru/ipo/genconditions/17569_0_Решение о выпуске_БО-П01.pdf</t>
         </is>
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="2" t="inlineStr">
-        <is>
-          <t>ТАЛЬВЕН-БО-П01</t>
-        </is>
-      </c>
+      <c r="A191" s="2" t="inlineStr"/>
       <c r="B191" s="2" t="inlineStr"/>
-      <c r="C191" s="2" t="inlineStr">
-        <is>
-          <t>RU000A10DSX6</t>
-        </is>
-      </c>
+      <c r="C191" s="2" t="inlineStr"/>
       <c r="D191" s="2" t="inlineStr"/>
-      <c r="E191" s="2" t="n">
+      <c r="E191" s="2" t="inlineStr"/>
+      <c r="F191" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F191" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>Информационный (отчётность эмитента) +
-Раскрытие отчётности эмитента</t>
+          <t>Выплата дивидендов, распределение прибыли</t>
         </is>
       </c>
       <c r="H191" s="2" t="inlineStr">
         <is>
-          <t>Нарушение Эмитентом сроков публикации годовой аудированной консолидированной финансовой отчетности, составленной в соответствии с Международными стандартами финансовой отчетности (далее - МСФО) с прил…</t>
+          <t>Снижение суммарной доли прямого и/или косвенного участия Крючкова Дмитрия Анатольевича (ИНН 772124380803) в уставном капитале Эмитента до уровня менее 25% (Двадцати пяти процентов) в результате продаж…</t>
         </is>
       </c>
       <c r="I191" s="2" t="inlineStr">
@@ -10492,7 +10392,7 @@
       </c>
       <c r="J191" s="2" t="inlineStr">
         <is>
-          <t>п. 5.6.1, 1</t>
+          <t>п. 5.6.1, 2</t>
         </is>
       </c>
       <c r="K191" s="2" t="n">
@@ -10505,7 +10405,7 @@
       </c>
       <c r="M191" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Нарушение Эмитентом сроков публикации годовой аудированной консолидированной финансовой отчетности, составленной в соответствии с Международными стандартами финансовой отчетности (далее - МСФО) с приложением аудиторского заключения в отношении такой отчетности (далее - Финансовая отчетность), а именно неопубликование такой отчётности в указанный ниже срок. Для целей выполнения обязательства, предусмотренного настоящим подпунктом, Эмитент в течение срока обращения Биржевых облигаций принимает на </t>
+          <t>Снижение суммарной доли прямого и/или косвенного участия Крючкова Дмитрия Анатольевича (ИНН 772124380803) в уставном капитале Эмитента до уровня менее 25% (Двадцати пяти процентов) в результате продажи, обмена, дарения, передачи в качестве обеспечения по кредитному соглашению или иного действия, направленного на отчуждение доли такого участника в уставном капитале Эмитента. Моментом наступления указанного События является дата, в которую имело место прекращение владения (снижение суммарной доли)</t>
         </is>
       </c>
       <c r="N191" s="3" t="inlineStr">
@@ -10515,23 +10415,32 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="2" t="inlineStr"/>
+      <c r="A192" s="2" t="inlineStr">
+        <is>
+          <t>ЛАЗЕРНЫЕ СИСТЕМЫ-БО-01</t>
+        </is>
+      </c>
       <c r="B192" s="2" t="inlineStr"/>
-      <c r="C192" s="2" t="inlineStr"/>
+      <c r="C192" s="2" t="inlineStr">
+        <is>
+          <t>RU000A109JX8</t>
+        </is>
+      </c>
       <c r="D192" s="2" t="inlineStr"/>
-      <c r="E192" s="2" t="inlineStr"/>
+      <c r="E192" s="2" t="n">
+        <v>2</v>
+      </c>
       <c r="F192" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>Информационный (отчётность эмитента) +
-Раскрытие отчётности эмитента</t>
+          <t>Раскрытие отчётности</t>
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr">
         <is>
-          <t>Снижение суммарной доли прямого и/или косвенного участия Крючкова Дмитрия Анатольевича (ИНН 772124380803) в уставном капитале Эмитента до уровня менее 25% (Двадцати пяти процентов) в результате продаж…</t>
+          <t>Не опубликование или опубликование промежуточной бухгалтерской отчетности Эмитента с нарушением сроков, указанных ниже</t>
         </is>
       </c>
       <c r="I192" s="2" t="inlineStr">
@@ -10541,7 +10450,7 @@
       </c>
       <c r="J192" s="2" t="inlineStr">
         <is>
-          <t>п. 5.6.1, 2</t>
+          <t>п. 5.6.1, 1</t>
         </is>
       </c>
       <c r="K192" s="2" t="n">
@@ -10549,48 +10458,37 @@
       </c>
       <c r="L192" s="2" t="inlineStr">
         <is>
-          <t>17569_0_Решение о выпуске_БО-П01.pdf</t>
+          <t>15622_0_Решение о выпуске БО-01.pdf</t>
         </is>
       </c>
       <c r="M192" s="2" t="inlineStr">
         <is>
-          <t>Снижение суммарной доли прямого и/или косвенного участия Крючкова Дмитрия Анатольевича (ИНН 772124380803) в уставном капитале Эмитента до уровня менее 25% (Двадцати пяти процентов) в результате продажи, обмена, дарения, передачи в качестве обеспечения по кредитному соглашению или иного действия, направленного на отчуждение доли такого участника в уставном капитале Эмитента. Моментом наступления указанного События является дата, в которую имело место прекращение владения (снижение суммарной доли)</t>
+          <t>Не опубликование или опубликование промежуточной бухгалтерской отчетности Эмитента с нарушением сроков, указанных ниже. Под промежуточной бухгалтерской отчетностью Эмитента подразумевается неаудированная промежуточная бухгалтерская отчетность (Бухгалтерский баланс, Отчет о финансовых результатах) Эмитента за отчетные периоды, состоящие из 3, 6 и 9 месяцев отчетного года, составленная в соответствии с Российскими стандартами бухгалтерского учета (далее – РСБУ). Моментом наступления указанного Соб</t>
         </is>
       </c>
       <c r="N192" s="3" t="inlineStr">
         <is>
-          <t>https://st.finam.ru/ipo/genconditions/17569_0_Решение о выпуске_БО-П01.pdf</t>
+          <t>https://st.finam.ru/ipo/genconditions/15622_0_Решение о выпуске БО-01.pdf</t>
         </is>
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="2" t="inlineStr">
-        <is>
-          <t>ЛАЗЕРНЫЕ СИСТЕМЫ-БО-01</t>
-        </is>
-      </c>
+      <c r="A193" s="2" t="inlineStr"/>
       <c r="B193" s="2" t="inlineStr"/>
-      <c r="C193" s="2" t="inlineStr">
-        <is>
-          <t>RU000A109JX8</t>
-        </is>
-      </c>
+      <c r="C193" s="2" t="inlineStr"/>
       <c r="D193" s="2" t="inlineStr"/>
-      <c r="E193" s="2" t="n">
+      <c r="E193" s="2" t="inlineStr"/>
+      <c r="F193" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F193" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="G193" s="2" t="inlineStr">
         <is>
-          <t>Информационный (отчётность эмитента) +
-Раскрытие отчётности эмитента</t>
+          <t>Раскрытие отчётности</t>
         </is>
       </c>
       <c r="H193" s="2" t="inlineStr">
         <is>
-          <t>Не опубликование или опубликование промежуточной бухгалтерской отчетности Эмитента с нарушением сроков, указанных ниже</t>
+          <t>Не опубликование или опубликование годовой индивидуальной финансовой отчетности Эмитента, составленной в соответствии с Международными стандартами финансовой отчетности (МСФО), вместе с аудиторским за…</t>
         </is>
       </c>
       <c r="I193" s="2" t="inlineStr">
@@ -10600,7 +10498,7 @@
       </c>
       <c r="J193" s="2" t="inlineStr">
         <is>
-          <t>п. 5.6.1, 1</t>
+          <t>п. 5.6.1, 2</t>
         </is>
       </c>
       <c r="K193" s="2" t="n">
@@ -10613,7 +10511,7 @@
       </c>
       <c r="M193" s="2" t="inlineStr">
         <is>
-          <t>Не опубликование или опубликование промежуточной бухгалтерской отчетности Эмитента с нарушением сроков, указанных ниже. Под промежуточной бухгалтерской отчетностью Эмитента подразумевается неаудированная промежуточная бухгалтерская отчетность (Бухгалтерский баланс, Отчет о финансовых результатах) Эмитента за отчетные периоды, состоящие из 3, 6 и 9 месяцев отчетного года, составленная в соответствии с Российскими стандартами бухгалтерского учета (далее – РСБУ). Моментом наступления указанного Соб</t>
+          <t>Не опубликование или опубликование годовой индивидуальной финансовой отчетности Эмитента, составленной в соответствии с Международными стандартами финансовой отчетности (МСФО), вместе с аудиторским заключением о ней, с нарушением сроков, указанных ниже. Эмитент обязуется публиковать на Странице в сети Интернет в течение периода с даты начала размещения Биржевых облигаций до даты погашения Биржевых облигаций годовую индивидуальную финансовую отчетность Эмитента по МСФО вместе с аудиторским заключ</t>
         </is>
       </c>
       <c r="N193" s="3" t="inlineStr">
@@ -10623,92 +10521,90 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="2" t="inlineStr"/>
+      <c r="A194" s="2" t="inlineStr">
+        <is>
+          <t>ЛАЗЕРНЫЕ СИСТЕМЫ-БО-02</t>
+        </is>
+      </c>
       <c r="B194" s="2" t="inlineStr"/>
-      <c r="C194" s="2" t="inlineStr"/>
+      <c r="C194" s="2" t="inlineStr">
+        <is>
+          <t>RU000A10EFW3</t>
+        </is>
+      </c>
       <c r="D194" s="2" t="inlineStr"/>
-      <c r="E194" s="2" t="inlineStr"/>
+      <c r="E194" s="2" t="n">
+        <v>4</v>
+      </c>
       <c r="F194" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G194" s="2" t="inlineStr">
+        <is>
+          <t>Кросс-дефолт</t>
+        </is>
+      </c>
+      <c r="H194" s="2" t="inlineStr">
+        <is>
+          <t>В случае нарушения Эмитентом какого-либо (любого) из перечисленных ниже обязательств перед третьими лицам (кросс-дефолт): - просрочка платежа по кредитным договорам и договорам займа Эмитента более че…</t>
+        </is>
+      </c>
+      <c r="I194" s="2" t="inlineStr">
+        <is>
+          <t>Решение о выпуске</t>
+        </is>
+      </c>
+      <c r="J194" s="2" t="inlineStr">
+        <is>
+          <t>п. 5.6.1, 1</t>
+        </is>
+      </c>
+      <c r="K194" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="L194" s="2" t="inlineStr">
+        <is>
+          <t>17896_0_Решение о выпуске БО-02.pdf</t>
+        </is>
+      </c>
+      <c r="M194" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">В случае нарушения Эмитентом какого-либо (любого) из перечисленных ниже обязательств перед третьими лицам (кросс-дефолт): - просрочка платежа по кредитным договорам и договорам займа Эмитента более чем на 10 (Десять) рабочих дней с даты, установленной в документах, закрепляющих срок платежа, или отказ от исполнения указанного обязательства (далее – «Дата неисполнения»); - просрочка выплаты очередного процента (купона) по иным ценным бумагам Эмитента более чем на 10 (Десять) рабочих дней с даты, </t>
+        </is>
+      </c>
+      <c r="N194" s="3" t="inlineStr">
+        <is>
+          <t>https://st.finam.ru/ipo/genconditions/17896_0_Решение о выпуске БО-02.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="inlineStr"/>
+      <c r="B195" s="2" t="inlineStr"/>
+      <c r="C195" s="2" t="inlineStr"/>
+      <c r="D195" s="2" t="inlineStr"/>
+      <c r="E195" s="2" t="inlineStr"/>
+      <c r="F195" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="G194" s="2" t="inlineStr">
-        <is>
-          <t>Информационный (отчётность эмитента) +
-Раскрытие отчётности эмитента</t>
-        </is>
-      </c>
-      <c r="H194" s="2" t="inlineStr">
-        <is>
-          <t>Не опубликование или опубликование годовой индивидуальной финансовой отчетности Эмитента, составленной в соответствии с Международными стандартами финансовой отчетности (МСФО), вместе с аудиторским за…</t>
-        </is>
-      </c>
-      <c r="I194" s="2" t="inlineStr">
-        <is>
-          <t>Решение о выпуске</t>
-        </is>
-      </c>
-      <c r="J194" s="2" t="inlineStr">
+      <c r="G195" s="2" t="inlineStr">
+        <is>
+          <t>Раскрытие отчётности</t>
+        </is>
+      </c>
+      <c r="H195" s="2" t="inlineStr">
+        <is>
+          <t>Неопубликование промежуточной бухгалтерской отчетности Эмитента в сроки, указанные ниже</t>
+        </is>
+      </c>
+      <c r="I195" s="2" t="inlineStr">
+        <is>
+          <t>Решение о выпуске</t>
+        </is>
+      </c>
+      <c r="J195" s="2" t="inlineStr">
         <is>
           <t>п. 5.6.1, 2</t>
-        </is>
-      </c>
-      <c r="K194" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="L194" s="2" t="inlineStr">
-        <is>
-          <t>15622_0_Решение о выпуске БО-01.pdf</t>
-        </is>
-      </c>
-      <c r="M194" s="2" t="inlineStr">
-        <is>
-          <t>Не опубликование или опубликование годовой индивидуальной финансовой отчетности Эмитента, составленной в соответствии с Международными стандартами финансовой отчетности (МСФО), вместе с аудиторским заключением о ней, с нарушением сроков, указанных ниже. Эмитент обязуется публиковать на Странице в сети Интернет в течение периода с даты начала размещения Биржевых облигаций до даты погашения Биржевых облигаций годовую индивидуальную финансовую отчетность Эмитента по МСФО вместе с аудиторским заключ</t>
-        </is>
-      </c>
-      <c r="N194" s="3" t="inlineStr">
-        <is>
-          <t>https://st.finam.ru/ipo/genconditions/15622_0_Решение о выпуске БО-01.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" s="2" t="inlineStr">
-        <is>
-          <t>ЛАЗЕРНЫЕ СИСТЕМЫ-БО-02</t>
-        </is>
-      </c>
-      <c r="B195" s="2" t="inlineStr"/>
-      <c r="C195" s="2" t="inlineStr">
-        <is>
-          <t>RU000A10EFW3</t>
-        </is>
-      </c>
-      <c r="D195" s="2" t="inlineStr"/>
-      <c r="E195" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="F195" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G195" s="2" t="inlineStr">
-        <is>
-          <t>Информационный (отчётность эмитента) +
-Раскрытие отчётности эмитента</t>
-        </is>
-      </c>
-      <c r="H195" s="2" t="inlineStr">
-        <is>
-          <t>В случае нарушения Эмитентом какого-либо (любого) из перечисленных ниже обязательств перед третьими лицам (кросс-дефолт): - просрочка платежа по кредитным договорам и договорам займа Эмитента более че…</t>
-        </is>
-      </c>
-      <c r="I195" s="2" t="inlineStr">
-        <is>
-          <t>Решение о выпуске</t>
-        </is>
-      </c>
-      <c r="J195" s="2" t="inlineStr">
-        <is>
-          <t>п. 5.6.1, 1</t>
         </is>
       </c>
       <c r="K195" s="2" t="n">
@@ -10721,7 +10617,7 @@
       </c>
       <c r="M195" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">В случае нарушения Эмитентом какого-либо (любого) из перечисленных ниже обязательств перед третьими лицам (кросс-дефолт): - просрочка платежа по кредитным договорам и договорам займа Эмитента более чем на 10 (Десять) рабочих дней с даты, установленной в документах, закрепляющих срок платежа, или отказ от исполнения указанного обязательства (далее – «Дата неисполнения»); - просрочка выплаты очередного процента (купона) по иным ценным бумагам Эмитента более чем на 10 (Десять) рабочих дней с даты, </t>
+          <t>Неопубликование промежуточной бухгалтерской отчетности Эмитента в сроки, указанные ниже. Под промежуточной бухгалтерской отчетностью Эмитента подразумевается неаудированная промежуточная бухгалтерская отчетность Эмитента за отчетные периоды, состоящие из 3, 6 и 9 месяцев отчетного года, составленная в соответствии с Российскими стандартами бухгалтерского учета (далее – РСБУ). Моментом наступления указанного События является рабочий день, следующий за днем истечения срока для опубликования промеж</t>
         </is>
       </c>
       <c r="N195" s="3" t="inlineStr">
@@ -10737,17 +10633,16 @@
       <c r="D196" s="2" t="inlineStr"/>
       <c r="E196" s="2" t="inlineStr"/>
       <c r="F196" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G196" s="2" t="inlineStr">
         <is>
-          <t>Информационный (отчётность эмитента) +
-Раскрытие отчётности эмитента</t>
+          <t>Раскрытие отчётности</t>
         </is>
       </c>
       <c r="H196" s="2" t="inlineStr">
         <is>
-          <t>Неопубликование промежуточной бухгалтерской отчетности Эмитента в сроки, указанные ниже</t>
+          <t>Не опубликование годовой индивидуальной финансовой отчетности Эмитента, составленной в соответствии с Международными стандартами финансовой отчетности (далее - МСФО), вместе с аудиторским заключением …</t>
         </is>
       </c>
       <c r="I196" s="2" t="inlineStr">
@@ -10757,7 +10652,7 @@
       </c>
       <c r="J196" s="2" t="inlineStr">
         <is>
-          <t>п. 5.6.1, 2</t>
+          <t>п. 5.6.1, 3</t>
         </is>
       </c>
       <c r="K196" s="2" t="n">
@@ -10770,7 +10665,7 @@
       </c>
       <c r="M196" s="2" t="inlineStr">
         <is>
-          <t>Неопубликование промежуточной бухгалтерской отчетности Эмитента в сроки, указанные ниже. Под промежуточной бухгалтерской отчетностью Эмитента подразумевается неаудированная промежуточная бухгалтерская отчетность Эмитента за отчетные периоды, состоящие из 3, 6 и 9 месяцев отчетного года, составленная в соответствии с Российскими стандартами бухгалтерского учета (далее – РСБУ). Моментом наступления указанного События является рабочий день, следующий за днем истечения срока для опубликования промеж</t>
+          <t>Не опубликование годовой индивидуальной финансовой отчетности Эмитента, составленной в соответствии с Международными стандартами финансовой отчетности (далее - МСФО), вместе с аудиторским заключением в отношении такой отчетности в сроки, указанные ниже. 7 Эмитент обязуется публиковать на Странице в Сети Интернет в течение периода с даты начала размещения Биржевых облигаций до даты погашения Биржевых облигаций годовую индивидуальную финансовую отчетность Эмитента по МСФО вместе с аудиторским закл</t>
         </is>
       </c>
       <c r="N196" s="3" t="inlineStr">
@@ -10786,17 +10681,16 @@
       <c r="D197" s="2" t="inlineStr"/>
       <c r="E197" s="2" t="inlineStr"/>
       <c r="F197" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G197" s="2" t="inlineStr">
         <is>
-          <t>Информационный (отчётность эмитента) +
-Раскрытие отчётности эмитента</t>
+          <t>Раскрытие отчётности</t>
         </is>
       </c>
       <c r="H197" s="2" t="inlineStr">
         <is>
-          <t>Не опубликование годовой индивидуальной финансовой отчетности Эмитента, составленной в соответствии с Международными стандартами финансовой отчетности (далее - МСФО), вместе с аудиторским заключением …</t>
+          <t>Превышение соотношения «Чистый долг» к «EBITDA» значения 4:1</t>
         </is>
       </c>
       <c r="I197" s="2" t="inlineStr">
@@ -10806,7 +10700,7 @@
       </c>
       <c r="J197" s="2" t="inlineStr">
         <is>
-          <t>п. 5.6.1, 3</t>
+          <t>п. 5.6.1, 4</t>
         </is>
       </c>
       <c r="K197" s="2" t="n">
@@ -10819,7 +10713,7 @@
       </c>
       <c r="M197" s="2" t="inlineStr">
         <is>
-          <t>Не опубликование годовой индивидуальной финансовой отчетности Эмитента, составленной в соответствии с Международными стандартами финансовой отчетности (далее - МСФО), вместе с аудиторским заключением в отношении такой отчетности в сроки, указанные ниже. 7 Эмитент обязуется публиковать на Странице в Сети Интернет в течение периода с даты начала размещения Биржевых облигаций до даты погашения Биржевых облигаций годовую индивидуальную финансовую отчетность Эмитента по МСФО вместе с аудиторским закл</t>
+          <t>Превышение соотношения «Чистый долг» к «EBITDA» значения 4:1. Порядок расчета данного коэффициента: Отношение Чистого долга к EBITDA = Чистый долг/ EBITDA. Данный коэффициент рассчитывается на основе показателей годовой индивидуальной финансовой отчетности Эмитента, составленной в соответствии с Международными стандартами финансовой отчетности (МСФО), вместе с аудиторским заключением в отношении такой отчетности (далее по пункту – Финансовая отчетность). Показатель «Чистый долг» рассчитывается п</t>
         </is>
       </c>
       <c r="N197" s="3" t="inlineStr">
@@ -10829,23 +10723,34 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="2" t="inlineStr"/>
+      <c r="A198" s="2" t="inlineStr">
+        <is>
+          <t>ЛЕГЕНДА-002Р-06</t>
+        </is>
+      </c>
       <c r="B198" s="2" t="inlineStr"/>
-      <c r="C198" s="2" t="inlineStr"/>
+      <c r="C198" s="2" t="inlineStr">
+        <is>
+          <t>RU000A10EVH1</t>
+        </is>
+      </c>
       <c r="D198" s="2" t="inlineStr"/>
-      <c r="E198" s="2" t="inlineStr"/>
-      <c r="F198" s="2" t="n">
-        <v>4</v>
+      <c r="E198" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F198" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="G198" s="2" t="inlineStr">
         <is>
-          <t>Информационный (отчётность эмитента) +
-Раскрытие отчётности эмитента</t>
+          <t>Положения о досрочном погашении</t>
         </is>
       </c>
       <c r="H198" s="2" t="inlineStr">
         <is>
-          <t>Превышение соотношения «Чистый долг» к «EBITDA» значения 4:1</t>
+          <t>Put-опция у владельцев отсутствует</t>
         </is>
       </c>
       <c r="I198" s="2" t="inlineStr">
@@ -10853,40 +10758,30 @@
           <t>Решение о выпуске</t>
         </is>
       </c>
-      <c r="J198" s="2" t="inlineStr">
-        <is>
-          <t>п. 5.6.1, 4</t>
-        </is>
-      </c>
-      <c r="K198" s="2" t="n">
-        <v>7</v>
-      </c>
+      <c r="J198" s="2" t="inlineStr"/>
+      <c r="K198" s="2" t="inlineStr"/>
       <c r="L198" s="2" t="inlineStr">
         <is>
-          <t>17896_0_Решение о выпуске БО-02.pdf</t>
-        </is>
-      </c>
-      <c r="M198" s="2" t="inlineStr">
-        <is>
-          <t>Превышение соотношения «Чистый долг» к «EBITDA» значения 4:1. Порядок расчета данного коэффициента: Отношение Чистого долга к EBITDA = Чистый долг/ EBITDA. Данный коэффициент рассчитывается на основе показателей годовой индивидуальной финансовой отчетности Эмитента, составленной в соответствии с Международными стандартами финансовой отчетности (МСФО), вместе с аудиторским заключением в отношении такой отчетности (далее по пункту – Финансовая отчетность). Показатель «Чистый долг» рассчитывается п</t>
-        </is>
-      </c>
+          <t>18126_0_Решение о выпуске_002P-06.pdf</t>
+        </is>
+      </c>
+      <c r="M198" s="2" t="inlineStr"/>
       <c r="N198" s="3" t="inlineStr">
         <is>
-          <t>https://st.finam.ru/ipo/genconditions/17896_0_Решение о выпуске БО-02.pdf</t>
+          <t>https://st.finam.ru/ipo/genconditions/18126_0_Решение о выпуске_002P-06.pdf</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>ЛЕГЕНДА-002Р-06</t>
+          <t>ЛЕГЕНДА-002Р-04</t>
         </is>
       </c>
       <c r="B199" s="2" t="inlineStr"/>
       <c r="C199" s="2" t="inlineStr">
         <is>
-          <t>RU000A10EVH1</t>
+          <t>RU000A10C6Z5</t>
         </is>
       </c>
       <c r="D199" s="2" t="inlineStr"/>
@@ -10917,26 +10812,26 @@
       <c r="K199" s="2" t="inlineStr"/>
       <c r="L199" s="2" t="inlineStr">
         <is>
-          <t>18126_0_Решение о выпуске_002P-06.pdf</t>
+          <t>16925_0_Решение о выпуске_002P-04.pdf</t>
         </is>
       </c>
       <c r="M199" s="2" t="inlineStr"/>
       <c r="N199" s="3" t="inlineStr">
         <is>
-          <t>https://st.finam.ru/ipo/genconditions/18126_0_Решение о выпуске_002P-06.pdf</t>
+          <t>https://st.finam.ru/ipo/genconditions/16925_0_Решение о выпуске_002P-04.pdf</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>ЛЕГЕНДА-002Р-04</t>
+          <t>ЛЕГЕНДА-002Р-05</t>
         </is>
       </c>
       <c r="B200" s="2" t="inlineStr"/>
       <c r="C200" s="2" t="inlineStr">
         <is>
-          <t>RU000A10C6Z5</t>
+          <t>RU000A10C6Y8</t>
         </is>
       </c>
       <c r="D200" s="2" t="inlineStr"/>
@@ -10967,26 +10862,26 @@
       <c r="K200" s="2" t="inlineStr"/>
       <c r="L200" s="2" t="inlineStr">
         <is>
-          <t>16925_0_Решение о выпуске_002P-04.pdf</t>
+          <t>16926_0_Решение о выпуске_002Р-05.pdf</t>
         </is>
       </c>
       <c r="M200" s="2" t="inlineStr"/>
       <c r="N200" s="3" t="inlineStr">
         <is>
-          <t>https://st.finam.ru/ipo/genconditions/16925_0_Решение о выпуске_002P-04.pdf</t>
+          <t>https://st.finam.ru/ipo/genconditions/16926_0_Решение о выпуске_002Р-05.pdf</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>ЛЕГЕНДА-002Р-05</t>
+          <t>ЛЕГЕНДА-002Р-07</t>
         </is>
       </c>
       <c r="B201" s="2" t="inlineStr"/>
       <c r="C201" s="2" t="inlineStr">
         <is>
-          <t>RU000A10C6Y8</t>
+          <t>RU000A10FBB3</t>
         </is>
       </c>
       <c r="D201" s="2" t="inlineStr"/>
@@ -11017,292 +10912,288 @@
       <c r="K201" s="2" t="inlineStr"/>
       <c r="L201" s="2" t="inlineStr">
         <is>
-          <t>16926_0_Решение о выпуске_002Р-05.pdf</t>
+          <t>18295_0_Решение о выпуске_002P-07.pdf</t>
         </is>
       </c>
       <c r="M201" s="2" t="inlineStr"/>
       <c r="N201" s="3" t="inlineStr">
         <is>
-          <t>https://st.finam.ru/ipo/genconditions/16926_0_Решение о выпуске_002Р-05.pdf</t>
+          <t>https://st.finam.ru/ipo/genconditions/18295_0_Решение о выпуске_002P-07.pdf</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>ЛЕГЕНДА-002Р-07</t>
+          <t>РОДЕЛЕН-001Р-03</t>
         </is>
       </c>
       <c r="B202" s="2" t="inlineStr"/>
       <c r="C202" s="2" t="inlineStr">
         <is>
-          <t>RU000A10FBB3</t>
+          <t>RU000A105M59</t>
         </is>
       </c>
       <c r="D202" s="2" t="inlineStr"/>
       <c r="E202" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F202" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G202" s="2" t="inlineStr">
+        <is>
+          <t>Иное</t>
+        </is>
+      </c>
+      <c r="H202" s="2" t="inlineStr">
+        <is>
+          <t>5.6.1.</t>
+        </is>
+      </c>
+      <c r="I202" s="2" t="inlineStr">
+        <is>
+          <t>Решение о выпуске</t>
+        </is>
+      </c>
+      <c r="J202" s="2" t="inlineStr">
+        <is>
+          <t>п. 5.6.1, 1</t>
+        </is>
+      </c>
+      <c r="K202" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="L202" s="2" t="inlineStr">
+        <is>
+          <t>12586_0_Решение_о_выпуске_001Р-03.pdf</t>
+        </is>
+      </c>
+      <c r="M202" s="2" t="inlineStr">
+        <is>
+          <t>5.6.1. Досрочное погашение облигаций по требованию их владельцев. Требование (заявление) о досрочном погашении Биржевых облигаций направляется в соответствии с действующим законодательством. Владелец Биржевых облигаций, права которого на Биржевые облигации учитываются депозитарием, осуществляющим учет прав на них, предъявляет требование к Эмитенту о досрочном погашении Биржевых облигаций или отзывает такое требование путем дачи соответствующих указаний (инструкций) лицу, которое осуществляет уче</t>
+        </is>
+      </c>
+      <c r="N202" s="3" t="inlineStr">
+        <is>
+          <t>https://st.finam.ru/ipo/genconditions/12586_0_Решение_о_выпуске_001Р-03.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="7" t="inlineStr"/>
+      <c r="B203" s="7" t="inlineStr"/>
+      <c r="C203" s="7" t="inlineStr"/>
+      <c r="D203" s="7" t="inlineStr"/>
+      <c r="E203" s="7" t="inlineStr"/>
+      <c r="F203" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G203" s="7" t="inlineStr">
+        <is>
+          <t>Делистинг</t>
+        </is>
+      </c>
+      <c r="H203" s="7" t="inlineStr">
+        <is>
+          <t>Досрочное погашение в случае делистинга (из Программы)</t>
+        </is>
+      </c>
+      <c r="I203" s="7" t="inlineStr">
+        <is>
+          <t>Программа облигаций</t>
+        </is>
+      </c>
+      <c r="J203" s="7" t="inlineStr">
+        <is>
+          <t>п. 9.5.1</t>
+        </is>
+      </c>
+      <c r="K203" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="F202" s="2" t="inlineStr">
+      <c r="L203" s="7" t="inlineStr">
+        <is>
+          <t>12586_0_Программа_001Р.pdf</t>
+        </is>
+      </c>
+      <c r="M203" s="7" t="inlineStr">
+        <is>
+          <t>лигаций по требованию их владельцев: В Условиях выпуска также могут быть установлены дополнительные к случаям, указанным в настоящем пункте Программы, случаи досрочного погашения Биржевых облигаций по требованию их владельцев. Владельцы Биржевых облигаций вправе предъявить их к досрочному погашению в случае делистинга Биржевых облигаций на всех биржах, осуществивших их допуск к организованным торгам. Стоимость (порядок определения стоимости) досрочного погашения: Досрочное погашение Биржевых обл</t>
+        </is>
+      </c>
+      <c r="N203" s="8" t="inlineStr">
+        <is>
+          <t>https://st.finam.ru/ipo/decision/12586_0_Программа_001Р.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="inlineStr">
+        <is>
+          <t>РОДЕЛЕН-001Р-04</t>
+        </is>
+      </c>
+      <c r="B204" s="2" t="inlineStr"/>
+      <c r="C204" s="2" t="inlineStr">
+        <is>
+          <t>RU000A105SK4</t>
+        </is>
+      </c>
+      <c r="D204" s="2" t="inlineStr"/>
+      <c r="E204" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F204" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G204" s="2" t="inlineStr">
+        <is>
+          <t>Иное</t>
+        </is>
+      </c>
+      <c r="H204" s="2" t="inlineStr">
+        <is>
+          <t>5.6.1.</t>
+        </is>
+      </c>
+      <c r="I204" s="2" t="inlineStr">
+        <is>
+          <t>Решение о выпуске</t>
+        </is>
+      </c>
+      <c r="J204" s="2" t="inlineStr">
+        <is>
+          <t>п. 5.6.1, 1</t>
+        </is>
+      </c>
+      <c r="K204" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="L204" s="2" t="inlineStr">
+        <is>
+          <t>13658_0_Решение_о_выпуске_001Р-04.pdf</t>
+        </is>
+      </c>
+      <c r="M204" s="2" t="inlineStr">
+        <is>
+          <t>5.6.1. Досрочное погашение облигаций по требованию их владельцев. Требование (заявление) о досрочном погашении Биржевых облигаций направляется в соответствии с действующим законодательством. Владелец Биржевых облигаций, права которого на Биржевые облигации учитываются депозитарием, осуществляющим учет прав на них, предъявляет требование к Эмитенту о досрочном погашении Биржевых облигаций или отзывает такое требование путем дачи соответствующих указаний (инструкций) лицу, которое осуществляет уче</t>
+        </is>
+      </c>
+      <c r="N204" s="3" t="inlineStr">
+        <is>
+          <t>https://st.finam.ru/ipo/genconditions/13658_0_Решение_о_выпуске_001Р-04.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="7" t="inlineStr"/>
+      <c r="B205" s="7" t="inlineStr"/>
+      <c r="C205" s="7" t="inlineStr"/>
+      <c r="D205" s="7" t="inlineStr"/>
+      <c r="E205" s="7" t="inlineStr"/>
+      <c r="F205" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G205" s="7" t="inlineStr">
+        <is>
+          <t>Делистинг</t>
+        </is>
+      </c>
+      <c r="H205" s="7" t="inlineStr">
+        <is>
+          <t>Досрочное погашение в случае делистинга (из Программы)</t>
+        </is>
+      </c>
+      <c r="I205" s="7" t="inlineStr">
+        <is>
+          <t>Программа облигаций</t>
+        </is>
+      </c>
+      <c r="J205" s="7" t="inlineStr">
+        <is>
+          <t>п. 9.5.1</t>
+        </is>
+      </c>
+      <c r="K205" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L205" s="7" t="inlineStr">
+        <is>
+          <t>13658_0_Программа_001Р.pdf</t>
+        </is>
+      </c>
+      <c r="M205" s="7" t="inlineStr">
+        <is>
+          <t>лигаций по требованию их владельцев: В Условиях выпуска также могут быть установлены дополнительные к случаям, указанным в настоящем пункте Программы, случаи досрочного погашения Биржевых облигаций по требованию их владельцев. Владельцы Биржевых облигаций вправе предъявить их к досрочному погашению в случае делистинга Биржевых облигаций на всех биржах, осуществивших их допуск к организованным торгам. Стоимость (порядок определения стоимости) досрочного погашения: Досрочное погашение Биржевых обл</t>
+        </is>
+      </c>
+      <c r="N205" s="8" t="inlineStr">
+        <is>
+          <t>https://st.finam.ru/ipo/decision/13658_0_Программа_001Р.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="2" t="inlineStr">
+        <is>
+          <t>РОДЕЛЕН-002P-01</t>
+        </is>
+      </c>
+      <c r="B206" s="2" t="inlineStr"/>
+      <c r="C206" s="2" t="inlineStr">
+        <is>
+          <t>RU000A107076</t>
+        </is>
+      </c>
+      <c r="D206" s="2" t="inlineStr"/>
+      <c r="E206" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F206" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G202" s="2" t="inlineStr">
+      <c r="G206" s="2" t="inlineStr">
         <is>
           <t>Положения о досрочном погашении</t>
         </is>
       </c>
-      <c r="H202" s="2" t="inlineStr">
+      <c r="H206" s="2" t="inlineStr">
         <is>
           <t>Put-опция у владельцев отсутствует</t>
         </is>
       </c>
-      <c r="I202" s="2" t="inlineStr">
-        <is>
-          <t>Решение о выпуске</t>
-        </is>
-      </c>
-      <c r="J202" s="2" t="inlineStr"/>
-      <c r="K202" s="2" t="inlineStr"/>
-      <c r="L202" s="2" t="inlineStr">
-        <is>
-          <t>18295_0_Решение о выпуске_002P-07.pdf</t>
-        </is>
-      </c>
-      <c r="M202" s="2" t="inlineStr"/>
-      <c r="N202" s="3" t="inlineStr">
-        <is>
-          <t>https://st.finam.ru/ipo/genconditions/18295_0_Решение о выпуске_002P-07.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" s="2" t="inlineStr">
-        <is>
-          <t>РОДЕЛЕН-001Р-03</t>
-        </is>
-      </c>
-      <c r="B203" s="2" t="inlineStr"/>
-      <c r="C203" s="2" t="inlineStr">
-        <is>
-          <t>RU000A105M59</t>
-        </is>
-      </c>
-      <c r="D203" s="2" t="inlineStr"/>
-      <c r="E203" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="F203" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G203" s="2" t="inlineStr">
-        <is>
-          <t>Информационный (отчётность эмитента) +
-Раскрытие отчётности эмитента</t>
-        </is>
-      </c>
-      <c r="H203" s="2" t="inlineStr">
-        <is>
-          <t>5.6.1.</t>
-        </is>
-      </c>
-      <c r="I203" s="2" t="inlineStr">
-        <is>
-          <t>Решение о выпуске</t>
-        </is>
-      </c>
-      <c r="J203" s="2" t="inlineStr">
-        <is>
-          <t>п. 5.6.1, 1</t>
-        </is>
-      </c>
-      <c r="K203" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="L203" s="2" t="inlineStr">
-        <is>
-          <t>12586_0_Решение_о_выпуске_001Р-03.pdf</t>
-        </is>
-      </c>
-      <c r="M203" s="2" t="inlineStr">
-        <is>
-          <t>5.6.1. Досрочное погашение облигаций по требованию их владельцев. Требование (заявление) о досрочном погашении Биржевых облигаций направляется в соответствии с действующим законодательством. Владелец Биржевых облигаций, права которого на Биржевые облигации учитываются депозитарием, осуществляющим учет прав на них, предъявляет требование к Эмитенту о досрочном погашении Биржевых облигаций или отзывает такое требование путем дачи соответствующих указаний (инструкций) лицу, которое осуществляет уче</t>
-        </is>
-      </c>
-      <c r="N203" s="3" t="inlineStr">
-        <is>
-          <t>https://st.finam.ru/ipo/genconditions/12586_0_Решение_о_выпуске_001Р-03.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" s="7" t="inlineStr"/>
-      <c r="B204" s="7" t="inlineStr"/>
-      <c r="C204" s="7" t="inlineStr"/>
-      <c r="D204" s="7" t="inlineStr"/>
-      <c r="E204" s="7" t="inlineStr"/>
-      <c r="F204" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G204" s="7" t="inlineStr">
-        <is>
-          <t>Информационный (отчётность эмитента) +
-Раскрытие отчётности эмитента</t>
-        </is>
-      </c>
-      <c r="H204" s="7" t="inlineStr">
-        <is>
-          <t>Досрочное погашение в случае делистинга (из Программы)</t>
-        </is>
-      </c>
-      <c r="I204" s="7" t="inlineStr">
-        <is>
-          <t>Программа облигаций</t>
-        </is>
-      </c>
-      <c r="J204" s="7" t="inlineStr">
-        <is>
-          <t>п. 9.5.1</t>
-        </is>
-      </c>
-      <c r="K204" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L204" s="7" t="inlineStr">
-        <is>
-          <t>12586_0_Программа_001Р.pdf</t>
-        </is>
-      </c>
-      <c r="M204" s="7" t="inlineStr">
-        <is>
-          <t>лигаций по требованию их владельцев: В Условиях выпуска также могут быть установлены дополнительные к случаям, указанным в настоящем пункте Программы, случаи досрочного погашения Биржевых облигаций по требованию их владельцев. Владельцы Биржевых облигаций вправе предъявить их к досрочному погашению в случае делистинга Биржевых облигаций на всех биржах, осуществивших их допуск к организованным торгам. Стоимость (порядок определения стоимости) досрочного погашения: Досрочное погашение Биржевых обл</t>
-        </is>
-      </c>
-      <c r="N204" s="8" t="inlineStr">
-        <is>
-          <t>https://st.finam.ru/ipo/decision/12586_0_Программа_001Р.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" s="2" t="inlineStr">
-        <is>
-          <t>РОДЕЛЕН-001Р-04</t>
-        </is>
-      </c>
-      <c r="B205" s="2" t="inlineStr"/>
-      <c r="C205" s="2" t="inlineStr">
-        <is>
-          <t>RU000A105SK4</t>
-        </is>
-      </c>
-      <c r="D205" s="2" t="inlineStr"/>
-      <c r="E205" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="F205" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G205" s="2" t="inlineStr">
-        <is>
-          <t>Информационный (отчётность эмитента) +
-Раскрытие отчётности эмитента</t>
-        </is>
-      </c>
-      <c r="H205" s="2" t="inlineStr">
-        <is>
-          <t>5.6.1.</t>
-        </is>
-      </c>
-      <c r="I205" s="2" t="inlineStr">
-        <is>
-          <t>Решение о выпуске</t>
-        </is>
-      </c>
-      <c r="J205" s="2" t="inlineStr">
-        <is>
-          <t>п. 5.6.1, 1</t>
-        </is>
-      </c>
-      <c r="K205" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="L205" s="2" t="inlineStr">
-        <is>
-          <t>13658_0_Решение_о_выпуске_001Р-04.pdf</t>
-        </is>
-      </c>
-      <c r="M205" s="2" t="inlineStr">
-        <is>
-          <t>5.6.1. Досрочное погашение облигаций по требованию их владельцев. Требование (заявление) о досрочном погашении Биржевых облигаций направляется в соответствии с действующим законодательством. Владелец Биржевых облигаций, права которого на Биржевые облигации учитываются депозитарием, осуществляющим учет прав на них, предъявляет требование к Эмитенту о досрочном погашении Биржевых облигаций или отзывает такое требование путем дачи соответствующих указаний (инструкций) лицу, которое осуществляет уче</t>
-        </is>
-      </c>
-      <c r="N205" s="3" t="inlineStr">
-        <is>
-          <t>https://st.finam.ru/ipo/genconditions/13658_0_Решение_о_выпуске_001Р-04.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" s="7" t="inlineStr"/>
-      <c r="B206" s="7" t="inlineStr"/>
-      <c r="C206" s="7" t="inlineStr"/>
-      <c r="D206" s="7" t="inlineStr"/>
-      <c r="E206" s="7" t="inlineStr"/>
-      <c r="F206" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G206" s="7" t="inlineStr">
-        <is>
-          <t>Информационный (отчётность эмитента) +
-Раскрытие отчётности эмитента</t>
-        </is>
-      </c>
-      <c r="H206" s="7" t="inlineStr">
-        <is>
-          <t>Досрочное погашение в случае делистинга (из Программы)</t>
-        </is>
-      </c>
-      <c r="I206" s="7" t="inlineStr">
-        <is>
-          <t>Программа облигаций</t>
-        </is>
-      </c>
-      <c r="J206" s="7" t="inlineStr">
-        <is>
-          <t>п. 9.5.1</t>
-        </is>
-      </c>
-      <c r="K206" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L206" s="7" t="inlineStr">
-        <is>
-          <t>13658_0_Программа_001Р.pdf</t>
-        </is>
-      </c>
-      <c r="M206" s="7" t="inlineStr">
-        <is>
-          <t>лигаций по требованию их владельцев: В Условиях выпуска также могут быть установлены дополнительные к случаям, указанным в настоящем пункте Программы, случаи досрочного погашения Биржевых облигаций по требованию их владельцев. Владельцы Биржевых облигаций вправе предъявить их к досрочному погашению в случае делистинга Биржевых облигаций на всех биржах, осуществивших их допуск к организованным торгам. Стоимость (порядок определения стоимости) досрочного погашения: Досрочное погашение Биржевых обл</t>
-        </is>
-      </c>
-      <c r="N206" s="8" t="inlineStr">
-        <is>
-          <t>https://st.finam.ru/ipo/decision/13658_0_Программа_001Р.pdf</t>
+      <c r="I206" s="2" t="inlineStr">
+        <is>
+          <t>Решение о выпуске</t>
+        </is>
+      </c>
+      <c r="J206" s="2" t="inlineStr"/>
+      <c r="K206" s="2" t="inlineStr"/>
+      <c r="L206" s="2" t="inlineStr">
+        <is>
+          <t>14412_0_Решение_002P-01.pdf</t>
+        </is>
+      </c>
+      <c r="M206" s="2" t="inlineStr"/>
+      <c r="N206" s="3" t="inlineStr">
+        <is>
+          <t>https://st.finam.ru/ipo/decision/14412_0_Решение_002P-01.pdf</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>РОДЕЛЕН-002P-01</t>
+          <t>РОДЕЛЕН-002P-02</t>
         </is>
       </c>
       <c r="B207" s="2" t="inlineStr"/>
       <c r="C207" s="2" t="inlineStr">
         <is>
-          <t>RU000A107076</t>
+          <t>RU000A107SA1</t>
         </is>
       </c>
       <c r="D207" s="2" t="inlineStr"/>
@@ -11333,26 +11224,26 @@
       <c r="K207" s="2" t="inlineStr"/>
       <c r="L207" s="2" t="inlineStr">
         <is>
-          <t>14412_0_Решение_002P-01.pdf</t>
+          <t>14970_0_Решение_002P-02.pdf</t>
         </is>
       </c>
       <c r="M207" s="2" t="inlineStr"/>
       <c r="N207" s="3" t="inlineStr">
         <is>
-          <t>https://st.finam.ru/ipo/decision/14412_0_Решение_002P-01.pdf</t>
+          <t>https://st.finam.ru/ipo/genconditions/14970_0_Решение_002P-02.pdf</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>РОДЕЛЕН-002P-02</t>
+          <t>РОДЕЛЕН-002P-03</t>
         </is>
       </c>
       <c r="B208" s="2" t="inlineStr"/>
       <c r="C208" s="2" t="inlineStr">
         <is>
-          <t>RU000A107SA1</t>
+          <t>RU000A10B2F7</t>
         </is>
       </c>
       <c r="D208" s="2" t="inlineStr"/>
@@ -11383,26 +11274,26 @@
       <c r="K208" s="2" t="inlineStr"/>
       <c r="L208" s="2" t="inlineStr">
         <is>
-          <t>14970_0_Решение_002P-02.pdf</t>
+          <t>16307_0_Решение_002P-03.pdf</t>
         </is>
       </c>
       <c r="M208" s="2" t="inlineStr"/>
       <c r="N208" s="3" t="inlineStr">
         <is>
-          <t>https://st.finam.ru/ipo/genconditions/14970_0_Решение_002P-02.pdf</t>
+          <t>https://st.finam.ru/ipo/genconditions/16307_0_Решение_002P-03.pdf</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>РОДЕЛЕН-002P-03</t>
+          <t>РОДЕЛЕН-002P-04</t>
         </is>
       </c>
       <c r="B209" s="2" t="inlineStr"/>
       <c r="C209" s="2" t="inlineStr">
         <is>
-          <t>RU000A10B2F7</t>
+          <t>RU000A10C626</t>
         </is>
       </c>
       <c r="D209" s="2" t="inlineStr"/>
@@ -11433,26 +11324,26 @@
       <c r="K209" s="2" t="inlineStr"/>
       <c r="L209" s="2" t="inlineStr">
         <is>
-          <t>16307_0_Решение_002P-03.pdf</t>
+          <t>16867_0_Решение_002P-04.pdf</t>
         </is>
       </c>
       <c r="M209" s="2" t="inlineStr"/>
       <c r="N209" s="3" t="inlineStr">
         <is>
-          <t>https://st.finam.ru/ipo/genconditions/16307_0_Решение_002P-03.pdf</t>
+          <t>https://st.finam.ru/ipo/genconditions/16867_0_Решение_002P-04.pdf</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>РОДЕЛЕН-002P-04</t>
+          <t>РОДЕЛЕН-002P-05</t>
         </is>
       </c>
       <c r="B210" s="2" t="inlineStr"/>
       <c r="C210" s="2" t="inlineStr">
         <is>
-          <t>RU000A10C626</t>
+          <t>RU000A10EQD0</t>
         </is>
       </c>
       <c r="D210" s="2" t="inlineStr"/>
@@ -11483,26 +11374,26 @@
       <c r="K210" s="2" t="inlineStr"/>
       <c r="L210" s="2" t="inlineStr">
         <is>
-          <t>16867_0_Решение_002P-04.pdf</t>
+          <t>17909_0_Решение о выпуске 002Р-05.pdf</t>
         </is>
       </c>
       <c r="M210" s="2" t="inlineStr"/>
       <c r="N210" s="3" t="inlineStr">
         <is>
-          <t>https://st.finam.ru/ipo/genconditions/16867_0_Решение_002P-04.pdf</t>
+          <t>https://st.finam.ru/ipo/genconditions/17909_0_Решение о выпуске 002Р-05.pdf</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>РОДЕЛЕН-002P-05</t>
+          <t>РОДЕЛЕН-002P-06</t>
         </is>
       </c>
       <c r="B211" s="2" t="inlineStr"/>
       <c r="C211" s="2" t="inlineStr">
         <is>
-          <t>RU000A10EQD0</t>
+          <t>RU000A10FJ65</t>
         </is>
       </c>
       <c r="D211" s="2" t="inlineStr"/>
@@ -11533,26 +11424,26 @@
       <c r="K211" s="2" t="inlineStr"/>
       <c r="L211" s="2" t="inlineStr">
         <is>
-          <t>17909_0_Решение о выпуске 002Р-05.pdf</t>
+          <t>18366_0_Решение_002P-06.pdf</t>
         </is>
       </c>
       <c r="M211" s="2" t="inlineStr"/>
       <c r="N211" s="3" t="inlineStr">
         <is>
-          <t>https://st.finam.ru/ipo/genconditions/17909_0_Решение о выпуске 002Р-05.pdf</t>
+          <t>https://st.finam.ru/ipo/genconditions/18366_0_Решение_002P-06.pdf</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>РОДЕЛЕН-002P-06</t>
+          <t>ПРОЕКТ 111-001Р-01</t>
         </is>
       </c>
       <c r="B212" s="2" t="inlineStr"/>
       <c r="C212" s="2" t="inlineStr">
         <is>
-          <t>RU000A10FJ65</t>
+          <t>RU000A106U90</t>
         </is>
       </c>
       <c r="D212" s="2" t="inlineStr"/>
@@ -11583,45 +11474,43 @@
       <c r="K212" s="2" t="inlineStr"/>
       <c r="L212" s="2" t="inlineStr">
         <is>
-          <t>18366_0_Решение_002P-06.pdf</t>
+          <t>14430_0_Решение 001Р-01.pdf</t>
         </is>
       </c>
       <c r="M212" s="2" t="inlineStr"/>
       <c r="N212" s="3" t="inlineStr">
         <is>
-          <t>https://st.finam.ru/ipo/genconditions/18366_0_Решение_002P-06.pdf</t>
+          <t>https://st.finam.ru/ipo/genconditions/14430_0_Решение 001Р-01.pdf</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>ПРОЕКТ 111-001Р-01</t>
+          <t>РОЛЬФ-001Р-03</t>
         </is>
       </c>
       <c r="B213" s="2" t="inlineStr"/>
       <c r="C213" s="2" t="inlineStr">
         <is>
-          <t>RU000A106U90</t>
+          <t>RU000A109LC8</t>
         </is>
       </c>
       <c r="D213" s="2" t="inlineStr"/>
       <c r="E213" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F213" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="F213" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="G213" s="2" t="inlineStr">
         <is>
-          <t>Положения о досрочном погашении</t>
+          <t>Делистинг</t>
         </is>
       </c>
       <c r="H213" s="2" t="inlineStr">
         <is>
-          <t>Put-опция у владельцев отсутствует</t>
+          <t>Досрочное погашение в случае делистинга</t>
         </is>
       </c>
       <c r="I213" s="2" t="inlineStr">
@@ -11629,48 +11518,47 @@
           <t>Решение о выпуске</t>
         </is>
       </c>
-      <c r="J213" s="2" t="inlineStr"/>
-      <c r="K213" s="2" t="inlineStr"/>
+      <c r="J213" s="2" t="inlineStr">
+        <is>
+          <t>п. 5.6.1, 1</t>
+        </is>
+      </c>
+      <c r="K213" s="2" t="n">
+        <v>6</v>
+      </c>
       <c r="L213" s="2" t="inlineStr">
         <is>
-          <t>14430_0_Решение 001Р-01.pdf</t>
-        </is>
-      </c>
-      <c r="M213" s="2" t="inlineStr"/>
+          <t>15669_0_Решение_о_выпуске_001Р-03.pdf</t>
+        </is>
+      </c>
+      <c r="M213" s="2" t="inlineStr">
+        <is>
+          <t>5.6.1 Досрочное погашение облигаций по требованию их владельцев: Владельцы Биржевых облигаций вправе предъявить их к досрочному погашению в случае делистинга Биржевых облигаций на всех биржах, осуществивших их допуск к организованным торгам. Досрочное погашение Биржевых облигаций производится денежными средствами в российских рублях в безналичном порядке. Владелец Биржевых облигаций, права которого на Биржевые облигации учитываются депозитарием, осущест</t>
+        </is>
+      </c>
       <c r="N213" s="3" t="inlineStr">
         <is>
-          <t>https://st.finam.ru/ipo/genconditions/14430_0_Решение 001Р-01.pdf</t>
+          <t>https://st.finam.ru/ipo/genconditions/15669_0_Решение_о_выпуске_001Р-03.pdf</t>
         </is>
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="2" t="inlineStr">
-        <is>
-          <t>РОЛЬФ-001Р-03</t>
-        </is>
-      </c>
+      <c r="A214" s="2" t="inlineStr"/>
       <c r="B214" s="2" t="inlineStr"/>
-      <c r="C214" s="2" t="inlineStr">
-        <is>
-          <t>RU000A109LC8</t>
-        </is>
-      </c>
+      <c r="C214" s="2" t="inlineStr"/>
       <c r="D214" s="2" t="inlineStr"/>
-      <c r="E214" s="2" t="n">
-        <v>3</v>
-      </c>
+      <c r="E214" s="2" t="inlineStr"/>
       <c r="F214" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G214" s="2" t="inlineStr">
         <is>
-          <t>Информационный (отчётность эмитента) +
-Раскрытие отчётности эмитента</t>
+          <t>Раскрытие отчётности</t>
         </is>
       </c>
       <c r="H214" s="2" t="inlineStr">
         <is>
-          <t>Досрочное погашение в случае делистинга</t>
+          <t>Нераскрытие или раскрытие годовой консолидированной финансовой отчетности АО «Промагрологистика» (ОГРН 1047796793956, ИНН 7701562811) с нарушением сроков, указанных ниже, начиная с отчетности за 2024 …</t>
         </is>
       </c>
       <c r="I214" s="2" t="inlineStr">
@@ -11680,7 +11568,7 @@
       </c>
       <c r="J214" s="2" t="inlineStr">
         <is>
-          <t>п. 5.6.1, 1</t>
+          <t>п. 5.6.1, 2</t>
         </is>
       </c>
       <c r="K214" s="2" t="n">
@@ -11693,7 +11581,7 @@
       </c>
       <c r="M214" s="2" t="inlineStr">
         <is>
-          <t>5.6.1 Досрочное погашение облигаций по требованию их владельцев: Владельцы Биржевых облигаций вправе предъявить их к досрочному погашению в случае делистинга Биржевых облигаций на всех биржах, осуществивших их допуск к организованным торгам. Досрочное погашение Биржевых облигаций производится денежными средствами в российских рублях в безналичном порядке. Владелец Биржевых облигаций, права которого на Биржевые облигации учитываются депозитарием, осущест</t>
+          <t>Нераскрытие или раскрытие годовой консолидированной финансовой отчетности АО «Промагрологистика» (ОГРН 1047796793956, ИНН 7701562811) с нарушением сроков, указанных ниже, начиная с отчетности за 2024 год. Под годовой консолидированной финансовой отчетностью АО «Промагрологистика» подразумевается консолидированная финансовая отчетность АО «Промагрологистика» за отчетный год, составленная в соответствии с Международными стандартами финансовой отчетности (МСФО) с приложенным аудиторским заключением</t>
         </is>
       </c>
       <c r="N214" s="3" t="inlineStr">
@@ -11703,23 +11591,32 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="2" t="inlineStr"/>
+      <c r="A215" s="2" t="inlineStr">
+        <is>
+          <t>РОЛЬФ-001Р-06</t>
+        </is>
+      </c>
       <c r="B215" s="2" t="inlineStr"/>
-      <c r="C215" s="2" t="inlineStr"/>
+      <c r="C215" s="2" t="inlineStr">
+        <is>
+          <t>RU000A10ASD4</t>
+        </is>
+      </c>
       <c r="D215" s="2" t="inlineStr"/>
-      <c r="E215" s="2" t="inlineStr"/>
+      <c r="E215" s="2" t="n">
+        <v>2</v>
+      </c>
       <c r="F215" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G215" s="2" t="inlineStr">
         <is>
-          <t>Информационный (отчётность эмитента) +
-Раскрытие отчётности эмитента</t>
+          <t>Делистинг</t>
         </is>
       </c>
       <c r="H215" s="2" t="inlineStr">
         <is>
-          <t>Нераскрытие или раскрытие годовой консолидированной финансовой отчетности АО «Промагрологистика» (ОГРН 1047796793956, ИНН 7701562811) с нарушением сроков, указанных ниже, начиная с отчетности за 2024 …</t>
+          <t>Досрочное погашение в случае делистинга</t>
         </is>
       </c>
       <c r="I215" s="2" t="inlineStr">
@@ -11729,7 +11626,7 @@
       </c>
       <c r="J215" s="2" t="inlineStr">
         <is>
-          <t>п. 5.6.1, 2</t>
+          <t>п. 5.6.1, 1</t>
         </is>
       </c>
       <c r="K215" s="2" t="n">
@@ -11737,92 +11634,90 @@
       </c>
       <c r="L215" s="2" t="inlineStr">
         <is>
-          <t>15669_0_Решение_о_выпуске_001Р-03.pdf</t>
+          <t>16161_0_Решение_о_выпуске_001Р-06.pdf</t>
         </is>
       </c>
       <c r="M215" s="2" t="inlineStr">
         <is>
+          <t>5.6.1 Досрочное погашение облигаций по требованию их владельцев: Владельцы Биржевых облигаций вправе предъявить их к досрочному погашению в случае делистинга Биржевых облигаций на всех биржах, осуществивших их допуск к организованным торгам. Досрочное погашение Биржевых облигаций производится денежными средствами в российских рублях в безналичном порядке. Владелец Биржевых облигаций, права которого на Биржевые облигации учитываются депозитарием, осущест</t>
+        </is>
+      </c>
+      <c r="N215" s="3" t="inlineStr">
+        <is>
+          <t>https://st.finam.ru/ipo/genconditions/16161_0_Решение_о_выпуске_001Р-06.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="2" t="inlineStr"/>
+      <c r="B216" s="2" t="inlineStr"/>
+      <c r="C216" s="2" t="inlineStr"/>
+      <c r="D216" s="2" t="inlineStr"/>
+      <c r="E216" s="2" t="inlineStr"/>
+      <c r="F216" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G216" s="2" t="inlineStr">
+        <is>
+          <t>Раскрытие отчётности</t>
+        </is>
+      </c>
+      <c r="H216" s="2" t="inlineStr">
+        <is>
+          <t>Нераскрытие или раскрытие годовой консолидированной финансовой отчетности АО «Промагрологистика» (ОГРН 1047796793956, ИНН 7701562811) с нарушением сроков, указанных ниже, начиная с отчетности за 2024 …</t>
+        </is>
+      </c>
+      <c r="I216" s="2" t="inlineStr">
+        <is>
+          <t>Решение о выпуске</t>
+        </is>
+      </c>
+      <c r="J216" s="2" t="inlineStr">
+        <is>
+          <t>п. 5.6.1, 2</t>
+        </is>
+      </c>
+      <c r="K216" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="L216" s="2" t="inlineStr">
+        <is>
+          <t>16161_0_Решение_о_выпуске_001Р-06.pdf</t>
+        </is>
+      </c>
+      <c r="M216" s="2" t="inlineStr">
+        <is>
           <t>Нераскрытие или раскрытие годовой консолидированной финансовой отчетности АО «Промагрологистика» (ОГРН 1047796793956, ИНН 7701562811) с нарушением сроков, указанных ниже, начиная с отчетности за 2024 год. Под годовой консолидированной финансовой отчетностью АО «Промагрологистика» подразумевается консолидированная финансовая отчетность АО «Промагрологистика» за отчетный год, составленная в соответствии с Международными стандартами финансовой отчетности (МСФО) с приложенным аудиторским заключением</t>
         </is>
       </c>
-      <c r="N215" s="3" t="inlineStr">
-        <is>
-          <t>https://st.finam.ru/ipo/genconditions/15669_0_Решение_о_выпуске_001Р-03.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" s="7" t="inlineStr"/>
-      <c r="B216" s="7" t="inlineStr"/>
-      <c r="C216" s="7" t="inlineStr"/>
-      <c r="D216" s="7" t="inlineStr"/>
-      <c r="E216" s="7" t="inlineStr"/>
-      <c r="F216" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="G216" s="7" t="inlineStr">
-        <is>
-          <t>Информационный (отчётность эмитента) +
-Раскрытие отчётности эмитента</t>
-        </is>
-      </c>
-      <c r="H216" s="7" t="inlineStr">
-        <is>
-          <t>Досрочное погашение в случае ликвидации (из Программы)</t>
-        </is>
-      </c>
-      <c r="I216" s="7" t="inlineStr">
-        <is>
-          <t>Программа облигаций</t>
-        </is>
-      </c>
-      <c r="J216" s="7" t="inlineStr">
-        <is>
-          <t>п. 9.5.1</t>
-        </is>
-      </c>
-      <c r="K216" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L216" s="7" t="inlineStr">
-        <is>
-          <t>15669_0_Программа.pdf</t>
-        </is>
-      </c>
-      <c r="M216" s="7" t="inlineStr">
-        <is>
-          <t>9.5.1. Программы, а также предусмотренных законодательством Российской Федерации. В случае ликвидации Эмитента владелец Биржевой облигации вправе получить причитающиеся денежные средства в порядке очередности, установленной в соответствии со статьей 64 Гражданского кодекса Российской Федерации. Все задолженности Эмитента по Биржевым облигациям будут юридически равны и в равной степени обязательны к</t>
-        </is>
-      </c>
-      <c r="N216" s="8" t="inlineStr">
-        <is>
-          <t>https://st.finam.ru/ipo/decision/15669_0_Программа.pdf</t>
+      <c r="N216" s="3" t="inlineStr">
+        <is>
+          <t>https://st.finam.ru/ipo/genconditions/16161_0_Решение_о_выпуске_001Р-06.pdf</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>РОЛЬФ-001Р-06</t>
+          <t>РОЛЬФ-001Р-07</t>
         </is>
       </c>
       <c r="B217" s="2" t="inlineStr"/>
       <c r="C217" s="2" t="inlineStr">
         <is>
-          <t>RU000A10ASD4</t>
+          <t>RU000A10ASE2</t>
         </is>
       </c>
       <c r="D217" s="2" t="inlineStr"/>
       <c r="E217" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F217" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G217" s="2" t="inlineStr">
         <is>
-          <t>Информационный (отчётность эмитента) +
-Раскрытие отчётности эмитента</t>
+          <t>Делистинг</t>
         </is>
       </c>
       <c r="H217" s="2" t="inlineStr">
@@ -11841,21 +11736,21 @@
         </is>
       </c>
       <c r="K217" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L217" s="2" t="inlineStr">
         <is>
-          <t>16161_0_Решение_о_выпуске_001Р-06.pdf</t>
+          <t>16160_0_Решение_о_выпуске_001Р-07.pdf</t>
         </is>
       </c>
       <c r="M217" s="2" t="inlineStr">
         <is>
-          <t>5.6.1 Досрочное погашение облигаций по требованию их владельцев: Владельцы Биржевых облигаций вправе предъявить их к досрочному погашению в случае делистинга Биржевых облигаций на всех биржах, осуществивших их допуск к организованным торгам. Досрочное погашение Биржевых облигаций производится денежными средствами в российских рублях в безналичном порядке. Владелец Биржевых облигаций, права которого на Биржевые облигации учитываются депозитарием, осущест</t>
+          <t>5.6.1 Досрочное погашение облигаций по требованию их владельцев: Владельцы Биржевых облигаций вправе предъявить их к досрочному погашению в случае делистинга Биржевых облигаций на всех биржах, осуществивших их допуск к организованным торгам. Досрочное погашение Биржевых облигаций производится денежными средствами в российских рублях в безналичном порядке. Владелец Биржевых облигаций, права которого на Биржевые облигации учитываются5 депоз</t>
         </is>
       </c>
       <c r="N217" s="3" t="inlineStr">
         <is>
-          <t>https://st.finam.ru/ipo/genconditions/16161_0_Решение_о_выпуске_001Р-06.pdf</t>
+          <t>https://st.finam.ru/ipo/genconditions/16160_0_Решение_о_выпуске_001Р-07.pdf</t>
         </is>
       </c>
     </row>
@@ -11870,8 +11765,7 @@
       </c>
       <c r="G218" s="2" t="inlineStr">
         <is>
-          <t>Информационный (отчётность эмитента) +
-Раскрытие отчётности эмитента</t>
+          <t>Раскрытие отчётности</t>
         </is>
       </c>
       <c r="H218" s="2" t="inlineStr">
@@ -11890,11 +11784,11 @@
         </is>
       </c>
       <c r="K218" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L218" s="2" t="inlineStr">
         <is>
-          <t>16161_0_Решение_о_выпуске_001Р-06.pdf</t>
+          <t>16160_0_Решение_о_выпуске_001Р-07.pdf</t>
         </is>
       </c>
       <c r="M218" s="2" t="inlineStr">
@@ -11904,87 +11798,85 @@
       </c>
       <c r="N218" s="3" t="inlineStr">
         <is>
-          <t>https://st.finam.ru/ipo/genconditions/16161_0_Решение_о_выпуске_001Р-06.pdf</t>
+          <t>https://st.finam.ru/ipo/genconditions/16160_0_Решение_о_выпуске_001Р-07.pdf</t>
         </is>
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="7" t="inlineStr"/>
-      <c r="B219" s="7" t="inlineStr"/>
-      <c r="C219" s="7" t="inlineStr"/>
-      <c r="D219" s="7" t="inlineStr"/>
-      <c r="E219" s="7" t="inlineStr"/>
-      <c r="F219" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="G219" s="7" t="inlineStr">
-        <is>
-          <t>Информационный (отчётность эмитента) +
-Раскрытие отчётности эмитента</t>
-        </is>
-      </c>
-      <c r="H219" s="7" t="inlineStr">
-        <is>
-          <t>Досрочное погашение в случае ликвидации (из Программы)</t>
-        </is>
-      </c>
-      <c r="I219" s="7" t="inlineStr">
-        <is>
-          <t>Программа облигаций (e-disclosure)</t>
-        </is>
-      </c>
-      <c r="J219" s="7" t="inlineStr">
-        <is>
-          <t>п. 9.3</t>
-        </is>
-      </c>
-      <c r="K219" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L219" s="7" t="inlineStr">
-        <is>
-          <t>files.aspx</t>
-        </is>
-      </c>
-      <c r="M219" s="7" t="inlineStr">
-        <is>
-          <t>ного погашения Биржевых облигаций и выплаты ему накопленного купонного дохода по Биржевым облигациям, рассчитанного на дату исполнения обязательств по досрочному погашению Биржевых облигаций, в случаях, указанных в п. 9.5.1. Программы, а также предусмотренных законодательством Российской Федерации. В случае ликвидации Эмитента владелец Биржевой облигации вправе получить причитающиеся денежные средства в порядке очередности, установленной в соответствии со статьей 64 Гражданского кодекса Российск</t>
-        </is>
-      </c>
-      <c r="N219" s="8" t="inlineStr">
-        <is>
-          <t>https://e-disclosure.ru/portal/files.aspx?id=37542&amp;type=7</t>
+      <c r="A219" s="2" t="inlineStr">
+        <is>
+          <t>РОЛЬФ-001Р-08</t>
+        </is>
+      </c>
+      <c r="B219" s="2" t="inlineStr"/>
+      <c r="C219" s="2" t="inlineStr">
+        <is>
+          <t>RU000A10BQ60</t>
+        </is>
+      </c>
+      <c r="D219" s="2" t="inlineStr"/>
+      <c r="E219" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F219" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G219" s="2" t="inlineStr">
+        <is>
+          <t>Делистинг</t>
+        </is>
+      </c>
+      <c r="H219" s="2" t="inlineStr">
+        <is>
+          <t>Досрочное погашение в случае делистинга</t>
+        </is>
+      </c>
+      <c r="I219" s="2" t="inlineStr">
+        <is>
+          <t>Решение о выпуске</t>
+        </is>
+      </c>
+      <c r="J219" s="2" t="inlineStr">
+        <is>
+          <t>п. 5.6.1, 1</t>
+        </is>
+      </c>
+      <c r="K219" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="L219" s="2" t="inlineStr">
+        <is>
+          <t>16652_0_Решение_о_выпуске_001Р-08.pdf</t>
+        </is>
+      </c>
+      <c r="M219" s="2" t="inlineStr">
+        <is>
+          <t>5.6.1 Досрочное погашение облигаций по требованию их владельцев: Владельцы Биржевых облигаций вправе предъявить их к досрочному погашению в случае делистинга Биржевых облигаций на всех биржах, осуществивших их допуск к организованным торгам. Досрочное погашение Биржевых облигаций производится денежными средствами в российских рублях в безналичном порядке. Владелец Биржевых облигаций, права которого на Биржевые облигации учитываются5 депоз</t>
+        </is>
+      </c>
+      <c r="N219" s="3" t="inlineStr">
+        <is>
+          <t>https://st.finam.ru/ipo/genconditions/16652_0_Решение_о_выпуске_001Р-08.pdf</t>
         </is>
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="2" t="inlineStr">
-        <is>
-          <t>РОЛЬФ-001Р-07</t>
-        </is>
-      </c>
+      <c r="A220" s="2" t="inlineStr"/>
       <c r="B220" s="2" t="inlineStr"/>
-      <c r="C220" s="2" t="inlineStr">
-        <is>
-          <t>RU000A10ASE2</t>
-        </is>
-      </c>
+      <c r="C220" s="2" t="inlineStr"/>
       <c r="D220" s="2" t="inlineStr"/>
-      <c r="E220" s="2" t="n">
-        <v>3</v>
-      </c>
+      <c r="E220" s="2" t="inlineStr"/>
       <c r="F220" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G220" s="2" t="inlineStr">
         <is>
-          <t>Информационный (отчётность эмитента) +
-Раскрытие отчётности эмитента</t>
+          <t>Раскрытие отчётности</t>
         </is>
       </c>
       <c r="H220" s="2" t="inlineStr">
         <is>
-          <t>Досрочное погашение в случае делистинга</t>
+          <t>Нераскрытие или раскрытие годовой консолидированной финансовой отчетности АО «Промагрологистика» (ОГРН 1047796793956, ИНН 7701562811) с нарушением сроков, указанных ниже, начиная с отчетности за 2024 …</t>
         </is>
       </c>
       <c r="I220" s="2" t="inlineStr">
@@ -11994,7 +11886,7 @@
       </c>
       <c r="J220" s="2" t="inlineStr">
         <is>
-          <t>п. 5.6.1, 1</t>
+          <t>п. 5.6.1, 2</t>
         </is>
       </c>
       <c r="K220" s="2" t="n">
@@ -12002,38 +11894,47 @@
       </c>
       <c r="L220" s="2" t="inlineStr">
         <is>
-          <t>16160_0_Решение_о_выпуске_001Р-07.pdf</t>
+          <t>16652_0_Решение_о_выпуске_001Р-08.pdf</t>
         </is>
       </c>
       <c r="M220" s="2" t="inlineStr">
         <is>
-          <t>5.6.1 Досрочное погашение облигаций по требованию их владельцев: Владельцы Биржевых облигаций вправе предъявить их к досрочному погашению в случае делистинга Биржевых облигаций на всех биржах, осуществивших их допуск к организованным торгам. Досрочное погашение Биржевых облигаций производится денежными средствами в российских рублях в безналичном порядке. Владелец Биржевых облигаций, права которого на Биржевые облигации учитываются5 депоз</t>
+          <t>Нераскрытие или раскрытие годовой консолидированной финансовой отчетности АО «Промагрологистика» (ОГРН 1047796793956, ИНН 7701562811) с нарушением сроков, указанных ниже, начиная с отчетности за 2024 год. Под годовой консолидированной финансовой отчетностью АО «Промагрологистика» подразумевается консолидированная финансовая отчетность АО «Промагрологистика» за отчетный год, составленная в соответствии с Международными стандартами финансовой отчетности (МСФО) с приложенным аудиторским заключением</t>
         </is>
       </c>
       <c r="N220" s="3" t="inlineStr">
         <is>
-          <t>https://st.finam.ru/ipo/genconditions/16160_0_Решение_о_выпуске_001Р-07.pdf</t>
+          <t>https://st.finam.ru/ipo/genconditions/16652_0_Решение_о_выпуске_001Р-08.pdf</t>
         </is>
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="2" t="inlineStr"/>
+      <c r="A221" s="2" t="inlineStr">
+        <is>
+          <t>РОЛЬФ-001Р-09</t>
+        </is>
+      </c>
       <c r="B221" s="2" t="inlineStr"/>
-      <c r="C221" s="2" t="inlineStr"/>
+      <c r="C221" s="2" t="inlineStr">
+        <is>
+          <t>RU000A10F850</t>
+        </is>
+      </c>
       <c r="D221" s="2" t="inlineStr"/>
-      <c r="E221" s="2" t="inlineStr"/>
+      <c r="E221" s="2" t="n">
+        <v>2</v>
+      </c>
       <c r="F221" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G221" s="2" t="inlineStr">
         <is>
-          <t>Информационный (отчётность эмитента) +
-Раскрытие отчётности эмитента</t>
+          <t>Раскрытие отчётности</t>
         </is>
       </c>
       <c r="H221" s="2" t="inlineStr">
         <is>
-          <t>Нераскрытие или раскрытие годовой консолидированной финансовой отчетности АО «Промагрологистика» (ОГРН 1047796793956, ИНН 7701562811) с нарушением сроков, указанных ниже, начиная с отчетности за 2024 …</t>
+          <t>Нарушение Эмитентом сроков публикации консолидированной финансовой отчетности АО «Промагрологистика» (ОГРН 1047796793956, ИНН 7701562811), установленных ниже</t>
         </is>
       </c>
       <c r="I221" s="2" t="inlineStr">
@@ -12043,7 +11944,7 @@
       </c>
       <c r="J221" s="2" t="inlineStr">
         <is>
-          <t>п. 5.6.1, 2</t>
+          <t>п. 5.6.1, 1</t>
         </is>
       </c>
       <c r="K221" s="2" t="n">
@@ -12051,97 +11952,95 @@
       </c>
       <c r="L221" s="2" t="inlineStr">
         <is>
-          <t>16160_0_Решение_о_выпуске_001Р-07.pdf</t>
+          <t>18254_0_Решение_о_выпуске_001Р-09.pdf</t>
         </is>
       </c>
       <c r="M221" s="2" t="inlineStr">
         <is>
-          <t>Нераскрытие или раскрытие годовой консолидированной финансовой отчетности АО «Промагрологистика» (ОГРН 1047796793956, ИНН 7701562811) с нарушением сроков, указанных ниже, начиная с отчетности за 2024 год. Под годовой консолидированной финансовой отчетностью АО «Промагрологистика» подразумевается консолидированная финансовая отчетность АО «Промагрологистика» за отчетный год, составленная в соответствии с Международными стандартами финансовой отчетности (МСФО) с приложенным аудиторским заключением</t>
+          <t>Нарушение Эмитентом сроков публикации консолидированной финансовой отчетности АО «Промагрологистика» (ОГРН 1047796793956, ИНН 7701562811), установленных ниже. Под годовой консолидированной финансовой отчетностью АО «Промагрологистика» подразумевается консолидированная финансовая отчетность АО «Промагрологистика» за отчетный год, составленная в соответствии с Международными стандартами финансовой отчетности (МСФО) с приложенным аудиторским заключением в отношении указанной годовой консолидированн</t>
         </is>
       </c>
       <c r="N221" s="3" t="inlineStr">
         <is>
-          <t>https://st.finam.ru/ipo/genconditions/16160_0_Решение_о_выпуске_001Р-07.pdf</t>
+          <t>https://st.finam.ru/ipo/genconditions/18254_0_Решение_о_выпуске_001Р-09.pdf</t>
         </is>
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="7" t="inlineStr"/>
-      <c r="B222" s="7" t="inlineStr"/>
-      <c r="C222" s="7" t="inlineStr"/>
-      <c r="D222" s="7" t="inlineStr"/>
-      <c r="E222" s="7" t="inlineStr"/>
-      <c r="F222" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="G222" s="7" t="inlineStr">
-        <is>
-          <t>Информационный (отчётность эмитента) +
-Раскрытие отчётности эмитента</t>
-        </is>
-      </c>
-      <c r="H222" s="7" t="inlineStr">
-        <is>
-          <t>Досрочное погашение в случае ликвидации (из Программы)</t>
-        </is>
-      </c>
-      <c r="I222" s="7" t="inlineStr">
-        <is>
-          <t>Программа облигаций (e-disclosure)</t>
-        </is>
-      </c>
-      <c r="J222" s="7" t="inlineStr">
-        <is>
-          <t>п. 9.3</t>
-        </is>
-      </c>
-      <c r="K222" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L222" s="7" t="inlineStr">
-        <is>
-          <t>files.aspx</t>
-        </is>
-      </c>
-      <c r="M222" s="7" t="inlineStr">
-        <is>
-          <t>ного погашения Биржевых облигаций и выплаты ему накопленного купонного дохода по Биржевым облигациям, рассчитанного на дату исполнения обязательств по досрочному погашению Биржевых облигаций, в случаях, указанных в п. 9.5.1. Программы, а также предусмотренных законодательством Российской Федерации. В случае ликвидации Эмитента владелец Биржевой облигации вправе получить причитающиеся денежные средства в порядке очередности, установленной в соответствии со статьей 64 Гражданского кодекса Российск</t>
-        </is>
-      </c>
-      <c r="N222" s="8" t="inlineStr">
-        <is>
-          <t>https://e-disclosure.ru/portal/files.aspx?id=37542&amp;type=7</t>
+      <c r="A222" s="2" t="inlineStr"/>
+      <c r="B222" s="2" t="inlineStr"/>
+      <c r="C222" s="2" t="inlineStr"/>
+      <c r="D222" s="2" t="inlineStr"/>
+      <c r="E222" s="2" t="inlineStr"/>
+      <c r="F222" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G222" s="2" t="inlineStr">
+        <is>
+          <t>Делистинг</t>
+        </is>
+      </c>
+      <c r="H222" s="2" t="inlineStr">
+        <is>
+          <t>Досрочное погашение в случае делистинга</t>
+        </is>
+      </c>
+      <c r="I222" s="2" t="inlineStr">
+        <is>
+          <t>Решение о выпуске</t>
+        </is>
+      </c>
+      <c r="J222" s="2" t="inlineStr">
+        <is>
+          <t>п. 5.6.1, 2</t>
+        </is>
+      </c>
+      <c r="K222" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="L222" s="2" t="inlineStr">
+        <is>
+          <t>18254_0_Решение_о_выпуске_001Р-09.pdf</t>
+        </is>
+      </c>
+      <c r="M222" s="2" t="inlineStr">
+        <is>
+          <t>5.6.1 Досрочное погашение облигаций по требованию их владельцев: Владельцы Биржевых облигаций вправе предъявить их к досрочному погашению в случае делистинга Биржевых облигаций на всех биржах, осуществивших их допуск к организованным торгам. Досрочное погашение Биржевых облигаций производится денежными средствами в российских рублях в безналичном порядке. Владелец Биржевых облигаций, права которого на Биржевые облигации учитываются5 депоз</t>
+        </is>
+      </c>
+      <c r="N222" s="3" t="inlineStr">
+        <is>
+          <t>https://st.finam.ru/ipo/genconditions/18254_0_Решение_о_выпуске_001Р-09.pdf</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>РОЛЬФ-001Р-08</t>
+          <t>ТАЛК ЛИЗИНГ-001P-02</t>
         </is>
       </c>
       <c r="B223" s="2" t="inlineStr"/>
       <c r="C223" s="2" t="inlineStr">
         <is>
-          <t>RU000A10BQ60</t>
+          <t>RU000A1090A1</t>
         </is>
       </c>
       <c r="D223" s="2" t="inlineStr"/>
       <c r="E223" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F223" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G223" s="2" t="inlineStr">
         <is>
-          <t>Информационный (отчётность эмитента) +
-Раскрытие отчётности эмитента</t>
+          <t>Раскрытие отчётности</t>
         </is>
       </c>
       <c r="H223" s="2" t="inlineStr">
         <is>
-          <t>Досрочное погашение в случае делистинга</t>
+          <t>Досрочное погашение в случае нарушения Эмитентом сроков</t>
         </is>
       </c>
       <c r="I223" s="2" t="inlineStr">
@@ -12155,42 +12054,51 @@
         </is>
       </c>
       <c r="K223" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L223" s="2" t="inlineStr">
         <is>
-          <t>16652_0_Решение_о_выпуске_001Р-08.pdf</t>
+          <t>15470_0_Решение_о_выпуске_001P-02.pdf</t>
         </is>
       </c>
       <c r="M223" s="2" t="inlineStr">
         <is>
-          <t>5.6.1 Досрочное погашение облигаций по требованию их владельцев: Владельцы Биржевых облигаций вправе предъявить их к досрочному погашению в случае делистинга Биржевых облигаций на всех биржах, осуществивших их допуск к организованным торгам. Досрочное погашение Биржевых облигаций производится денежными средствами в российских рублях в безналичном порядке. Владелец Биржевых облигаций, права которого на Биржевые облигации учитываются5 депоз</t>
+          <t>5.6.1 Досрочное погашение облигаций по требованию их владельцев Владельцы Биржевых облигаций вправе требовать досрочного погашения Биржевых облигаций в случае нарушения Эмитентом сроков публикации промежуточной бухгалтерской (финансовой) отчетности Эмитента за 3, 6 и 9 месяцев отчетного года, подготовленной в соответствии с Российскими стандартами бухгалтерского учета (далее – РСБУ), в составе формы 1 («Бухгалтерский баланс») и формы 2 («Отчет о финансовых результатах») на Страниц</t>
         </is>
       </c>
       <c r="N223" s="3" t="inlineStr">
         <is>
-          <t>https://st.finam.ru/ipo/genconditions/16652_0_Решение_о_выпуске_001Р-08.pdf</t>
+          <t>https://st.finam.ru/ipo/genconditions/15470_0_Решение_о_выпуске_001P-02.pdf</t>
         </is>
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="2" t="inlineStr"/>
+      <c r="A224" s="2" t="inlineStr">
+        <is>
+          <t>ТАЛК ЛИЗИНГ-001P-03</t>
+        </is>
+      </c>
       <c r="B224" s="2" t="inlineStr"/>
-      <c r="C224" s="2" t="inlineStr"/>
+      <c r="C224" s="2" t="inlineStr">
+        <is>
+          <t>RU000A109DP7</t>
+        </is>
+      </c>
       <c r="D224" s="2" t="inlineStr"/>
-      <c r="E224" s="2" t="inlineStr"/>
+      <c r="E224" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="F224" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G224" s="2" t="inlineStr">
         <is>
-          <t>Информационный (отчётность эмитента) +
-Раскрытие отчётности эмитента</t>
+          <t>Раскрытие отчётности</t>
         </is>
       </c>
       <c r="H224" s="2" t="inlineStr">
         <is>
-          <t>Нераскрытие или раскрытие годовой консолидированной финансовой отчетности АО «Промагрологистика» (ОГРН 1047796793956, ИНН 7701562811) с нарушением сроков, указанных ниже, начиная с отчетности за 2024 …</t>
+          <t>Досрочное погашение в случае нарушения Эмитентом сроков</t>
         </is>
       </c>
       <c r="I224" s="2" t="inlineStr">
@@ -12200,105 +12108,113 @@
       </c>
       <c r="J224" s="2" t="inlineStr">
         <is>
-          <t>п. 5.6.1, 2</t>
+          <t>п. 5.6.1, 1</t>
         </is>
       </c>
       <c r="K224" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L224" s="2" t="inlineStr">
         <is>
-          <t>16652_0_Решение_о_выпуске_001Р-08.pdf</t>
+          <t>15601_0_Решение о выпуске 001P-03.pdf</t>
         </is>
       </c>
       <c r="M224" s="2" t="inlineStr">
         <is>
-          <t>Нераскрытие или раскрытие годовой консолидированной финансовой отчетности АО «Промагрологистика» (ОГРН 1047796793956, ИНН 7701562811) с нарушением сроков, указанных ниже, начиная с отчетности за 2024 год. Под годовой консолидированной финансовой отчетностью АО «Промагрологистика» подразумевается консолидированная финансовая отчетность АО «Промагрологистика» за отчетный год, составленная в соответствии с Международными стандартами финансовой отчетности (МСФО) с приложенным аудиторским заключением</t>
+          <t>5.6.1 Досрочное погашение облигаций по требованию их владельцев Владельцы Биржевых облигаций вправе требовать досрочного погашения Биржевых облигаций в случае нарушения Эмитентом сроков публикации промежуточной бухгалтерской (финансовой) отчетности Эмитента за 3, 6 и 9 месяцев отчетного года, подготовленной в соответствии с Российскими стандартами бухгалтерского учета (далее – РСБУ), в составе формы 1 («Бухгалтерский баланс») и формы 2 («Отчет о финансовых результатах») на Страниц</t>
         </is>
       </c>
       <c r="N224" s="3" t="inlineStr">
         <is>
-          <t>https://st.finam.ru/ipo/genconditions/16652_0_Решение_о_выпуске_001Р-08.pdf</t>
+          <t>https://st.finam.ru/ipo/genconditions/15601_0_Решение о выпуске 001P-03.pdf</t>
         </is>
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="7" t="inlineStr"/>
-      <c r="B225" s="7" t="inlineStr"/>
-      <c r="C225" s="7" t="inlineStr"/>
-      <c r="D225" s="7" t="inlineStr"/>
-      <c r="E225" s="7" t="inlineStr"/>
-      <c r="F225" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="G225" s="7" t="inlineStr">
-        <is>
-          <t>Информационный (отчётность эмитента) +
-Раскрытие отчётности эмитента</t>
-        </is>
-      </c>
-      <c r="H225" s="7" t="inlineStr">
-        <is>
-          <t>Досрочное погашение в случае ликвидации (из Программы)</t>
-        </is>
-      </c>
-      <c r="I225" s="7" t="inlineStr">
-        <is>
-          <t>Программа облигаций (e-disclosure)</t>
-        </is>
-      </c>
-      <c r="J225" s="7" t="inlineStr">
-        <is>
-          <t>п. 9.3</t>
-        </is>
-      </c>
-      <c r="K225" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L225" s="7" t="inlineStr">
-        <is>
-          <t>files.aspx</t>
-        </is>
-      </c>
-      <c r="M225" s="7" t="inlineStr">
-        <is>
-          <t>ного погашения Биржевых облигаций и выплаты ему накопленного купонного дохода по Биржевым облигациям, рассчитанного на дату исполнения обязательств по досрочному погашению Биржевых облигаций, в случаях, указанных в п. 9.5.1. Программы, а также предусмотренных законодательством Российской Федерации. В случае ликвидации Эмитента владелец Биржевой облигации вправе получить причитающиеся денежные средства в порядке очередности, установленной в соответствии со статьей 64 Гражданского кодекса Российск</t>
-        </is>
-      </c>
-      <c r="N225" s="8" t="inlineStr">
-        <is>
-          <t>https://e-disclosure.ru/portal/files.aspx?id=37542&amp;type=7</t>
+      <c r="A225" s="2" t="inlineStr">
+        <is>
+          <t>ТАЛК ЛИЗИНГ-002P-01</t>
+        </is>
+      </c>
+      <c r="B225" s="2" t="inlineStr"/>
+      <c r="C225" s="2" t="inlineStr">
+        <is>
+          <t>RU000A10B5C7</t>
+        </is>
+      </c>
+      <c r="D225" s="2" t="inlineStr"/>
+      <c r="E225" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F225" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G225" s="2" t="inlineStr">
+        <is>
+          <t>Раскрытие отчётности</t>
+        </is>
+      </c>
+      <c r="H225" s="2" t="inlineStr">
+        <is>
+          <t>Досрочное погашение в случае нарушения Эмитентом сроков</t>
+        </is>
+      </c>
+      <c r="I225" s="2" t="inlineStr">
+        <is>
+          <t>Решение о выпуске</t>
+        </is>
+      </c>
+      <c r="J225" s="2" t="inlineStr">
+        <is>
+          <t>п. 5.6.1, 1</t>
+        </is>
+      </c>
+      <c r="K225" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="L225" s="2" t="inlineStr">
+        <is>
+          <t>16436_0_Решение о выпуске 002P-01.pdf</t>
+        </is>
+      </c>
+      <c r="M225" s="2" t="inlineStr">
+        <is>
+          <t>5.6.1 Досрочное погашение облигаций по требованию их владельцев Владельцы Биржевых облигаций вправе требовать досрочного погашения Биржевых облигаций в случае нарушения Эмитентом сроков публикации промежуточной бухгалтерской (финансовой) отчетности Эмитента за 3, 6 и 9 месяцев отчетного года, подготовленной в соответствии с Российскими стандартами бухгалтерского учета (далее – РСБУ), в составе бухгалтерского баланса, отчета о финансовых результатах и приложений к ним, на Странице</t>
+        </is>
+      </c>
+      <c r="N225" s="3" t="inlineStr">
+        <is>
+          <t>https://st.finam.ru/ipo/genconditions/16436_0_Решение о выпуске 002P-01.pdf</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>РОЛЬФ-001Р-09</t>
+          <t>ТАЛК ЛИЗИНГ-002P-02</t>
         </is>
       </c>
       <c r="B226" s="2" t="inlineStr"/>
       <c r="C226" s="2" t="inlineStr">
         <is>
-          <t>RU000A10F850</t>
+          <t>RU000A10BWN3</t>
         </is>
       </c>
       <c r="D226" s="2" t="inlineStr"/>
       <c r="E226" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F226" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G226" s="2" t="inlineStr">
         <is>
-          <t>Информационный (отчётность эмитента) +
-Раскрытие отчётности эмитента</t>
+          <t>Раскрытие отчётности</t>
         </is>
       </c>
       <c r="H226" s="2" t="inlineStr">
         <is>
-          <t>Нарушение Эмитентом сроков публикации консолидированной финансовой отчетности АО «Промагрологистика» (ОГРН 1047796793956, ИНН 7701562811), установленных ниже</t>
+          <t>Досрочное погашение в случае нарушения Эмитентом сроков</t>
         </is>
       </c>
       <c r="I226" s="2" t="inlineStr">
@@ -12312,42 +12228,51 @@
         </is>
       </c>
       <c r="K226" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L226" s="2" t="inlineStr">
         <is>
-          <t>18254_0_Решение_о_выпуске_001Р-09.pdf</t>
+          <t>16837_0_Решение о выпуске 002P-02.pdf</t>
         </is>
       </c>
       <c r="M226" s="2" t="inlineStr">
         <is>
-          <t>Нарушение Эмитентом сроков публикации консолидированной финансовой отчетности АО «Промагрологистика» (ОГРН 1047796793956, ИНН 7701562811), установленных ниже. Под годовой консолидированной финансовой отчетностью АО «Промагрологистика» подразумевается консолидированная финансовая отчетность АО «Промагрологистика» за отчетный год, составленная в соответствии с Международными стандартами финансовой отчетности (МСФО) с приложенным аудиторским заключением в отношении указанной годовой консолидированн</t>
+          <t>5.6.1 Досрочное погашение облигаций по требованию их владельцев Владельцы Биржевых облигаций вправе требовать досрочного погашения Биржевых облигаций в случае нарушения Эмитентом сроков публикации промежуточной бухгалтерской (финансовой) отчетности Эмитента за 3, 6 и 9 месяцев отчетного года, подготовленной в соответствии с Российскими стандартами бухгалтерского учета (далее – РСБУ), в составе бухгалтерского баланса, отчета о финансовых результатах и приложений к ним, на Странице</t>
         </is>
       </c>
       <c r="N226" s="3" t="inlineStr">
         <is>
-          <t>https://st.finam.ru/ipo/genconditions/18254_0_Решение_о_выпуске_001Р-09.pdf</t>
+          <t>https://st.finam.ru/ipo/genconditions/16837_0_Решение о выпуске 002P-02.pdf</t>
         </is>
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="2" t="inlineStr"/>
+      <c r="A227" s="2" t="inlineStr">
+        <is>
+          <t>ТАЛК ЛИЗИНГ-002P-03</t>
+        </is>
+      </c>
       <c r="B227" s="2" t="inlineStr"/>
-      <c r="C227" s="2" t="inlineStr"/>
+      <c r="C227" s="2" t="inlineStr">
+        <is>
+          <t>RU000A10CUF1</t>
+        </is>
+      </c>
       <c r="D227" s="2" t="inlineStr"/>
-      <c r="E227" s="2" t="inlineStr"/>
+      <c r="E227" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="F227" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G227" s="2" t="inlineStr">
         <is>
-          <t>Информационный (отчётность эмитента) +
-Раскрытие отчётности эмитента</t>
+          <t>Раскрытие отчётности</t>
         </is>
       </c>
       <c r="H227" s="2" t="inlineStr">
         <is>
-          <t>Досрочное погашение в случае делистинга</t>
+          <t>Досрочное погашение в случае нарушения Эмитентом сроков</t>
         </is>
       </c>
       <c r="I227" s="2" t="inlineStr">
@@ -12357,105 +12282,115 @@
       </c>
       <c r="J227" s="2" t="inlineStr">
         <is>
-          <t>п. 5.6.1, 2</t>
+          <t>п. 5.6.1, 1</t>
         </is>
       </c>
       <c r="K227" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L227" s="2" t="inlineStr">
         <is>
-          <t>18254_0_Решение_о_выпуске_001Р-09.pdf</t>
+          <t>17221_0_Решение о выпуске 002P-03.pdf</t>
         </is>
       </c>
       <c r="M227" s="2" t="inlineStr">
         <is>
-          <t>5.6.1 Досрочное погашение облигаций по требованию их владельцев: Владельцы Биржевых облигаций вправе предъявить их к досрочному погашению в случае делистинга Биржевых облигаций на всех биржах, осуществивших их допуск к организованным торгам. Досрочное погашение Биржевых облигаций производится денежными средствами в российских рублях в безналичном порядке. Владелец Биржевых облигаций, права которого на Биржевые облигации учитываются5 депоз</t>
+          <t>5.6.1 Досрочное погашение облигаций по требованию их владельцев Владельцы Биржевых облигаций вправе требовать досрочного погашения Биржевых облигаций в случае нарушения Эмитентом сроков публикации промежуточной бухгалтерской (финансовой) отчетности Эмитента за 3, 6 и 9 месяцев отчетного года, подготовленной в соответствии с Российскими стандартами бухгалтерского учета (далее – РСБУ), в составе бухгалтерского баланса, отчета о финансовых результатах и приложений к ним, на Странице</t>
         </is>
       </c>
       <c r="N227" s="3" t="inlineStr">
         <is>
-          <t>https://st.finam.ru/ipo/genconditions/18254_0_Решение_о_выпуске_001Р-09.pdf</t>
+          <t>https://st.finam.ru/ipo/decision/17221_0_Решение о выпуске 002P-03.pdf</t>
         </is>
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="7" t="inlineStr"/>
-      <c r="B228" s="7" t="inlineStr"/>
-      <c r="C228" s="7" t="inlineStr"/>
-      <c r="D228" s="7" t="inlineStr"/>
-      <c r="E228" s="7" t="inlineStr"/>
-      <c r="F228" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="G228" s="7" t="inlineStr">
-        <is>
-          <t>Информационный (отчётность эмитента) +
-Раскрытие отчётности эмитента</t>
-        </is>
-      </c>
-      <c r="H228" s="7" t="inlineStr">
-        <is>
-          <t>Досрочное погашение в случае ликвидации (из Программы)</t>
-        </is>
-      </c>
-      <c r="I228" s="7" t="inlineStr">
-        <is>
-          <t>Программа облигаций (e-disclosure)</t>
-        </is>
-      </c>
-      <c r="J228" s="7" t="inlineStr">
-        <is>
-          <t>п. 9.3</t>
-        </is>
-      </c>
-      <c r="K228" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L228" s="7" t="inlineStr">
-        <is>
-          <t>files.aspx</t>
-        </is>
-      </c>
-      <c r="M228" s="7" t="inlineStr">
-        <is>
-          <t>ного погашения Биржевых облигаций и выплаты ему накопленного купонного дохода по Биржевым облигациям, рассчитанного на дату исполнения обязательств по досрочному погашению Биржевых облигаций, в случаях, указанных в п. 9.5.1. Программы, а также предусмотренных законодательством Российской Федерации. В случае ликвидации Эмитента владелец Биржевой облигации вправе получить причитающиеся денежные средства в порядке очередности, установленной в соответствии со статьей 64 Гражданского кодекса Российск</t>
-        </is>
-      </c>
-      <c r="N228" s="8" t="inlineStr">
-        <is>
-          <t>https://e-disclosure.ru/portal/files.aspx?id=37542&amp;type=7</t>
+      <c r="A228" s="2" t="inlineStr">
+        <is>
+          <t>ТАЛК ЛИЗИНГ-003P-01</t>
+        </is>
+      </c>
+      <c r="B228" s="2" t="inlineStr"/>
+      <c r="C228" s="2" t="inlineStr">
+        <is>
+          <t>RU000A10FPN8</t>
+        </is>
+      </c>
+      <c r="D228" s="2" t="inlineStr"/>
+      <c r="E228" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F228" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G228" s="2" t="inlineStr">
+        <is>
+          <t>Раскрытие отчётности</t>
+        </is>
+      </c>
+      <c r="H228" s="2" t="inlineStr">
+        <is>
+          <t>Досрочное погашение в случае нарушения Эмитентом сроков</t>
+        </is>
+      </c>
+      <c r="I228" s="2" t="inlineStr">
+        <is>
+          <t>Решение о выпуске</t>
+        </is>
+      </c>
+      <c r="J228" s="2" t="inlineStr">
+        <is>
+          <t>п. 5.6.1, 1</t>
+        </is>
+      </c>
+      <c r="K228" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="L228" s="2" t="inlineStr">
+        <is>
+          <t>18523_0_Решение о выпуске 003P-01.pdf</t>
+        </is>
+      </c>
+      <c r="M228" s="2" t="inlineStr">
+        <is>
+          <t>5.6.1 Досрочное погашение облигаций по требованию их владельцев Владельцы Биржевых облигаций вправе требовать досрочного погашения Биржевых облигаций в случае нарушения Эмитентом сроков публикации промежуточной бухгалтерской (финансовой) отчетности Эмитента, установленных ниже (далее – Событие досрочного погашения по требованию владельцев Биржевых облигаций). Под промежуточной бухгалтерской (финансовой) отчетностью Эмитента подразумевается неаудированная промежуточная бухгалтерска</t>
+        </is>
+      </c>
+      <c r="N228" s="3" t="inlineStr">
+        <is>
+          <t>https://st.finam.ru/ipo/genconditions/18523_0_Решение о выпуске 003P-01.pdf</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>ТАЛК ЛИЗИНГ-001P-02</t>
+          <t>ТГК-14-001Р-02</t>
         </is>
       </c>
       <c r="B229" s="2" t="inlineStr"/>
       <c r="C229" s="2" t="inlineStr">
         <is>
-          <t>RU000A1090A1</t>
+          <t>RU000A106MW0</t>
         </is>
       </c>
       <c r="D229" s="2" t="inlineStr"/>
       <c r="E229" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F229" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="F229" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="G229" s="2" t="inlineStr">
         <is>
-          <t>Информационный (отчётность эмитента) +
-Раскрытие отчётности эмитента</t>
+          <t>Положения о досрочном погашении</t>
         </is>
       </c>
       <c r="H229" s="2" t="inlineStr">
         <is>
-          <t>Досрочное погашение в случае нарушения Эмитентом сроков</t>
+          <t>Put-опция у владельцев отсутствует</t>
         </is>
       </c>
       <c r="I229" s="2" t="inlineStr">
@@ -12463,58 +12398,49 @@
           <t>Решение о выпуске</t>
         </is>
       </c>
-      <c r="J229" s="2" t="inlineStr">
-        <is>
-          <t>п. 5.6.1, 1</t>
-        </is>
-      </c>
-      <c r="K229" s="2" t="n">
-        <v>7</v>
-      </c>
+      <c r="J229" s="2" t="inlineStr"/>
+      <c r="K229" s="2" t="inlineStr"/>
       <c r="L229" s="2" t="inlineStr">
         <is>
-          <t>15470_0_Решение_о_выпуске_001P-02.pdf</t>
-        </is>
-      </c>
-      <c r="M229" s="2" t="inlineStr">
-        <is>
-          <t>5.6.1 Досрочное погашение облигаций по требованию их владельцев Владельцы Биржевых облигаций вправе требовать досрочного погашения Биржевых облигаций в случае нарушения Эмитентом сроков публикации промежуточной бухгалтерской (финансовой) отчетности Эмитента за 3, 6 и 9 месяцев отчетного года, подготовленной в соответствии с Российскими стандартами бухгалтерского учета (далее – РСБУ), в составе формы 1 («Бухгалтерский баланс») и формы 2 («Отчет о финансовых результатах») на Страниц</t>
-        </is>
-      </c>
+          <t>14287_0_Решение_о_выпуске_001Р-02.pdf</t>
+        </is>
+      </c>
+      <c r="M229" s="2" t="inlineStr"/>
       <c r="N229" s="3" t="inlineStr">
         <is>
-          <t>https://st.finam.ru/ipo/genconditions/15470_0_Решение_о_выпуске_001P-02.pdf</t>
+          <t>https://st.finam.ru/ipo/genconditions/14287_0_Решение_о_выпуске_001Р-02.pdf</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>ТАЛК ЛИЗИНГ-001P-03</t>
+          <t>ТГК-14-001Р-03</t>
         </is>
       </c>
       <c r="B230" s="2" t="inlineStr"/>
       <c r="C230" s="2" t="inlineStr">
         <is>
-          <t>RU000A109DP7</t>
+          <t>RU000A10AEF9</t>
         </is>
       </c>
       <c r="D230" s="2" t="inlineStr"/>
       <c r="E230" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F230" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="F230" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="G230" s="2" t="inlineStr">
         <is>
-          <t>Информационный (отчётность эмитента) +
-Раскрытие отчётности эмитента</t>
+          <t>Положения о досрочном погашении</t>
         </is>
       </c>
       <c r="H230" s="2" t="inlineStr">
         <is>
-          <t>Досрочное погашение в случае нарушения Эмитентом сроков</t>
+          <t>Put-опция у владельцев отсутствует</t>
         </is>
       </c>
       <c r="I230" s="2" t="inlineStr">
@@ -12522,58 +12448,49 @@
           <t>Решение о выпуске</t>
         </is>
       </c>
-      <c r="J230" s="2" t="inlineStr">
-        <is>
-          <t>п. 5.6.1, 1</t>
-        </is>
-      </c>
-      <c r="K230" s="2" t="n">
-        <v>7</v>
-      </c>
+      <c r="J230" s="2" t="inlineStr"/>
+      <c r="K230" s="2" t="inlineStr"/>
       <c r="L230" s="2" t="inlineStr">
         <is>
-          <t>15601_0_Решение о выпуске 001P-03.pdf</t>
-        </is>
-      </c>
-      <c r="M230" s="2" t="inlineStr">
-        <is>
-          <t>5.6.1 Досрочное погашение облигаций по требованию их владельцев Владельцы Биржевых облигаций вправе требовать досрочного погашения Биржевых облигаций в случае нарушения Эмитентом сроков публикации промежуточной бухгалтерской (финансовой) отчетности Эмитента за 3, 6 и 9 месяцев отчетного года, подготовленной в соответствии с Российскими стандартами бухгалтерского учета (далее – РСБУ), в составе формы 1 («Бухгалтерский баланс») и формы 2 («Отчет о финансовых результатах») на Страниц</t>
-        </is>
-      </c>
+          <t>16028_0_Решение_о_выпуске_001Р-03.pdf</t>
+        </is>
+      </c>
+      <c r="M230" s="2" t="inlineStr"/>
       <c r="N230" s="3" t="inlineStr">
         <is>
-          <t>https://st.finam.ru/ipo/genconditions/15601_0_Решение о выпуске 001P-03.pdf</t>
+          <t>https://st.finam.ru/ipo/genconditions/16028_0_Решение_о_выпуске_001Р-03.pdf</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>ТАЛК ЛИЗИНГ-002P-01</t>
+          <t>ТГК-14-001Р-04</t>
         </is>
       </c>
       <c r="B231" s="2" t="inlineStr"/>
       <c r="C231" s="2" t="inlineStr">
         <is>
-          <t>RU000A10B5C7</t>
+          <t>RU000A10AEE2</t>
         </is>
       </c>
       <c r="D231" s="2" t="inlineStr"/>
       <c r="E231" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F231" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="F231" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="G231" s="2" t="inlineStr">
         <is>
-          <t>Информационный (отчётность эмитента) +
-Раскрытие отчётности эмитента</t>
+          <t>Положения о досрочном погашении</t>
         </is>
       </c>
       <c r="H231" s="2" t="inlineStr">
         <is>
-          <t>Досрочное погашение в случае нарушения Эмитентом сроков</t>
+          <t>Put-опция у владельцев отсутствует</t>
         </is>
       </c>
       <c r="I231" s="2" t="inlineStr">
@@ -12581,58 +12498,49 @@
           <t>Решение о выпуске</t>
         </is>
       </c>
-      <c r="J231" s="2" t="inlineStr">
-        <is>
-          <t>п. 5.6.1, 1</t>
-        </is>
-      </c>
-      <c r="K231" s="2" t="n">
-        <v>7</v>
-      </c>
+      <c r="J231" s="2" t="inlineStr"/>
+      <c r="K231" s="2" t="inlineStr"/>
       <c r="L231" s="2" t="inlineStr">
         <is>
-          <t>16436_0_Решение о выпуске 002P-01.pdf</t>
-        </is>
-      </c>
-      <c r="M231" s="2" t="inlineStr">
-        <is>
-          <t>5.6.1 Досрочное погашение облигаций по требованию их владельцев Владельцы Биржевых облигаций вправе требовать досрочного погашения Биржевых облигаций в случае нарушения Эмитентом сроков публикации промежуточной бухгалтерской (финансовой) отчетности Эмитента за 3, 6 и 9 месяцев отчетного года, подготовленной в соответствии с Российскими стандартами бухгалтерского учета (далее – РСБУ), в составе бухгалтерского баланса, отчета о финансовых результатах и приложений к ним, на Странице</t>
-        </is>
-      </c>
+          <t>16029_0_Решение_о_выпуске_001Р-04.pdf</t>
+        </is>
+      </c>
+      <c r="M231" s="2" t="inlineStr"/>
       <c r="N231" s="3" t="inlineStr">
         <is>
-          <t>https://st.finam.ru/ipo/genconditions/16436_0_Решение о выпуске 002P-01.pdf</t>
+          <t>https://st.finam.ru/ipo/genconditions/16029_0_Решение_о_выпуске_001Р-04.pdf</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>ТАЛК ЛИЗИНГ-002P-02</t>
+          <t>ТГК-14-001Р-05</t>
         </is>
       </c>
       <c r="B232" s="2" t="inlineStr"/>
       <c r="C232" s="2" t="inlineStr">
         <is>
-          <t>RU000A10BWN3</t>
+          <t>RU000A10AS02</t>
         </is>
       </c>
       <c r="D232" s="2" t="inlineStr"/>
       <c r="E232" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F232" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="F232" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="G232" s="2" t="inlineStr">
         <is>
-          <t>Информационный (отчётность эмитента) +
-Раскрытие отчётности эмитента</t>
+          <t>Положения о досрочном погашении</t>
         </is>
       </c>
       <c r="H232" s="2" t="inlineStr">
         <is>
-          <t>Досрочное погашение в случае нарушения Эмитентом сроков</t>
+          <t>Put-опция у владельцев отсутствует</t>
         </is>
       </c>
       <c r="I232" s="2" t="inlineStr">
@@ -12640,58 +12548,49 @@
           <t>Решение о выпуске</t>
         </is>
       </c>
-      <c r="J232" s="2" t="inlineStr">
-        <is>
-          <t>п. 5.6.1, 1</t>
-        </is>
-      </c>
-      <c r="K232" s="2" t="n">
-        <v>7</v>
-      </c>
+      <c r="J232" s="2" t="inlineStr"/>
+      <c r="K232" s="2" t="inlineStr"/>
       <c r="L232" s="2" t="inlineStr">
         <is>
-          <t>16837_0_Решение о выпуске 002P-02.pdf</t>
-        </is>
-      </c>
-      <c r="M232" s="2" t="inlineStr">
-        <is>
-          <t>5.6.1 Досрочное погашение облигаций по требованию их владельцев Владельцы Биржевых облигаций вправе требовать досрочного погашения Биржевых облигаций в случае нарушения Эмитентом сроков публикации промежуточной бухгалтерской (финансовой) отчетности Эмитента за 3, 6 и 9 месяцев отчетного года, подготовленной в соответствии с Российскими стандартами бухгалтерского учета (далее – РСБУ), в составе бухгалтерского баланса, отчета о финансовых результатах и приложений к ним, на Странице</t>
-        </is>
-      </c>
+          <t>16152_0_Решение_о_выпуске_001Р-05.pdf</t>
+        </is>
+      </c>
+      <c r="M232" s="2" t="inlineStr"/>
       <c r="N232" s="3" t="inlineStr">
         <is>
-          <t>https://st.finam.ru/ipo/genconditions/16837_0_Решение о выпуске 002P-02.pdf</t>
+          <t>https://st.finam.ru/ipo/genconditions/16152_0_Решение_о_выпуске_001Р-05.pdf</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
         <is>
-          <t>ТАЛК ЛИЗИНГ-002P-03</t>
+          <t>ТГК-14-001Р-06</t>
         </is>
       </c>
       <c r="B233" s="2" t="inlineStr"/>
       <c r="C233" s="2" t="inlineStr">
         <is>
-          <t>RU000A10CUF1</t>
+          <t>RU000A10ARZ9</t>
         </is>
       </c>
       <c r="D233" s="2" t="inlineStr"/>
       <c r="E233" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F233" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="F233" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="G233" s="2" t="inlineStr">
         <is>
-          <t>Информационный (отчётность эмитента) +
-Раскрытие отчётности эмитента</t>
+          <t>Положения о досрочном погашении</t>
         </is>
       </c>
       <c r="H233" s="2" t="inlineStr">
         <is>
-          <t>Досрочное погашение в случае нарушения Эмитентом сроков</t>
+          <t>Put-опция у владельцев отсутствует</t>
         </is>
       </c>
       <c r="I233" s="2" t="inlineStr">
@@ -12699,58 +12598,49 @@
           <t>Решение о выпуске</t>
         </is>
       </c>
-      <c r="J233" s="2" t="inlineStr">
-        <is>
-          <t>п. 5.6.1, 1</t>
-        </is>
-      </c>
-      <c r="K233" s="2" t="n">
-        <v>7</v>
-      </c>
+      <c r="J233" s="2" t="inlineStr"/>
+      <c r="K233" s="2" t="inlineStr"/>
       <c r="L233" s="2" t="inlineStr">
         <is>
-          <t>17221_0_Решение о выпуске 002P-03.pdf</t>
-        </is>
-      </c>
-      <c r="M233" s="2" t="inlineStr">
-        <is>
-          <t>5.6.1 Досрочное погашение облигаций по требованию их владельцев Владельцы Биржевых облигаций вправе требовать досрочного погашения Биржевых облигаций в случае нарушения Эмитентом сроков публикации промежуточной бухгалтерской (финансовой) отчетности Эмитента за 3, 6 и 9 месяцев отчетного года, подготовленной в соответствии с Российскими стандартами бухгалтерского учета (далее – РСБУ), в составе бухгалтерского баланса, отчета о финансовых результатах и приложений к ним, на Странице</t>
-        </is>
-      </c>
+          <t>16153_0_Решение_о_выпуске_001Р-06.pdf</t>
+        </is>
+      </c>
+      <c r="M233" s="2" t="inlineStr"/>
       <c r="N233" s="3" t="inlineStr">
         <is>
-          <t>https://st.finam.ru/ipo/decision/17221_0_Решение о выпуске 002P-03.pdf</t>
+          <t>https://st.finam.ru/ipo/genconditions/16153_0_Решение_о_выпуске_001Р-06.pdf</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>ТАЛК ЛИЗИНГ-003P-01</t>
+          <t>ТГК-14-001Р-07</t>
         </is>
       </c>
       <c r="B234" s="2" t="inlineStr"/>
       <c r="C234" s="2" t="inlineStr">
         <is>
-          <t>RU000A10FPN8</t>
+          <t>RU000A10BPF3</t>
         </is>
       </c>
       <c r="D234" s="2" t="inlineStr"/>
       <c r="E234" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F234" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="F234" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="G234" s="2" t="inlineStr">
         <is>
-          <t>Информационный (отчётность эмитента) +
-Раскрытие отчётности эмитента</t>
+          <t>Положения о досрочном погашении</t>
         </is>
       </c>
       <c r="H234" s="2" t="inlineStr">
         <is>
-          <t>Досрочное погашение в случае нарушения Эмитентом сроков</t>
+          <t>Put-опция у владельцев отсутствует</t>
         </is>
       </c>
       <c r="I234" s="2" t="inlineStr">
@@ -12758,59 +12648,47 @@
           <t>Решение о выпуске</t>
         </is>
       </c>
-      <c r="J234" s="2" t="inlineStr">
-        <is>
-          <t>п. 5.6.1, 1</t>
-        </is>
-      </c>
-      <c r="K234" s="2" t="n">
-        <v>8</v>
-      </c>
+      <c r="J234" s="2" t="inlineStr"/>
+      <c r="K234" s="2" t="inlineStr"/>
       <c r="L234" s="2" t="inlineStr">
         <is>
-          <t>18523_0_Решение о выпуске 003P-01.pdf</t>
-        </is>
-      </c>
-      <c r="M234" s="2" t="inlineStr">
-        <is>
-          <t>5.6.1 Досрочное погашение облигаций по требованию их владельцев Владельцы Биржевых облигаций вправе требовать досрочного погашения Биржевых облигаций в случае нарушения Эмитентом сроков публикации промежуточной бухгалтерской (финансовой) отчетности Эмитента, установленных ниже (далее – Событие досрочного погашения по требованию владельцев Биржевых облигаций). Под промежуточной бухгалтерской (финансовой) отчетностью Эмитента подразумевается неаудированная промежуточная бухгалтерска</t>
-        </is>
-      </c>
+          <t>16626_0_Решение_о_выпуске_001Р-07.pdf</t>
+        </is>
+      </c>
+      <c r="M234" s="2" t="inlineStr"/>
       <c r="N234" s="3" t="inlineStr">
         <is>
-          <t>https://st.finam.ru/ipo/genconditions/18523_0_Решение о выпуске 003P-01.pdf</t>
+          <t>https://st.finam.ru/ipo/genconditions/16626_0_Решение_о_выпуске_001Р-07.pdf</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
         <is>
-          <t>ТГК-14-001Р-02</t>
+          <t>ТД РКС-002Р-04</t>
         </is>
       </c>
       <c r="B235" s="2" t="inlineStr"/>
       <c r="C235" s="2" t="inlineStr">
         <is>
-          <t>RU000A106MW0</t>
+          <t>RU000A108RK0</t>
         </is>
       </c>
       <c r="D235" s="2" t="inlineStr"/>
       <c r="E235" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F235" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="F235" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="G235" s="2" t="inlineStr">
         <is>
-          <t>Положения о досрочном погашении</t>
+          <t>Раскрытие отчётности</t>
         </is>
       </c>
       <c r="H235" s="2" t="inlineStr">
         <is>
-          <t>Put-опция у владельцев отсутствует</t>
+          <t>нераскрытие на Странице Поручителя в сети Интернет годовой консолидированной финансовой отчётности Поручителя, составленной в соответствии с Международными стандартами финансовой отчетности (далее - М…</t>
         </is>
       </c>
       <c r="I235" s="2" t="inlineStr">
@@ -12818,49 +12696,57 @@
           <t>Решение о выпуске</t>
         </is>
       </c>
-      <c r="J235" s="2" t="inlineStr"/>
-      <c r="K235" s="2" t="inlineStr"/>
+      <c r="J235" s="2" t="inlineStr">
+        <is>
+          <t>п. 5.6.1, 1</t>
+        </is>
+      </c>
+      <c r="K235" s="2" t="n">
+        <v>7</v>
+      </c>
       <c r="L235" s="2" t="inlineStr">
         <is>
-          <t>14287_0_Решение_о_выпуске_001Р-02.pdf</t>
-        </is>
-      </c>
-      <c r="M235" s="2" t="inlineStr"/>
+          <t>15303_0_решение о выпуске 002P-04.pdf</t>
+        </is>
+      </c>
+      <c r="M235" s="2" t="inlineStr">
+        <is>
+          <t>нераскрытие на Странице Поручителя в сети Интернет годовой консолидированной финансовой отчётности Поручителя, составленной в соответствии с Международными стандартами финансовой отчетности (далее - МСФО), с приложением аудиторского заключения в отношении такой отчётности в срок до 120 (Ста двадцати) дней после даты окончания отчетного года, за который составлена данная отчетность. Стоимость (порядок определения стоимости) досрочного погашения облигаций: Досрочное погашение Биржевых облигаций по</t>
+        </is>
+      </c>
       <c r="N235" s="3" t="inlineStr">
         <is>
-          <t>https://st.finam.ru/ipo/genconditions/14287_0_Решение_о_выпуске_001Р-02.pdf</t>
+          <t>https://st.finam.ru/ipo/genconditions/15303_0_решение о выпуске 002P-04.pdf</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>ТГК-14-001Р-03</t>
+          <t>ТД РКС-002Р-05</t>
         </is>
       </c>
       <c r="B236" s="2" t="inlineStr"/>
       <c r="C236" s="2" t="inlineStr">
         <is>
-          <t>RU000A10AEF9</t>
+          <t>RU000A10BQM7</t>
         </is>
       </c>
       <c r="D236" s="2" t="inlineStr"/>
       <c r="E236" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F236" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="F236" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="G236" s="2" t="inlineStr">
         <is>
-          <t>Положения о досрочном погашении</t>
+          <t>Раскрытие отчётности</t>
         </is>
       </c>
       <c r="H236" s="2" t="inlineStr">
         <is>
-          <t>Put-опция у владельцев отсутствует</t>
+          <t>нераскрытие на Странице Поручителя в сети Интернет годовой консолидированной финансовой отчётности Поручителя, составленной в соответствии с Международными стандартами финансовой отчетности, с приложе…</t>
         </is>
       </c>
       <c r="I236" s="2" t="inlineStr">
@@ -12868,49 +12754,47 @@
           <t>Решение о выпуске</t>
         </is>
       </c>
-      <c r="J236" s="2" t="inlineStr"/>
-      <c r="K236" s="2" t="inlineStr"/>
+      <c r="J236" s="2" t="inlineStr">
+        <is>
+          <t>п. 5.6.1, 1</t>
+        </is>
+      </c>
+      <c r="K236" s="2" t="n">
+        <v>7</v>
+      </c>
       <c r="L236" s="2" t="inlineStr">
         <is>
-          <t>16028_0_Решение_о_выпуске_001Р-03.pdf</t>
-        </is>
-      </c>
-      <c r="M236" s="2" t="inlineStr"/>
+          <t>16667_0_решение о выпуске 002P-05.pdf</t>
+        </is>
+      </c>
+      <c r="M236" s="2" t="inlineStr">
+        <is>
+          <t>нераскрытие на Странице Поручителя в сети Интернет годовой консолидированной финансовой отчётности Поручителя, составленной в соответствии с Международными стандартами финансовой отчетности, с приложением аудиторского заключения в отношении такой отчётности (Консолидированная финансовая отчетность) в срок до 120 (Ста двадцати) дней после даты окончания отчетного года, за который составлена данная отчетность. Моментом наступления События досрочного погашения по требованию владельцев Биржевых обли</t>
+        </is>
+      </c>
       <c r="N236" s="3" t="inlineStr">
         <is>
-          <t>https://st.finam.ru/ipo/genconditions/16028_0_Решение_о_выпуске_001Р-03.pdf</t>
+          <t>https://st.finam.ru/ipo/genconditions/16667_0_решение о выпуске 002P-05.pdf</t>
         </is>
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="2" t="inlineStr">
-        <is>
-          <t>ТГК-14-001Р-04</t>
-        </is>
-      </c>
+      <c r="A237" s="2" t="inlineStr"/>
       <c r="B237" s="2" t="inlineStr"/>
-      <c r="C237" s="2" t="inlineStr">
-        <is>
-          <t>RU000A10AEE2</t>
-        </is>
-      </c>
+      <c r="C237" s="2" t="inlineStr"/>
       <c r="D237" s="2" t="inlineStr"/>
-      <c r="E237" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F237" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="E237" s="2" t="inlineStr"/>
+      <c r="F237" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="G237" s="2" t="inlineStr">
         <is>
-          <t>Положения о досрочном погашении</t>
+          <t>Раскрытие отчётности</t>
         </is>
       </c>
       <c r="H237" s="2" t="inlineStr">
         <is>
-          <t>Put-опция у владельцев отсутствует</t>
+          <t>нераскрытие на Странице Поручителя в сети Интернет годовой бухгалтерской (финансовой) отчетности Поручителя, составленной в соответствии с Российскими стандартами бухгалтерского учета (далее - РСБУ), …</t>
         </is>
       </c>
       <c r="I237" s="2" t="inlineStr">
@@ -12918,49 +12802,57 @@
           <t>Решение о выпуске</t>
         </is>
       </c>
-      <c r="J237" s="2" t="inlineStr"/>
-      <c r="K237" s="2" t="inlineStr"/>
+      <c r="J237" s="2" t="inlineStr">
+        <is>
+          <t>п. 5.6.1, 2</t>
+        </is>
+      </c>
+      <c r="K237" s="2" t="n">
+        <v>7</v>
+      </c>
       <c r="L237" s="2" t="inlineStr">
         <is>
-          <t>16029_0_Решение_о_выпуске_001Р-04.pdf</t>
-        </is>
-      </c>
-      <c r="M237" s="2" t="inlineStr"/>
+          <t>16667_0_решение о выпуске 002P-05.pdf</t>
+        </is>
+      </c>
+      <c r="M237" s="2" t="inlineStr">
+        <is>
+          <t>нераскрытие на Странице Поручителя в сети Интернет годовой бухгалтерской (финансовой) отчетности Поручителя, составленной в соответствии с Российскими стандартами бухгалтерского учета (далее - РСБУ), в частности, с Федеральным законом от</t>
+        </is>
+      </c>
       <c r="N237" s="3" t="inlineStr">
         <is>
-          <t>https://st.finam.ru/ipo/genconditions/16029_0_Решение_о_выпуске_001Р-04.pdf</t>
+          <t>https://st.finam.ru/ipo/genconditions/16667_0_решение о выпуске 002P-05.pdf</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>ТГК-14-001Р-05</t>
+          <t>ТД РКС-002Р-06</t>
         </is>
       </c>
       <c r="B238" s="2" t="inlineStr"/>
       <c r="C238" s="2" t="inlineStr">
         <is>
-          <t>RU000A10AS02</t>
+          <t>RU000A10C758</t>
         </is>
       </c>
       <c r="D238" s="2" t="inlineStr"/>
       <c r="E238" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F238" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="F238" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="G238" s="2" t="inlineStr">
         <is>
-          <t>Положения о досрочном погашении</t>
+          <t>Раскрытие отчётности</t>
         </is>
       </c>
       <c r="H238" s="2" t="inlineStr">
         <is>
-          <t>Put-опция у владельцев отсутствует</t>
+          <t>нераскрытие на Странице Поручителя в сети Интернет годовой консолидированной финансовой отчётности Поручителя, составленной в соответствии с Международными стандартами финансовой отчетности, с приложе…</t>
         </is>
       </c>
       <c r="I238" s="2" t="inlineStr">
@@ -12968,49 +12860,47 @@
           <t>Решение о выпуске</t>
         </is>
       </c>
-      <c r="J238" s="2" t="inlineStr"/>
-      <c r="K238" s="2" t="inlineStr"/>
+      <c r="J238" s="2" t="inlineStr">
+        <is>
+          <t>п. 5.6.1, 1</t>
+        </is>
+      </c>
+      <c r="K238" s="2" t="n">
+        <v>8</v>
+      </c>
       <c r="L238" s="2" t="inlineStr">
         <is>
-          <t>16152_0_Решение_о_выпуске_001Р-05.pdf</t>
-        </is>
-      </c>
-      <c r="M238" s="2" t="inlineStr"/>
+          <t>16929_0_решение о выпуске 002P-06.pdf</t>
+        </is>
+      </c>
+      <c r="M238" s="2" t="inlineStr">
+        <is>
+          <t>нераскрытие на Странице Поручителя в сети Интернет годовой консолидированной финансовой отчётности Поручителя, составленной в соответствии с Международными стандартами финансовой отчетности, с приложением аудиторского заключения в отношении такой отчётности (Консолидированная финансовая отчетность) в срок до 120 (Ста двадцати) дней после даты окончания отчетного года, за который составлена данная отчетность. Моментом наступления События досрочного погашения по требованию владельцев Биржевых обли</t>
+        </is>
+      </c>
       <c r="N238" s="3" t="inlineStr">
         <is>
-          <t>https://st.finam.ru/ipo/genconditions/16152_0_Решение_о_выпуске_001Р-05.pdf</t>
+          <t>https://st.finam.ru/ipo/genconditions/16929_0_решение о выпуске 002P-06.pdf</t>
         </is>
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="2" t="inlineStr">
-        <is>
-          <t>ТГК-14-001Р-06</t>
-        </is>
-      </c>
+      <c r="A239" s="2" t="inlineStr"/>
       <c r="B239" s="2" t="inlineStr"/>
-      <c r="C239" s="2" t="inlineStr">
-        <is>
-          <t>RU000A10ARZ9</t>
-        </is>
-      </c>
+      <c r="C239" s="2" t="inlineStr"/>
       <c r="D239" s="2" t="inlineStr"/>
-      <c r="E239" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F239" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="E239" s="2" t="inlineStr"/>
+      <c r="F239" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="G239" s="2" t="inlineStr">
         <is>
-          <t>Положения о досрочном погашении</t>
+          <t>Раскрытие отчётности</t>
         </is>
       </c>
       <c r="H239" s="2" t="inlineStr">
         <is>
-          <t>Put-опция у владельцев отсутствует</t>
+          <t>нераскрытие на Странице Поручителя в сети Интернет годовой бухгалтерской (финансовой) отчетности Поручителя, составленной в соответствии с Российскими стандартами бухгалтерского учета (далее - РСБУ), …</t>
         </is>
       </c>
       <c r="I239" s="2" t="inlineStr">
@@ -13018,49 +12908,57 @@
           <t>Решение о выпуске</t>
         </is>
       </c>
-      <c r="J239" s="2" t="inlineStr"/>
-      <c r="K239" s="2" t="inlineStr"/>
+      <c r="J239" s="2" t="inlineStr">
+        <is>
+          <t>п. 5.6.1, 2</t>
+        </is>
+      </c>
+      <c r="K239" s="2" t="n">
+        <v>8</v>
+      </c>
       <c r="L239" s="2" t="inlineStr">
         <is>
-          <t>16153_0_Решение_о_выпуске_001Р-06.pdf</t>
-        </is>
-      </c>
-      <c r="M239" s="2" t="inlineStr"/>
+          <t>16929_0_решение о выпуске 002P-06.pdf</t>
+        </is>
+      </c>
+      <c r="M239" s="2" t="inlineStr">
+        <is>
+          <t>нераскрытие на Странице Поручителя в сети Интернет годовой бухгалтерской (финансовой) отчетности Поручителя, составленной в соответствии с Российскими стандартами бухгалтерского учета (далее - РСБУ), в частности, с Федеральным законом от</t>
+        </is>
+      </c>
       <c r="N239" s="3" t="inlineStr">
         <is>
-          <t>https://st.finam.ru/ipo/genconditions/16153_0_Решение_о_выпуске_001Р-06.pdf</t>
+          <t>https://st.finam.ru/ipo/genconditions/16929_0_решение о выпуске 002P-06.pdf</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>ТГК-14-001Р-07</t>
+          <t>ТД РКС-002Р-07</t>
         </is>
       </c>
       <c r="B240" s="2" t="inlineStr"/>
       <c r="C240" s="2" t="inlineStr">
         <is>
-          <t>RU000A10BPF3</t>
+          <t>RU000A10E6S8</t>
         </is>
       </c>
       <c r="D240" s="2" t="inlineStr"/>
       <c r="E240" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F240" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="F240" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="G240" s="2" t="inlineStr">
         <is>
-          <t>Положения о досрочном погашении</t>
+          <t>Раскрытие отчётности</t>
         </is>
       </c>
       <c r="H240" s="2" t="inlineStr">
         <is>
-          <t>Put-опция у владельцев отсутствует</t>
+          <t>нераскрытие на Странице Поручителя в сети Интернет годовой консолидированной финансовой отчётности Поручителя, составленной в соответствии с Международными стандартами финансовой отчетности (далее – М…</t>
         </is>
       </c>
       <c r="I240" s="2" t="inlineStr">
@@ -13068,48 +12966,47 @@
           <t>Решение о выпуске</t>
         </is>
       </c>
-      <c r="J240" s="2" t="inlineStr"/>
-      <c r="K240" s="2" t="inlineStr"/>
+      <c r="J240" s="2" t="inlineStr">
+        <is>
+          <t>п. 5.6.1, 1</t>
+        </is>
+      </c>
+      <c r="K240" s="2" t="n">
+        <v>8</v>
+      </c>
       <c r="L240" s="2" t="inlineStr">
         <is>
-          <t>16626_0_Решение_о_выпуске_001Р-07.pdf</t>
-        </is>
-      </c>
-      <c r="M240" s="2" t="inlineStr"/>
+          <t>17758_0_решение о выпуске 002P-07.pdf</t>
+        </is>
+      </c>
+      <c r="M240" s="2" t="inlineStr">
+        <is>
+          <t>нераскрытие на Странице Поручителя в сети Интернет годовой консолидированной финансовой отчётности Поручителя, составленной в соответствии с Международными стандартами финансовой отчетности (далее – МСФО), с приложением аудиторского заключения в отношении такой отчётности (Консолидированная финансовая отчетность) в срок до 120 (Ста двадцати) дней после даты окончания отчетного года, за который составлена данная отчетность. Моментом наступления События досрочного погашения по требованию владельце</t>
+        </is>
+      </c>
       <c r="N240" s="3" t="inlineStr">
         <is>
-          <t>https://st.finam.ru/ipo/genconditions/16626_0_Решение_о_выпуске_001Р-07.pdf</t>
+          <t>https://st.finam.ru/ipo/genconditions/17758_0_решение о выпуске 002P-07.pdf</t>
         </is>
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="2" t="inlineStr">
-        <is>
-          <t>ТД РКС-002Р-04</t>
-        </is>
-      </c>
+      <c r="A241" s="2" t="inlineStr"/>
       <c r="B241" s="2" t="inlineStr"/>
-      <c r="C241" s="2" t="inlineStr">
-        <is>
-          <t>RU000A108RK0</t>
-        </is>
-      </c>
+      <c r="C241" s="2" t="inlineStr"/>
       <c r="D241" s="2" t="inlineStr"/>
-      <c r="E241" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="E241" s="2" t="inlineStr"/>
       <c r="F241" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G241" s="2" t="inlineStr">
         <is>
-          <t>Информационный (отчётность эмитента) +
-Раскрытие отчётности эмитента</t>
+          <t>Раскрытие отчётности</t>
         </is>
       </c>
       <c r="H241" s="2" t="inlineStr">
         <is>
-          <t>нераскрытие на Странице Поручителя в сети Интернет годовой консолидированной финансовой отчётности Поручителя, составленной в соответствии с Международными стандартами финансовой отчетности (далее - М…</t>
+          <t>нераскрытие на Странице Поручителя в сети Интернет годовой бухгалтерской (финансовой) отчетности Поручителя, составленной в соответствии с Российскими стандартами бухгалтерского учета (далее - РСБУ), …</t>
         </is>
       </c>
       <c r="I241" s="2" t="inlineStr">
@@ -13119,38 +13016,38 @@
       </c>
       <c r="J241" s="2" t="inlineStr">
         <is>
-          <t>п. 5.6.1, 1</t>
+          <t>п. 5.6.1, 2</t>
         </is>
       </c>
       <c r="K241" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L241" s="2" t="inlineStr">
         <is>
-          <t>15303_0_решение о выпуске 002P-04.pdf</t>
+          <t>17758_0_решение о выпуске 002P-07.pdf</t>
         </is>
       </c>
       <c r="M241" s="2" t="inlineStr">
         <is>
-          <t>нераскрытие на Странице Поручителя в сети Интернет годовой консолидированной финансовой отчётности Поручителя, составленной в соответствии с Международными стандартами финансовой отчетности (далее - МСФО), с приложением аудиторского заключения в отношении такой отчётности в срок до 120 (Ста двадцати) дней после даты окончания отчетного года, за который составлена данная отчетность. Стоимость (порядок определения стоимости) досрочного погашения облигаций: Досрочное погашение Биржевых облигаций по</t>
+          <t>нераскрытие на Странице Поручителя в сети Интернет годовой бухгалтерской (финансовой) отчетности Поручителя, составленной в соответствии с Российскими стандартами бухгалтерского учета (далее - РСБУ), в частности, с Федеральным законом от</t>
         </is>
       </c>
       <c r="N241" s="3" t="inlineStr">
         <is>
-          <t>https://st.finam.ru/ipo/genconditions/15303_0_решение о выпуске 002P-04.pdf</t>
+          <t>https://st.finam.ru/ipo/genconditions/17758_0_решение о выпуске 002P-07.pdf</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
         <is>
-          <t>ТД РКС-002Р-05</t>
+          <t>ТД РКС-002Р-08</t>
         </is>
       </c>
       <c r="B242" s="2" t="inlineStr"/>
       <c r="C242" s="2" t="inlineStr">
         <is>
-          <t>RU000A10BQM7</t>
+          <t>RU000A10F0X0</t>
         </is>
       </c>
       <c r="D242" s="2" t="inlineStr"/>
@@ -13162,13 +13059,12 @@
       </c>
       <c r="G242" s="2" t="inlineStr">
         <is>
-          <t>Информационный (отчётность эмитента) +
-Раскрытие отчётности эмитента</t>
+          <t>Раскрытие отчётности</t>
         </is>
       </c>
       <c r="H242" s="2" t="inlineStr">
         <is>
-          <t>нераскрытие на Странице Поручителя в сети Интернет годовой консолидированной финансовой отчётности Поручителя, составленной в соответствии с Международными стандартами финансовой отчетности, с приложе…</t>
+          <t>нераскрытие на Странице Поручителя в сети Интернет годовой консолидированной финансовой отчётности Поручителя, составленной в соответствии с Международными стандартами финансовой отчетности (далее – М…</t>
         </is>
       </c>
       <c r="I242" s="2" t="inlineStr">
@@ -13182,21 +13078,21 @@
         </is>
       </c>
       <c r="K242" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L242" s="2" t="inlineStr">
         <is>
-          <t>16667_0_решение о выпуске 002P-05.pdf</t>
+          <t>18172_0_решение о выпуске 002P-08.pdf</t>
         </is>
       </c>
       <c r="M242" s="2" t="inlineStr">
         <is>
-          <t>нераскрытие на Странице Поручителя в сети Интернет годовой консолидированной финансовой отчётности Поручителя, составленной в соответствии с Международными стандартами финансовой отчетности, с приложением аудиторского заключения в отношении такой отчётности (Консолидированная финансовая отчетность) в срок до 120 (Ста двадцати) дней после даты окончания отчетного года, за который составлена данная отчетность. Моментом наступления События досрочного погашения по требованию владельцев Биржевых обли</t>
+          <t>нераскрытие на Странице Поручителя в сети Интернет годовой консолидированной финансовой отчётности Поручителя, составленной в соответствии с Международными стандартами финансовой отчетности (далее – МСФО), с приложением аудиторского заключения в отношении такой отчётности (Консолидированная финансовая отчетность) в срок до 120 (Ста двадцати) дней после даты окончания отчетного года, за который составлена данная отчетность. Моментом наступления События досрочного погашения по требованию владельце</t>
         </is>
       </c>
       <c r="N242" s="3" t="inlineStr">
         <is>
-          <t>https://st.finam.ru/ipo/genconditions/16667_0_решение о выпуске 002P-05.pdf</t>
+          <t>https://st.finam.ru/ipo/genconditions/18172_0_решение о выпуске 002P-08.pdf</t>
         </is>
       </c>
     </row>
@@ -13211,8 +13107,7 @@
       </c>
       <c r="G243" s="2" t="inlineStr">
         <is>
-          <t>Информационный (отчётность эмитента) +
-Раскрытие отчётности эмитента</t>
+          <t>Раскрытие отчётности</t>
         </is>
       </c>
       <c r="H243" s="2" t="inlineStr">
@@ -13231,11 +13126,11 @@
         </is>
       </c>
       <c r="K243" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L243" s="2" t="inlineStr">
         <is>
-          <t>16667_0_решение о выпуске 002P-05.pdf</t>
+          <t>18172_0_решение о выпуске 002P-08.pdf</t>
         </is>
       </c>
       <c r="M243" s="2" t="inlineStr">
@@ -13245,504 +13140,486 @@
       </c>
       <c r="N243" s="3" t="inlineStr">
         <is>
-          <t>https://st.finam.ru/ipo/genconditions/16667_0_решение о выпуске 002P-05.pdf</t>
+          <t>https://st.finam.ru/ipo/genconditions/18172_0_решение о выпуске 002P-08.pdf</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
         <is>
-          <t>ТД РКС-002Р-06</t>
+          <t>УНИВЕРСАЛЬНАЯ ЛИЗИНГОВАЯ КОМПАНИЯ-001Р-01</t>
         </is>
       </c>
       <c r="B244" s="2" t="inlineStr"/>
       <c r="C244" s="2" t="inlineStr">
         <is>
-          <t>RU000A10C758</t>
+          <t>RU000A10BTT6</t>
         </is>
       </c>
       <c r="D244" s="2" t="inlineStr"/>
       <c r="E244" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F244" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G244" s="2" t="inlineStr">
+        <is>
+          <t>Положения о досрочном погашении</t>
+        </is>
+      </c>
+      <c r="H244" s="2" t="inlineStr">
+        <is>
+          <t>Put-опция у владельцев отсутствует</t>
+        </is>
+      </c>
+      <c r="I244" s="2" t="inlineStr">
+        <is>
+          <t>Решение о выпуске</t>
+        </is>
+      </c>
+      <c r="J244" s="2" t="inlineStr"/>
+      <c r="K244" s="2" t="inlineStr"/>
+      <c r="L244" s="2" t="inlineStr">
+        <is>
+          <t>16674_0_Решение_001P-01.pdf</t>
+        </is>
+      </c>
+      <c r="M244" s="2" t="inlineStr"/>
+      <c r="N244" s="3" t="inlineStr">
+        <is>
+          <t>https://st.finam.ru/ipo/genconditions/16674_0_Решение_001P-01.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="2" t="inlineStr">
+        <is>
+          <t>ЦИФРА БРОКЕР-П01-02</t>
+        </is>
+      </c>
+      <c r="B245" s="2" t="inlineStr"/>
+      <c r="C245" s="2" t="inlineStr">
+        <is>
+          <t>RU000A1040E8</t>
+        </is>
+      </c>
+      <c r="D245" s="2" t="inlineStr"/>
+      <c r="E245" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F244" s="2" t="n">
+      <c r="F245" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="G244" s="2" t="inlineStr">
-        <is>
-          <t>Информационный (отчётность эмитента) +
-Раскрытие отчётности эмитента</t>
-        </is>
-      </c>
-      <c r="H244" s="2" t="inlineStr">
-        <is>
-          <t>нераскрытие на Странице Поручителя в сети Интернет годовой консолидированной финансовой отчётности Поручителя, составленной в соответствии с Международными стандартами финансовой отчетности, с приложе…</t>
-        </is>
-      </c>
-      <c r="I244" s="2" t="inlineStr">
-        <is>
-          <t>Решение о выпуске</t>
-        </is>
-      </c>
-      <c r="J244" s="2" t="inlineStr">
-        <is>
-          <t>п. 5.6.1, 1</t>
-        </is>
-      </c>
-      <c r="K244" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="L244" s="2" t="inlineStr">
-        <is>
-          <t>16929_0_решение о выпуске 002P-06.pdf</t>
-        </is>
-      </c>
-      <c r="M244" s="2" t="inlineStr">
-        <is>
-          <t>нераскрытие на Странице Поручителя в сети Интернет годовой консолидированной финансовой отчётности Поручителя, составленной в соответствии с Международными стандартами финансовой отчетности, с приложением аудиторского заключения в отношении такой отчётности (Консолидированная финансовая отчетность) в срок до 120 (Ста двадцати) дней после даты окончания отчетного года, за который составлена данная отчетность. Моментом наступления События досрочного погашения по требованию владельцев Биржевых обли</t>
-        </is>
-      </c>
-      <c r="N244" s="3" t="inlineStr">
-        <is>
-          <t>https://st.finam.ru/ipo/genconditions/16929_0_решение о выпуске 002P-06.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="245">
-      <c r="A245" s="2" t="inlineStr"/>
-      <c r="B245" s="2" t="inlineStr"/>
-      <c r="C245" s="2" t="inlineStr"/>
-      <c r="D245" s="2" t="inlineStr"/>
-      <c r="E245" s="2" t="inlineStr"/>
-      <c r="F245" s="2" t="n">
-        <v>2</v>
-      </c>
       <c r="G245" s="2" t="inlineStr">
         <is>
-          <t>Информационный (отчётность эмитента) +
-Раскрытие отчётности эмитента</t>
+          <t>Иное</t>
         </is>
       </c>
       <c r="H245" s="2" t="inlineStr">
-        <is>
-          <t>нераскрытие на Странице Поручителя в сети Интернет годовой бухгалтерской (финансовой) отчетности Поручителя, составленной в соответствии с Российскими стандартами бухгалтерского учета (далее - РСБУ), …</t>
-        </is>
-      </c>
-      <c r="I245" s="2" t="inlineStr">
-        <is>
-          <t>Решение о выпуске</t>
-        </is>
-      </c>
-      <c r="J245" s="2" t="inlineStr">
-        <is>
-          <t>п. 5.6.1, 2</t>
-        </is>
-      </c>
-      <c r="K245" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="L245" s="2" t="inlineStr">
-        <is>
-          <t>16929_0_решение о выпуске 002P-06.pdf</t>
-        </is>
-      </c>
-      <c r="M245" s="2" t="inlineStr">
-        <is>
-          <t>нераскрытие на Странице Поручителя в сети Интернет годовой бухгалтерской (финансовой) отчетности Поручителя, составленной в соответствии с Российскими стандартами бухгалтерского учета (далее - РСБУ), в частности, с Федеральным законом от</t>
-        </is>
-      </c>
-      <c r="N245" s="3" t="inlineStr">
-        <is>
-          <t>https://st.finam.ru/ipo/genconditions/16929_0_решение о выпуске 002P-06.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="246">
-      <c r="A246" s="2" t="inlineStr">
-        <is>
-          <t>ТД РКС-002Р-07</t>
-        </is>
-      </c>
-      <c r="B246" s="2" t="inlineStr"/>
-      <c r="C246" s="2" t="inlineStr">
-        <is>
-          <t>RU000A10E6S8</t>
-        </is>
-      </c>
-      <c r="D246" s="2" t="inlineStr"/>
-      <c r="E246" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="F246" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G246" s="2" t="inlineStr">
-        <is>
-          <t>Информационный (отчётность эмитента) +
-Раскрытие отчётности эмитента</t>
-        </is>
-      </c>
-      <c r="H246" s="2" t="inlineStr">
-        <is>
-          <t>нераскрытие на Странице Поручителя в сети Интернет годовой консолидированной финансовой отчётности Поручителя, составленной в соответствии с Международными стандартами финансовой отчетности (далее – М…</t>
-        </is>
-      </c>
-      <c r="I246" s="2" t="inlineStr">
-        <is>
-          <t>Решение о выпуске</t>
-        </is>
-      </c>
-      <c r="J246" s="2" t="inlineStr">
-        <is>
-          <t>п. 5.6.1, 1</t>
-        </is>
-      </c>
-      <c r="K246" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="L246" s="2" t="inlineStr">
-        <is>
-          <t>17758_0_решение о выпуске 002P-07.pdf</t>
-        </is>
-      </c>
-      <c r="M246" s="2" t="inlineStr">
-        <is>
-          <t>нераскрытие на Странице Поручителя в сети Интернет годовой консолидированной финансовой отчётности Поручителя, составленной в соответствии с Международными стандартами финансовой отчетности (далее – МСФО), с приложением аудиторского заключения в отношении такой отчётности (Консолидированная финансовая отчетность) в срок до 120 (Ста двадцати) дней после даты окончания отчетного года, за который составлена данная отчетность. Моментом наступления События досрочного погашения по требованию владельце</t>
-        </is>
-      </c>
-      <c r="N246" s="3" t="inlineStr">
-        <is>
-          <t>https://st.finam.ru/ipo/genconditions/17758_0_решение о выпуске 002P-07.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="247">
-      <c r="A247" s="2" t="inlineStr"/>
-      <c r="B247" s="2" t="inlineStr"/>
-      <c r="C247" s="2" t="inlineStr"/>
-      <c r="D247" s="2" t="inlineStr"/>
-      <c r="E247" s="2" t="inlineStr"/>
-      <c r="F247" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G247" s="2" t="inlineStr">
-        <is>
-          <t>Информационный (отчётность эмитента) +
-Раскрытие отчётности эмитента</t>
-        </is>
-      </c>
-      <c r="H247" s="2" t="inlineStr">
-        <is>
-          <t>нераскрытие на Странице Поручителя в сети Интернет годовой бухгалтерской (финансовой) отчетности Поручителя, составленной в соответствии с Российскими стандартами бухгалтерского учета (далее - РСБУ), …</t>
-        </is>
-      </c>
-      <c r="I247" s="2" t="inlineStr">
-        <is>
-          <t>Решение о выпуске</t>
-        </is>
-      </c>
-      <c r="J247" s="2" t="inlineStr">
-        <is>
-          <t>п. 5.6.1, 2</t>
-        </is>
-      </c>
-      <c r="K247" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="L247" s="2" t="inlineStr">
-        <is>
-          <t>17758_0_решение о выпуске 002P-07.pdf</t>
-        </is>
-      </c>
-      <c r="M247" s="2" t="inlineStr">
-        <is>
-          <t>нераскрытие на Странице Поручителя в сети Интернет годовой бухгалтерской (финансовой) отчетности Поручителя, составленной в соответствии с Российскими стандартами бухгалтерского учета (далее - РСБУ), в частности, с Федеральным законом от</t>
-        </is>
-      </c>
-      <c r="N247" s="3" t="inlineStr">
-        <is>
-          <t>https://st.finam.ru/ipo/genconditions/17758_0_решение о выпуске 002P-07.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="248">
-      <c r="A248" s="2" t="inlineStr">
-        <is>
-          <t>ТД РКС-002Р-08</t>
-        </is>
-      </c>
-      <c r="B248" s="2" t="inlineStr"/>
-      <c r="C248" s="2" t="inlineStr">
-        <is>
-          <t>RU000A10F0X0</t>
-        </is>
-      </c>
-      <c r="D248" s="2" t="inlineStr"/>
-      <c r="E248" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="F248" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G248" s="2" t="inlineStr">
-        <is>
-          <t>Информационный (отчётность эмитента) +
-Раскрытие отчётности эмитента</t>
-        </is>
-      </c>
-      <c r="H248" s="2" t="inlineStr">
-        <is>
-          <t>нераскрытие на Странице Поручителя в сети Интернет годовой консолидированной финансовой отчётности Поручителя, составленной в соответствии с Международными стандартами финансовой отчетности (далее – М…</t>
-        </is>
-      </c>
-      <c r="I248" s="2" t="inlineStr">
-        <is>
-          <t>Решение о выпуске</t>
-        </is>
-      </c>
-      <c r="J248" s="2" t="inlineStr">
-        <is>
-          <t>п. 5.6.1, 1</t>
-        </is>
-      </c>
-      <c r="K248" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="L248" s="2" t="inlineStr">
-        <is>
-          <t>18172_0_решение о выпуске 002P-08.pdf</t>
-        </is>
-      </c>
-      <c r="M248" s="2" t="inlineStr">
-        <is>
-          <t>нераскрытие на Странице Поручителя в сети Интернет годовой консолидированной финансовой отчётности Поручителя, составленной в соответствии с Международными стандартами финансовой отчетности (далее – МСФО), с приложением аудиторского заключения в отношении такой отчётности (Консолидированная финансовая отчетность) в срок до 120 (Ста двадцати) дней после даты окончания отчетного года, за который составлена данная отчетность. Моментом наступления События досрочного погашения по требованию владельце</t>
-        </is>
-      </c>
-      <c r="N248" s="3" t="inlineStr">
-        <is>
-          <t>https://st.finam.ru/ipo/genconditions/18172_0_решение о выпуске 002P-08.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" s="2" t="inlineStr"/>
-      <c r="B249" s="2" t="inlineStr"/>
-      <c r="C249" s="2" t="inlineStr"/>
-      <c r="D249" s="2" t="inlineStr"/>
-      <c r="E249" s="2" t="inlineStr"/>
-      <c r="F249" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G249" s="2" t="inlineStr">
-        <is>
-          <t>Информационный (отчётность эмитента) +
-Раскрытие отчётности эмитента</t>
-        </is>
-      </c>
-      <c r="H249" s="2" t="inlineStr">
-        <is>
-          <t>нераскрытие на Странице Поручителя в сети Интернет годовой бухгалтерской (финансовой) отчетности Поручителя, составленной в соответствии с Российскими стандартами бухгалтерского учета (далее - РСБУ), …</t>
-        </is>
-      </c>
-      <c r="I249" s="2" t="inlineStr">
-        <is>
-          <t>Решение о выпуске</t>
-        </is>
-      </c>
-      <c r="J249" s="2" t="inlineStr">
-        <is>
-          <t>п. 5.6.1, 2</t>
-        </is>
-      </c>
-      <c r="K249" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="L249" s="2" t="inlineStr">
-        <is>
-          <t>18172_0_решение о выпуске 002P-08.pdf</t>
-        </is>
-      </c>
-      <c r="M249" s="2" t="inlineStr">
-        <is>
-          <t>нераскрытие на Странице Поручителя в сети Интернет годовой бухгалтерской (финансовой) отчетности Поручителя, составленной в соответствии с Российскими стандартами бухгалтерского учета (далее - РСБУ), в частности, с Федеральным законом от</t>
-        </is>
-      </c>
-      <c r="N249" s="3" t="inlineStr">
-        <is>
-          <t>https://st.finam.ru/ipo/genconditions/18172_0_решение о выпуске 002P-08.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="250">
-      <c r="A250" s="2" t="inlineStr">
-        <is>
-          <t>УНИВЕРСАЛЬНАЯ ЛИЗИНГОВАЯ КОМПАНИЯ-001Р-01</t>
-        </is>
-      </c>
-      <c r="B250" s="2" t="inlineStr"/>
-      <c r="C250" s="2" t="inlineStr">
-        <is>
-          <t>RU000A10BTT6</t>
-        </is>
-      </c>
-      <c r="D250" s="2" t="inlineStr"/>
-      <c r="E250" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F250" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G250" s="2" t="inlineStr">
-        <is>
-          <t>Положения о досрочном погашении</t>
-        </is>
-      </c>
-      <c r="H250" s="2" t="inlineStr">
-        <is>
-          <t>Put-опция у владельцев отсутствует</t>
-        </is>
-      </c>
-      <c r="I250" s="2" t="inlineStr">
-        <is>
-          <t>Решение о выпуске</t>
-        </is>
-      </c>
-      <c r="J250" s="2" t="inlineStr"/>
-      <c r="K250" s="2" t="inlineStr"/>
-      <c r="L250" s="2" t="inlineStr">
-        <is>
-          <t>16674_0_Решение_001P-01.pdf</t>
-        </is>
-      </c>
-      <c r="M250" s="2" t="inlineStr"/>
-      <c r="N250" s="3" t="inlineStr">
-        <is>
-          <t>https://st.finam.ru/ipo/genconditions/16674_0_Решение_001P-01.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" s="2" t="inlineStr">
-        <is>
-          <t>ЦИФРА БРОКЕР-П01-02</t>
-        </is>
-      </c>
-      <c r="B251" s="2" t="inlineStr"/>
-      <c r="C251" s="2" t="inlineStr">
-        <is>
-          <t>RU000A1040E8</t>
-        </is>
-      </c>
-      <c r="D251" s="2" t="inlineStr"/>
-      <c r="E251" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="F251" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G251" s="2" t="inlineStr">
-        <is>
-          <t>Информационный (отчётность эмитента) +
-Раскрытие отчётности эмитента</t>
-        </is>
-      </c>
-      <c r="H251" s="2" t="inlineStr">
         <is>
           <t>5.6.1 Досрочное погашение облигаций по требованию их владельцев
 Предусмотрена возможность досрочного погашения Биржевых облигаций по требованию их
 владельцев в порядке и на условиях, установленных дей</t>
         </is>
       </c>
+      <c r="I245" s="2" t="inlineStr">
+        <is>
+          <t>Решение о выпуске</t>
+        </is>
+      </c>
+      <c r="J245" s="2" t="inlineStr">
+        <is>
+          <t>п. 5.6.1, 1</t>
+        </is>
+      </c>
+      <c r="K245" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="L245" s="2" t="inlineStr">
+        <is>
+          <t>12435_0_Решение_П01-02 (1).pdf</t>
+        </is>
+      </c>
+      <c r="M245" s="2" t="inlineStr">
+        <is>
+          <t>5.6.1 Досрочное погашение облигаций по требованию их владельцев Предусмотрена возможность досрочного погашения Биржевых облигаций по требованию их владельцев в порядке и на условиях, установленных действующим законодательством Российской Федерации. Досрочное погашение Биржевых облигаций по требованию их владельцев производится денежными средствами в долларах США в безналичном порядке. Иные сведения, подлежащие указанию в настоящем пункте, приведены в пункте 9.5.1 Программы.</t>
+        </is>
+      </c>
+      <c r="N245" s="3" t="inlineStr">
+        <is>
+          <t>https://st.finam.ru/ipo/genconditions/12435_0_Решение_П01-02 (1).pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="7" t="inlineStr"/>
+      <c r="B246" s="7" t="inlineStr"/>
+      <c r="C246" s="7" t="inlineStr"/>
+      <c r="D246" s="7" t="inlineStr"/>
+      <c r="E246" s="7" t="inlineStr"/>
+      <c r="F246" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G246" s="7" t="inlineStr">
+        <is>
+          <t>Делистинг</t>
+        </is>
+      </c>
+      <c r="H246" s="7" t="inlineStr">
+        <is>
+          <t>Досрочное погашение в случае делистинга (из Программы)</t>
+        </is>
+      </c>
+      <c r="I246" s="7" t="inlineStr">
+        <is>
+          <t>Программа облигаций</t>
+        </is>
+      </c>
+      <c r="J246" s="7" t="inlineStr">
+        <is>
+          <t>п. 9.5.1</t>
+        </is>
+      </c>
+      <c r="K246" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L246" s="7" t="inlineStr">
+        <is>
+          <t>12435_0_Программа_П01.pdf</t>
+        </is>
+      </c>
+      <c r="M246" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">азанным в настоящем пункте Программы, случаи досрочного погашения Биржевых облигаций по требованию их владельцев. В этом случае Условия выпуска должны содержать порядок и условия такого досрочного погашения Биржевых облигаций. Владельцы Биржевых облигаций вправе предъявить их к досрочному погашению в случае делистинга Биржевых облигаций на всех биржах, осуществивших их допуск к организованным торгам. 13 Стоимость (порядок определения стоимости) досрочного погашения: Досрочное погашение Биржевых </t>
+        </is>
+      </c>
+      <c r="N246" s="8" t="inlineStr">
+        <is>
+          <t>https://st.finam.ru/ipo/decision/12435_0_Программа_П01.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="2" t="inlineStr">
+        <is>
+          <t>ЭЛЕКТРОРЕШЕНИЯ-001P-02</t>
+        </is>
+      </c>
+      <c r="B247" s="2" t="inlineStr"/>
+      <c r="C247" s="2" t="inlineStr">
+        <is>
+          <t>RU000A10D1J9</t>
+        </is>
+      </c>
+      <c r="D247" s="2" t="inlineStr"/>
+      <c r="E247" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F247" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G247" s="2" t="inlineStr">
+        <is>
+          <t>Положения о досрочном погашении</t>
+        </is>
+      </c>
+      <c r="H247" s="2" t="inlineStr">
+        <is>
+          <t>Put-опция у владельцев отсутствует</t>
+        </is>
+      </c>
+      <c r="I247" s="2" t="inlineStr">
+        <is>
+          <t>Решение о выпуске</t>
+        </is>
+      </c>
+      <c r="J247" s="2" t="inlineStr"/>
+      <c r="K247" s="2" t="inlineStr"/>
+      <c r="L247" s="2" t="inlineStr">
+        <is>
+          <t>17262_0_Решение_о_выпуске_001Р-02.pdf</t>
+        </is>
+      </c>
+      <c r="M247" s="2" t="inlineStr"/>
+      <c r="N247" s="3" t="inlineStr">
+        <is>
+          <t>https://st.finam.ru/ipo/genconditions/17262_0_Решение_о_выпуске_001Р-02.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="2" t="inlineStr">
+        <is>
+          <t>ЭЛЕКТРОРЕШЕНИЯ-001P-03</t>
+        </is>
+      </c>
+      <c r="B248" s="2" t="inlineStr"/>
+      <c r="C248" s="2" t="inlineStr">
+        <is>
+          <t>RU000A10ECY6</t>
+        </is>
+      </c>
+      <c r="D248" s="2" t="inlineStr"/>
+      <c r="E248" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F248" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G248" s="2" t="inlineStr">
+        <is>
+          <t>Положения о досрочном погашении</t>
+        </is>
+      </c>
+      <c r="H248" s="2" t="inlineStr">
+        <is>
+          <t>Put-опция у владельцев отсутствует</t>
+        </is>
+      </c>
+      <c r="I248" s="2" t="inlineStr">
+        <is>
+          <t>Решение о выпуске</t>
+        </is>
+      </c>
+      <c r="J248" s="2" t="inlineStr"/>
+      <c r="K248" s="2" t="inlineStr"/>
+      <c r="L248" s="2" t="inlineStr">
+        <is>
+          <t>17821_0_Решение_о_выпуске_001Р-03.pdf</t>
+        </is>
+      </c>
+      <c r="M248" s="2" t="inlineStr"/>
+      <c r="N248" s="3" t="inlineStr">
+        <is>
+          <t>https://st.finam.ru/ipo/genconditions/17821_0_Решение_о_выпуске_001Р-03.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="2" t="inlineStr">
+        <is>
+          <t>ЭЛЕКТРОРЕШЕНИЯ-001P-04</t>
+        </is>
+      </c>
+      <c r="B249" s="2" t="inlineStr"/>
+      <c r="C249" s="2" t="inlineStr">
+        <is>
+          <t>RU000A10FV02</t>
+        </is>
+      </c>
+      <c r="D249" s="2" t="inlineStr"/>
+      <c r="E249" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F249" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G249" s="2" t="inlineStr">
+        <is>
+          <t>Положения о досрочном погашении</t>
+        </is>
+      </c>
+      <c r="H249" s="2" t="inlineStr">
+        <is>
+          <t>Put-опция у владельцев отсутствует</t>
+        </is>
+      </c>
+      <c r="I249" s="2" t="inlineStr">
+        <is>
+          <t>Решение о выпуске</t>
+        </is>
+      </c>
+      <c r="J249" s="2" t="inlineStr"/>
+      <c r="K249" s="2" t="inlineStr"/>
+      <c r="L249" s="2" t="inlineStr">
+        <is>
+          <t>18567_0_Решение_001Р-04.pdf</t>
+        </is>
+      </c>
+      <c r="M249" s="2" t="inlineStr"/>
+      <c r="N249" s="3" t="inlineStr">
+        <is>
+          <t>https://st.finam.ru/ipo/decision/18567_0_Решение_001Р-04.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="2" t="inlineStr">
+        <is>
+          <t>ЭЛТЕРА-БО-01</t>
+        </is>
+      </c>
+      <c r="B250" s="2" t="inlineStr"/>
+      <c r="C250" s="2" t="inlineStr">
+        <is>
+          <t>RU000A10DTB0</t>
+        </is>
+      </c>
+      <c r="D250" s="2" t="inlineStr"/>
+      <c r="E250" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F250" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G250" s="2" t="inlineStr">
+        <is>
+          <t>Раскрытие отчётности</t>
+        </is>
+      </c>
+      <c r="H250" s="2" t="inlineStr">
+        <is>
+          <t>Не опубликована промежуточная бухгалтерская (финансовая) отчетность Эмитента, составленная за отчетный период, состоящий из 3, 6 и 9 месяцев отчетного года, по Российским стандартам бухгалтерского уче…</t>
+        </is>
+      </c>
+      <c r="I250" s="2" t="inlineStr">
+        <is>
+          <t>Решение о выпуске</t>
+        </is>
+      </c>
+      <c r="J250" s="2" t="inlineStr">
+        <is>
+          <t>п. 5.6.1, 1</t>
+        </is>
+      </c>
+      <c r="K250" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="L250" s="2" t="inlineStr">
+        <is>
+          <t>17617_0_Решение_о_выпуске БО-01.pdf</t>
+        </is>
+      </c>
+      <c r="M250" s="2" t="inlineStr">
+        <is>
+          <t>Не опубликована промежуточная бухгалтерская (финансовая) отчетность Эмитента, составленная за отчетный период, состоящий из 3, 6 и 9 месяцев отчетного года, по Российским стандартам бухгалтерского учета, в сроки, указанные ниже. Моментом наступления указанного События является рабочий день, следующий за днем истечения срока для опубликования промежуточной бухгалтерской (финансовой) отчетности Эмитента, составленной за отчетный период, состоящий из 3, 6 и 9 месяцев отчетного года, по Российским с</t>
+        </is>
+      </c>
+      <c r="N250" s="3" t="inlineStr">
+        <is>
+          <t>https://st.finam.ru/ipo/genconditions/17617_0_Решение_о_выпуске БО-01.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="2" t="inlineStr">
+        <is>
+          <t>ЭНЕРГОНИКА-001P-03</t>
+        </is>
+      </c>
+      <c r="B251" s="2" t="inlineStr"/>
+      <c r="C251" s="2" t="inlineStr">
+        <is>
+          <t>RU000A105492</t>
+        </is>
+      </c>
+      <c r="D251" s="2" t="inlineStr"/>
+      <c r="E251" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F251" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G251" s="2" t="inlineStr">
+        <is>
+          <t>Положения о досрочном погашении</t>
+        </is>
+      </c>
+      <c r="H251" s="2" t="inlineStr">
+        <is>
+          <t>Put-опция у владельцев отсутствует</t>
+        </is>
+      </c>
       <c r="I251" s="2" t="inlineStr">
         <is>
           <t>Решение о выпуске</t>
         </is>
       </c>
-      <c r="J251" s="2" t="inlineStr">
-        <is>
-          <t>п. 5.6.1, 1</t>
-        </is>
-      </c>
-      <c r="K251" s="2" t="n">
-        <v>6</v>
-      </c>
+      <c r="J251" s="2" t="inlineStr"/>
+      <c r="K251" s="2" t="inlineStr"/>
       <c r="L251" s="2" t="inlineStr">
         <is>
-          <t>12435_0_Решение_П01-02 (1).pdf</t>
-        </is>
-      </c>
-      <c r="M251" s="2" t="inlineStr">
-        <is>
-          <t>5.6.1 Досрочное погашение облигаций по требованию их владельцев Предусмотрена возможность досрочного погашения Биржевых облигаций по требованию их владельцев в порядке и на условиях, установленных действующим законодательством Российской Федерации. Досрочное погашение Биржевых облигаций по требованию их владельцев производится денежными средствами в долларах США в безналичном порядке. Иные сведения, подлежащие указанию в настоящем пункте, приведены в пункте 9.5.1 Программы.</t>
-        </is>
-      </c>
+          <t>13026_0_Решение_001P-03.pdf</t>
+        </is>
+      </c>
+      <c r="M251" s="2" t="inlineStr"/>
       <c r="N251" s="3" t="inlineStr">
         <is>
-          <t>https://st.finam.ru/ipo/genconditions/12435_0_Решение_П01-02 (1).pdf</t>
+          <t>https://st.finam.ru/ipo/decision/13026_0_Решение_001P-03.pdf</t>
         </is>
       </c>
     </row>
     <row r="252">
-      <c r="A252" s="7" t="inlineStr"/>
-      <c r="B252" s="7" t="inlineStr"/>
-      <c r="C252" s="7" t="inlineStr"/>
-      <c r="D252" s="7" t="inlineStr"/>
-      <c r="E252" s="7" t="inlineStr"/>
-      <c r="F252" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G252" s="7" t="inlineStr">
-        <is>
-          <t>Информационный (отчётность эмитента) +
-Раскрытие отчётности эмитента</t>
-        </is>
-      </c>
-      <c r="H252" s="7" t="inlineStr">
-        <is>
-          <t>Досрочное погашение в случае делистинга (из Программы)</t>
-        </is>
-      </c>
-      <c r="I252" s="7" t="inlineStr">
-        <is>
-          <t>Программа облигаций</t>
-        </is>
-      </c>
-      <c r="J252" s="7" t="inlineStr">
-        <is>
-          <t>п. 9.5.1</t>
-        </is>
-      </c>
-      <c r="K252" s="7" t="n">
+      <c r="A252" s="2" t="inlineStr">
+        <is>
+          <t>ЭНЕРГОНИКА-001P-04</t>
+        </is>
+      </c>
+      <c r="B252" s="2" t="inlineStr"/>
+      <c r="C252" s="2" t="inlineStr">
+        <is>
+          <t>RU000A106R79</t>
+        </is>
+      </c>
+      <c r="D252" s="2" t="inlineStr"/>
+      <c r="E252" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="L252" s="7" t="inlineStr">
-        <is>
-          <t>12435_0_Программа_П01.pdf</t>
-        </is>
-      </c>
-      <c r="M252" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">азанным в настоящем пункте Программы, случаи досрочного погашения Биржевых облигаций по требованию их владельцев. В этом случае Условия выпуска должны содержать порядок и условия такого досрочного погашения Биржевых облигаций. Владельцы Биржевых облигаций вправе предъявить их к досрочному погашению в случае делистинга Биржевых облигаций на всех биржах, осуществивших их допуск к организованным торгам. 13 Стоимость (порядок определения стоимости) досрочного погашения: Досрочное погашение Биржевых </t>
-        </is>
-      </c>
-      <c r="N252" s="8" t="inlineStr">
-        <is>
-          <t>https://st.finam.ru/ipo/decision/12435_0_Программа_П01.pdf</t>
+      <c r="F252" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G252" s="2" t="inlineStr">
+        <is>
+          <t>Положения о досрочном погашении</t>
+        </is>
+      </c>
+      <c r="H252" s="2" t="inlineStr">
+        <is>
+          <t>Put-опция у владельцев отсутствует</t>
+        </is>
+      </c>
+      <c r="I252" s="2" t="inlineStr">
+        <is>
+          <t>Решение о выпуске</t>
+        </is>
+      </c>
+      <c r="J252" s="2" t="inlineStr"/>
+      <c r="K252" s="2" t="inlineStr"/>
+      <c r="L252" s="2" t="inlineStr">
+        <is>
+          <t>14345_0_Решение о выпуске 001Р-04.pdf</t>
+        </is>
+      </c>
+      <c r="M252" s="2" t="inlineStr"/>
+      <c r="N252" s="3" t="inlineStr">
+        <is>
+          <t>https://st.finam.ru/ipo/genconditions/14345_0_Решение о выпуске 001Р-04.pdf</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="2" t="inlineStr">
         <is>
-          <t>ЭЛЕКТРОРЕШЕНИЯ-001P-02</t>
+          <t>ЭНЕРГОНИКА-001P-05</t>
         </is>
       </c>
       <c r="B253" s="2" t="inlineStr"/>
       <c r="C253" s="2" t="inlineStr">
         <is>
-          <t>RU000A10D1J9</t>
+          <t>RU000A10A4C1</t>
         </is>
       </c>
       <c r="D253" s="2" t="inlineStr"/>
@@ -13773,26 +13650,26 @@
       <c r="K253" s="2" t="inlineStr"/>
       <c r="L253" s="2" t="inlineStr">
         <is>
-          <t>17262_0_Решение_о_выпуске_001Р-02.pdf</t>
+          <t>15886_0_Решение о выпуске 001Р-05.pdf</t>
         </is>
       </c>
       <c r="M253" s="2" t="inlineStr"/>
       <c r="N253" s="3" t="inlineStr">
         <is>
-          <t>https://st.finam.ru/ipo/genconditions/17262_0_Решение_о_выпуске_001Р-02.pdf</t>
+          <t>https://st.finam.ru/ipo/genconditions/15886_0_Решение о выпуске 001Р-05.pdf</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
         <is>
-          <t>ЭЛЕКТРОРЕШЕНИЯ-001P-03</t>
+          <t>ЭНЕРГОНИКА-001P-06</t>
         </is>
       </c>
       <c r="B254" s="2" t="inlineStr"/>
       <c r="C254" s="2" t="inlineStr">
         <is>
-          <t>RU000A10ECY6</t>
+          <t>RU000A10BNK8</t>
         </is>
       </c>
       <c r="D254" s="2" t="inlineStr"/>
@@ -13823,26 +13700,26 @@
       <c r="K254" s="2" t="inlineStr"/>
       <c r="L254" s="2" t="inlineStr">
         <is>
-          <t>17821_0_Решение_о_выпуске_001Р-03.pdf</t>
+          <t>16660_0_Решение _001Р-06.pdf</t>
         </is>
       </c>
       <c r="M254" s="2" t="inlineStr"/>
       <c r="N254" s="3" t="inlineStr">
         <is>
-          <t>https://st.finam.ru/ipo/genconditions/17821_0_Решение_о_выпуске_001Р-03.pdf</t>
+          <t>https://st.finam.ru/ipo/decision/16660_0_Решение _001Р-06.pdf</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="2" t="inlineStr">
         <is>
-          <t>ЭЛЕКТРОРЕШЕНИЯ-001P-04</t>
+          <t>ЭНЕРГОНИКА-001P-07</t>
         </is>
       </c>
       <c r="B255" s="2" t="inlineStr"/>
       <c r="C255" s="2" t="inlineStr">
         <is>
-          <t>RU000A10FV02</t>
+          <t>RU000A10DBS2</t>
         </is>
       </c>
       <c r="D255" s="2" t="inlineStr"/>
@@ -13873,44 +13750,45 @@
       <c r="K255" s="2" t="inlineStr"/>
       <c r="L255" s="2" t="inlineStr">
         <is>
-          <t>18567_0_Решение_001Р-04.pdf</t>
+          <t>17385_0_Решение_о_выпуске_001Р_07.pdf</t>
         </is>
       </c>
       <c r="M255" s="2" t="inlineStr"/>
       <c r="N255" s="3" t="inlineStr">
         <is>
-          <t>https://st.finam.ru/ipo/decision/18567_0_Решение_001Р-04.pdf</t>
+          <t>https://st.finam.ru/ipo/genconditions/17385_0_Решение_о_выпуске_001Р_07.pdf</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
         <is>
-          <t>ЭЛТЕРА-БО-01</t>
+          <t>АГЕНТСТВО СУДЕБНОГО ВЗЫСКАНИЯ-БО-06-001P</t>
         </is>
       </c>
       <c r="B256" s="2" t="inlineStr"/>
       <c r="C256" s="2" t="inlineStr">
         <is>
-          <t>RU000A10DTB0</t>
+          <t>RU000A10G7Z9</t>
         </is>
       </c>
       <c r="D256" s="2" t="inlineStr"/>
       <c r="E256" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F256" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="F256" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="G256" s="2" t="inlineStr">
         <is>
-          <t>Информационный (отчётность эмитента) +
-Раскрытие отчётности эмитента</t>
+          <t>Положения о досрочном погашении</t>
         </is>
       </c>
       <c r="H256" s="2" t="inlineStr">
         <is>
-          <t>Не опубликована промежуточная бухгалтерская (финансовая) отчетность Эмитента, составленная за отчетный период, состоящий из 3, 6 и 9 месяцев отчетного года, по Российским стандартам бухгалтерского уче…</t>
+          <t>Put-опция у владельцев отсутствует</t>
         </is>
       </c>
       <c r="I256" s="2" t="inlineStr">
@@ -13918,40 +13796,30 @@
           <t>Решение о выпуске</t>
         </is>
       </c>
-      <c r="J256" s="2" t="inlineStr">
-        <is>
-          <t>п. 5.6.1, 1</t>
-        </is>
-      </c>
-      <c r="K256" s="2" t="n">
-        <v>6</v>
-      </c>
+      <c r="J256" s="2" t="inlineStr"/>
+      <c r="K256" s="2" t="inlineStr"/>
       <c r="L256" s="2" t="inlineStr">
         <is>
-          <t>17617_0_Решение_о_выпуске БО-01.pdf</t>
-        </is>
-      </c>
-      <c r="M256" s="2" t="inlineStr">
-        <is>
-          <t>Не опубликована промежуточная бухгалтерская (финансовая) отчетность Эмитента, составленная за отчетный период, состоящий из 3, 6 и 9 месяцев отчетного года, по Российским стандартам бухгалтерского учета, в сроки, указанные ниже. Моментом наступления указанного События является рабочий день, следующий за днем истечения срока для опубликования промежуточной бухгалтерской (финансовой) отчетности Эмитента, составленной за отчетный период, состоящий из 3, 6 и 9 месяцев отчетного года, по Российским с</t>
-        </is>
-      </c>
+          <t>18802_0_Решение_о_выпуске_БО-06-001Р.pdf</t>
+        </is>
+      </c>
+      <c r="M256" s="2" t="inlineStr"/>
       <c r="N256" s="3" t="inlineStr">
         <is>
-          <t>https://st.finam.ru/ipo/genconditions/17617_0_Решение_о_выпуске БО-01.pdf</t>
+          <t>https://st.finam.ru/ipo/genconditions/18802_0_Решение_о_выпуске_БО-06-001Р.pdf</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="2" t="inlineStr">
         <is>
-          <t>ЭНЕРГОНИКА-001P-03</t>
+          <t>РСГ-ФИНАНС-001Р-04</t>
         </is>
       </c>
       <c r="B257" s="2" t="inlineStr"/>
       <c r="C257" s="2" t="inlineStr">
         <is>
-          <t>RU000A105492</t>
+          <t>RU000A10G700</t>
         </is>
       </c>
       <c r="D257" s="2" t="inlineStr"/>
@@ -13982,45 +13850,43 @@
       <c r="K257" s="2" t="inlineStr"/>
       <c r="L257" s="2" t="inlineStr">
         <is>
-          <t>13026_0_Решение_001P-03.pdf</t>
+          <t>18801_0_Решение_001Р-04.pdf</t>
         </is>
       </c>
       <c r="M257" s="2" t="inlineStr"/>
       <c r="N257" s="3" t="inlineStr">
         <is>
-          <t>https://st.finam.ru/ipo/decision/13026_0_Решение_001P-03.pdf</t>
+          <t>https://st.finam.ru/ipo/genconditions/18801_0_Решение_001Р-04.pdf</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
         <is>
-          <t>ЭНЕРГОНИКА-001P-04</t>
+          <t>БУСТЕР.РУ-БО-04</t>
         </is>
       </c>
       <c r="B258" s="2" t="inlineStr"/>
       <c r="C258" s="2" t="inlineStr">
         <is>
-          <t>RU000A106R79</t>
+          <t>RU000A10G6B2</t>
         </is>
       </c>
       <c r="D258" s="2" t="inlineStr"/>
       <c r="E258" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F258" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="F258" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="G258" s="2" t="inlineStr">
         <is>
-          <t>Положения о досрочном погашении</t>
+          <t>Раскрытие отчётности</t>
         </is>
       </c>
       <c r="H258" s="2" t="inlineStr">
         <is>
-          <t>Put-опция у владельцев отсутствует</t>
+          <t>Нарушение Эмитентом сроков публикации на Странице в сети Интернет неаудированной промежуточной бухгалтерской (финансовой) отчетности Эмитента, составленной в соответствии с Федеральным законом от 06</t>
         </is>
       </c>
       <c r="I258" s="2" t="inlineStr">
@@ -14028,49 +13894,47 @@
           <t>Решение о выпуске</t>
         </is>
       </c>
-      <c r="J258" s="2" t="inlineStr"/>
-      <c r="K258" s="2" t="inlineStr"/>
+      <c r="J258" s="2" t="inlineStr">
+        <is>
+          <t>п. 5.6.1, 1</t>
+        </is>
+      </c>
+      <c r="K258" s="2" t="n">
+        <v>9</v>
+      </c>
       <c r="L258" s="2" t="inlineStr">
         <is>
-          <t>14345_0_Решение о выпуске 001Р-04.pdf</t>
-        </is>
-      </c>
-      <c r="M258" s="2" t="inlineStr"/>
+          <t>18764_0_РоВ БО-04.pdf</t>
+        </is>
+      </c>
+      <c r="M258" s="2" t="inlineStr">
+        <is>
+          <t>Нарушение Эмитентом сроков публикации на Странице в сети Интернет неаудированной промежуточной бухгалтерской (финансовой) отчетности Эмитента, составленной в соответствии с Федеральным законом от 06.12.2011 №402-ФЗ «О бухгалтерском учете», за отчетные периоды, состоящие из 3, 6, и 9 месяцев отчетного года (далее – промежуточная бухгалтерская (финансовая) отчетность Эмитента), установленных ниже. Для целей выполнения обязательств, предусмотренных выше, Эмитент в течение срока обращения Биржевых о</t>
+        </is>
+      </c>
       <c r="N258" s="3" t="inlineStr">
         <is>
-          <t>https://st.finam.ru/ipo/genconditions/14345_0_Решение о выпуске 001Р-04.pdf</t>
+          <t>https://st.finam.ru/ipo/genconditions/18764_0_РоВ БО-04.pdf</t>
         </is>
       </c>
     </row>
     <row r="259">
-      <c r="A259" s="2" t="inlineStr">
-        <is>
-          <t>ЭНЕРГОНИКА-001P-05</t>
-        </is>
-      </c>
+      <c r="A259" s="2" t="inlineStr"/>
       <c r="B259" s="2" t="inlineStr"/>
-      <c r="C259" s="2" t="inlineStr">
-        <is>
-          <t>RU000A10A4C1</t>
-        </is>
-      </c>
+      <c r="C259" s="2" t="inlineStr"/>
       <c r="D259" s="2" t="inlineStr"/>
-      <c r="E259" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F259" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="E259" s="2" t="inlineStr"/>
+      <c r="F259" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="G259" s="2" t="inlineStr">
         <is>
-          <t>Положения о досрочном погашении</t>
+          <t>Утрата контроля</t>
         </is>
       </c>
       <c r="H259" s="2" t="inlineStr">
         <is>
-          <t>Put-опция у владельцев отсутствует</t>
+          <t>Утрата Контроля Пащенко Максима Григорьевича (ИНН 541000273190) над Эмитентом и/или Поручителем в течение срока обращения Биржевых облигаций</t>
         </is>
       </c>
       <c r="I259" s="2" t="inlineStr">
@@ -14078,49 +13942,47 @@
           <t>Решение о выпуске</t>
         </is>
       </c>
-      <c r="J259" s="2" t="inlineStr"/>
-      <c r="K259" s="2" t="inlineStr"/>
+      <c r="J259" s="2" t="inlineStr">
+        <is>
+          <t>п. 5.6.1, 2</t>
+        </is>
+      </c>
+      <c r="K259" s="2" t="n">
+        <v>9</v>
+      </c>
       <c r="L259" s="2" t="inlineStr">
         <is>
-          <t>15886_0_Решение о выпуске 001Р-05.pdf</t>
-        </is>
-      </c>
-      <c r="M259" s="2" t="inlineStr"/>
+          <t>18764_0_РоВ БО-04.pdf</t>
+        </is>
+      </c>
+      <c r="M259" s="2" t="inlineStr">
+        <is>
+          <t>Утрата Контроля Пащенко Максима Григорьевича (ИНН 541000273190) над Эмитентом и/или Поручителем в течение срока обращения Биржевых облигаций. Под «Контролем» для целей настоящего пункта понимается право прямо или косвенно распоряжаться более чем 50 (Пятьюдесятью) процентами голосов в высшем органе управления Эмитента и/или Поручителя либо право назначать (избирать) единоличный исполнительный орган и (или) более 50 процентов состава коллегиального органа управления Эмитента и/или Поручителя (в сл</t>
+        </is>
+      </c>
       <c r="N259" s="3" t="inlineStr">
         <is>
-          <t>https://st.finam.ru/ipo/genconditions/15886_0_Решение о выпуске 001Р-05.pdf</t>
+          <t>https://st.finam.ru/ipo/genconditions/18764_0_РоВ БО-04.pdf</t>
         </is>
       </c>
     </row>
     <row r="260">
-      <c r="A260" s="2" t="inlineStr">
-        <is>
-          <t>ЭНЕРГОНИКА-001P-06</t>
-        </is>
-      </c>
+      <c r="A260" s="2" t="inlineStr"/>
       <c r="B260" s="2" t="inlineStr"/>
-      <c r="C260" s="2" t="inlineStr">
-        <is>
-          <t>RU000A10BNK8</t>
-        </is>
-      </c>
+      <c r="C260" s="2" t="inlineStr"/>
       <c r="D260" s="2" t="inlineStr"/>
-      <c r="E260" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F260" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="E260" s="2" t="inlineStr"/>
+      <c r="F260" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="G260" s="2" t="inlineStr">
         <is>
-          <t>Положения о досрочном погашении</t>
+          <t>Кросс-дефолт</t>
         </is>
       </c>
       <c r="H260" s="2" t="inlineStr">
         <is>
-          <t>Put-опция у владельцев отсутствует</t>
+          <t>Существенное нарушение Поручителем в течение срока обращения Биржевых облигаций условий исполнения обязательств по облигациям Поручителя (кросс-дефолт), а именно: - Просрочка Поручителем исполнения об…</t>
         </is>
       </c>
       <c r="I260" s="2" t="inlineStr">
@@ -14128,30 +13990,40 @@
           <t>Решение о выпуске</t>
         </is>
       </c>
-      <c r="J260" s="2" t="inlineStr"/>
-      <c r="K260" s="2" t="inlineStr"/>
+      <c r="J260" s="2" t="inlineStr">
+        <is>
+          <t>п. 5.6.1, 3</t>
+        </is>
+      </c>
+      <c r="K260" s="2" t="n">
+        <v>9</v>
+      </c>
       <c r="L260" s="2" t="inlineStr">
         <is>
-          <t>16660_0_Решение _001Р-06.pdf</t>
-        </is>
-      </c>
-      <c r="M260" s="2" t="inlineStr"/>
+          <t>18764_0_РоВ БО-04.pdf</t>
+        </is>
+      </c>
+      <c r="M260" s="2" t="inlineStr">
+        <is>
+          <t>Существенное нарушение Поручителем в течение срока обращения Биржевых облигаций условий исполнения обязательств по облигациям Поручителя (кросс-дефолт), а именно: - Просрочка Поручителем исполнения обязательства по выплате очередного процентного дохода по облигациям Поручителя на срок более 10 (Десяти) рабочих дней с даты, установленной в юридически обязывающих документах, закрепляющих права по таким облигациям или отказ от исполнения указанного обязательства (далее – «Дата неисполнения»); - Про</t>
+        </is>
+      </c>
       <c r="N260" s="3" t="inlineStr">
         <is>
-          <t>https://st.finam.ru/ipo/decision/16660_0_Решение _001Р-06.pdf</t>
+          <t>https://st.finam.ru/ipo/genconditions/18764_0_РоВ БО-04.pdf</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="2" t="inlineStr">
         <is>
-          <t>ЭНЕРГОНИКА-001P-07</t>
+          <t>ДИРЕКТЛИЗИНГ-002Р-07</t>
         </is>
       </c>
       <c r="B261" s="2" t="inlineStr"/>
       <c r="C261" s="2" t="inlineStr">
         <is>
-          <t>RU000A10DBS2</t>
+          <t>RU000A10G5G3</t>
         </is>
       </c>
       <c r="D261" s="2" t="inlineStr"/>
@@ -14182,60 +14054,592 @@
       <c r="K261" s="2" t="inlineStr"/>
       <c r="L261" s="2" t="inlineStr">
         <is>
-          <t>17385_0_Решение_о_выпуске_001Р_07.pdf</t>
+          <t>18754_0_РоВ_002Р-07.pdf</t>
         </is>
       </c>
       <c r="M261" s="2" t="inlineStr"/>
       <c r="N261" s="3" t="inlineStr">
         <is>
-          <t>https://st.finam.ru/ipo/genconditions/17385_0_Решение_о_выпуске_001Р_07.pdf</t>
+          <t>https://st.finam.ru/ipo/genconditions/18754_0_РоВ_002Р-07.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="2" t="inlineStr">
+        <is>
+          <t>ПКО ВЕРНЕМ-001Р-04</t>
+        </is>
+      </c>
+      <c r="B262" s="2" t="inlineStr"/>
+      <c r="C262" s="2" t="inlineStr">
+        <is>
+          <t>RU000A10G2Y3</t>
+        </is>
+      </c>
+      <c r="D262" s="2" t="inlineStr"/>
+      <c r="E262" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F262" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G262" s="2" t="inlineStr">
+        <is>
+          <t>Раскрытие отчётности</t>
+        </is>
+      </c>
+      <c r="H262" s="2" t="inlineStr">
+        <is>
+          <t>5.6.1.</t>
+        </is>
+      </c>
+      <c r="I262" s="2" t="inlineStr">
+        <is>
+          <t>Решение о выпуске</t>
+        </is>
+      </c>
+      <c r="J262" s="2" t="inlineStr">
+        <is>
+          <t>п. 5.6.1, 1</t>
+        </is>
+      </c>
+      <c r="K262" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="L262" s="2" t="inlineStr">
+        <is>
+          <t>18765_0_РоВ_001Р-04.pdf</t>
+        </is>
+      </c>
+      <c r="M262" s="2" t="inlineStr">
+        <is>
+          <t>5.6.1. Досрочное погашение облигаций по требованию их владельцев: Предусмотрена возможность досрочного погашения Биржевых облигаций по требованию их владельцев. Владельцы Биржевых облигаций вправе предъявить их к досрочному погашению в случае наступления следующего события (далее – «Событие досрочного погашения по требованию владельцев Биржевых облигаций»): Нераскрытие Эмитентом на Странице в сети Интернет в течение срока обращения Биржевых облигаций промежуточной бухгалтерской (финансовой) отче</t>
+        </is>
+      </c>
+      <c r="N262" s="3" t="inlineStr">
+        <is>
+          <t>https://st.finam.ru/ipo/genconditions/18765_0_РоВ_001Р-04.pdf</t>
         </is>
       </c>
     </row>
     <row r="263">
-      <c r="A263" s="9" t="inlineStr">
+      <c r="A263" s="2" t="inlineStr">
+        <is>
+          <t>ПКО ЗАЩИТА ОНЛАЙН-001P-01</t>
+        </is>
+      </c>
+      <c r="B263" s="2" t="inlineStr"/>
+      <c r="C263" s="2" t="inlineStr">
+        <is>
+          <t>RU000A10G080</t>
+        </is>
+      </c>
+      <c r="D263" s="2" t="inlineStr"/>
+      <c r="E263" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F263" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G263" s="2" t="inlineStr">
+        <is>
+          <t>Раскрытие отчётности</t>
+        </is>
+      </c>
+      <c r="H263" s="2" t="inlineStr">
+        <is>
+          <t>5.6.1.</t>
+        </is>
+      </c>
+      <c r="I263" s="2" t="inlineStr">
+        <is>
+          <t>Решение о выпуске</t>
+        </is>
+      </c>
+      <c r="J263" s="2" t="inlineStr">
+        <is>
+          <t>п. 5.6.1, 1</t>
+        </is>
+      </c>
+      <c r="K263" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="L263" s="2" t="inlineStr">
+        <is>
+          <t>18720_0_Решение о выпуске 001Р-01.pdf</t>
+        </is>
+      </c>
+      <c r="M263" s="2" t="inlineStr">
+        <is>
+          <t>5.6.1. Досрочное погашение облигаций по требованию их владельцев Предусмотрена возможность досрочного погашения Биржевых облигаций по требованию их владельцев. Владельцы Биржевых облигаций вправе предъявить их к досрочному погашению в случае наступления любого из следующих событий (далее – «События досрочного погашения по требованию владельцев Биржевых облигаций»): 1) Нераскрытие Эмитентом на Странице в сети Интернет в течение срока обращения Биржевых облигаций промежуточной бухгалтерской (финан</t>
+        </is>
+      </c>
+      <c r="N263" s="3" t="inlineStr">
+        <is>
+          <t>https://st.finam.ru/ipo/genconditions/18720_0_Решение о выпуске 001Р-01.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="2" t="inlineStr">
+        <is>
+          <t>ТАТНЕФТЕХИМ-001-Р-03</t>
+        </is>
+      </c>
+      <c r="B264" s="2" t="inlineStr"/>
+      <c r="C264" s="2" t="inlineStr">
+        <is>
+          <t>RU000A10G072</t>
+        </is>
+      </c>
+      <c r="D264" s="2" t="inlineStr"/>
+      <c r="E264" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F264" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G264" s="2" t="inlineStr">
+        <is>
+          <t>Раскрытие отчётности</t>
+        </is>
+      </c>
+      <c r="H264" s="2" t="inlineStr">
+        <is>
+          <t>Нарушение Эмитентом сроков публикации промежуточной бухгалтерской (финансовой) отчетности Эмитента, установленных ниже</t>
+        </is>
+      </c>
+      <c r="I264" s="2" t="inlineStr">
+        <is>
+          <t>Решение о выпуске</t>
+        </is>
+      </c>
+      <c r="J264" s="2" t="inlineStr">
+        <is>
+          <t>п. 5.6.1, 1</t>
+        </is>
+      </c>
+      <c r="K264" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="L264" s="2" t="inlineStr">
+        <is>
+          <t>18721_0_Решение_001-P-03.pdf</t>
+        </is>
+      </c>
+      <c r="M264" s="2" t="inlineStr">
+        <is>
+          <t>Нарушение Эмитентом сроков публикации промежуточной бухгалтерской (финансовой) отчетности Эмитента, установленных ниже. Под промежуточной бухгалтерской (финансовой) отчетностью Эмитента подразумевается неаудированная промежуточная бухгалтерская (финансовая) отчетность Эмитента за отчетные периоды, состоящие из 3,6 и 9 месяцев отчетного года, составленная в соответствии с Федеральным законом от 06.12.2011 № 402-ФЗ «О бухгалтерском учете». Эмитент в течение срока обращения Биржевых облигаций прини</t>
+        </is>
+      </c>
+      <c r="N264" s="3" t="inlineStr">
+        <is>
+          <t>https://st.finam.ru/ipo/genconditions/18721_0_Решение_001-P-03.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="2" t="inlineStr"/>
+      <c r="B265" s="2" t="inlineStr"/>
+      <c r="C265" s="2" t="inlineStr"/>
+      <c r="D265" s="2" t="inlineStr"/>
+      <c r="E265" s="2" t="inlineStr"/>
+      <c r="F265" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G265" s="2" t="inlineStr">
+        <is>
+          <t>Раскрытие отчётности</t>
+        </is>
+      </c>
+      <c r="H265" s="2" t="inlineStr">
+        <is>
+          <t>Нарушение Эмитентом сроков публикации годовой консолидированной финансовой отчетности Эмитента, установленных ниже</t>
+        </is>
+      </c>
+      <c r="I265" s="2" t="inlineStr">
+        <is>
+          <t>Решение о выпуске</t>
+        </is>
+      </c>
+      <c r="J265" s="2" t="inlineStr">
+        <is>
+          <t>п. 5.6.1, 2</t>
+        </is>
+      </c>
+      <c r="K265" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="L265" s="2" t="inlineStr">
+        <is>
+          <t>18721_0_Решение_001-P-03.pdf</t>
+        </is>
+      </c>
+      <c r="M265" s="2" t="inlineStr">
+        <is>
+          <t>Нарушение Эмитентом сроков публикации годовой консолидированной финансовой отчетности Эмитента, установленных ниже. Под годовой консолидированной финансовой отчетностью Эмитента подразумевается годовая консолидированная финансовая отчетность Эмитента, составленная в соответствии с Международными стандартами финансовой отчетности, вместе с аудиторским заключением, составленным в отношении такой отчетности. Эмитент в течение срока обращения Биржевых облигаций принимает на себя обязательство по рас</t>
+        </is>
+      </c>
+      <c r="N265" s="3" t="inlineStr">
+        <is>
+          <t>https://st.finam.ru/ipo/genconditions/18721_0_Решение_001-P-03.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="2" t="inlineStr"/>
+      <c r="B266" s="2" t="inlineStr"/>
+      <c r="C266" s="2" t="inlineStr"/>
+      <c r="D266" s="2" t="inlineStr"/>
+      <c r="E266" s="2" t="inlineStr"/>
+      <c r="F266" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G266" s="2" t="inlineStr">
+        <is>
+          <t>Иное</t>
+        </is>
+      </c>
+      <c r="H266" s="2" t="inlineStr">
+        <is>
+          <t>У Эмитента отсутствует действующий кредитный рейтинг, присвоенный/подтвержденный Эмитенту кредитным рейтинговым агентством</t>
+        </is>
+      </c>
+      <c r="I266" s="2" t="inlineStr">
+        <is>
+          <t>Решение о выпуске</t>
+        </is>
+      </c>
+      <c r="J266" s="2" t="inlineStr">
+        <is>
+          <t>п. 5.6.1, 3</t>
+        </is>
+      </c>
+      <c r="K266" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="L266" s="2" t="inlineStr">
+        <is>
+          <t>18721_0_Решение_001-P-03.pdf</t>
+        </is>
+      </c>
+      <c r="M266" s="2" t="inlineStr">
+        <is>
+          <t>У Эмитента отсутствует действующий кредитный рейтинг, присвоенный/подтвержденный Эмитенту кредитным рейтинговым агентством. Эмитент в течение срока обращения Биржевых облигаций принимает на себя обязательство иметь как минимум один действующий кредитный рейтинг, присвоенный/подтвержденный Эмитенту одним из кредитных рейтинговых агентств, внесенных Банком России в реестр кредитных рейтинговых агентств (ранее и далее – кредитное рейтинговое агентство). Информация о присвоенном/подтвержденном креди</t>
+        </is>
+      </c>
+      <c r="N266" s="3" t="inlineStr">
+        <is>
+          <t>https://st.finam.ru/ipo/genconditions/18721_0_Решение_001-P-03.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="2" t="inlineStr">
+        <is>
+          <t>ИНТЕРФУДГРУПП-БО-02</t>
+        </is>
+      </c>
+      <c r="B267" s="2" t="inlineStr"/>
+      <c r="C267" s="2" t="inlineStr">
+        <is>
+          <t>RU000A10G023</t>
+        </is>
+      </c>
+      <c r="D267" s="2" t="inlineStr"/>
+      <c r="E267" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F267" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G267" s="2" t="inlineStr">
+        <is>
+          <t>Раскрытие отчётности</t>
+        </is>
+      </c>
+      <c r="H267" s="2" t="inlineStr">
+        <is>
+          <t>Не опубликована промежуточная бухгалтерская (финансовая) отчетность Эмитента, составленная за отчетный период, состоящий из 3, 6 и 9 месяцев отчетного года, по Российским стандартам бухгалтерского уче…</t>
+        </is>
+      </c>
+      <c r="I267" s="2" t="inlineStr">
+        <is>
+          <t>Решение о выпуске</t>
+        </is>
+      </c>
+      <c r="J267" s="2" t="inlineStr">
+        <is>
+          <t>п. 5.6.1, 1</t>
+        </is>
+      </c>
+      <c r="K267" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="L267" s="2" t="inlineStr">
+        <is>
+          <t>18706_0_Решение о выпуске БО-02.pdf</t>
+        </is>
+      </c>
+      <c r="M267" s="2" t="inlineStr">
+        <is>
+          <t>Не опубликована промежуточная бухгалтерская (финансовая) отчетность Эмитента, составленная за отчетный период, состоящий из 3, 6 и 9 месяцев отчетного года, по Российским стандартам бухгалтерского учета. Для целей выполнения обязательств, предусмотренных настоящим подпунктом, Эмитент в течение срока обращения Биржевых облигаций принимает на себя обязательство по раскрытию на Странице в Сети Интернет:</t>
+        </is>
+      </c>
+      <c r="N267" s="3" t="inlineStr">
+        <is>
+          <t>https://st.finam.ru/ipo/genconditions/18706_0_Решение о выпуске БО-02.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="2" t="inlineStr"/>
+      <c r="B268" s="2" t="inlineStr"/>
+      <c r="C268" s="2" t="inlineStr"/>
+      <c r="D268" s="2" t="inlineStr"/>
+      <c r="E268" s="2" t="inlineStr"/>
+      <c r="F268" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G268" s="2" t="inlineStr">
+        <is>
+          <t>Раскрытие отчётности</t>
+        </is>
+      </c>
+      <c r="H268" s="2" t="inlineStr">
+        <is>
+          <t>промежуточной бухгалтерской (финансовой) отчетности, составленной в соответствии с Российскими стандартами бухгалтерского учета, за отчетный период, состоящий из 3, 6 и 9 месяцев отчетного года, в сро…</t>
+        </is>
+      </c>
+      <c r="I268" s="2" t="inlineStr">
+        <is>
+          <t>Решение о выпуске</t>
+        </is>
+      </c>
+      <c r="J268" s="2" t="inlineStr">
+        <is>
+          <t>п. 5.6.1, 2</t>
+        </is>
+      </c>
+      <c r="K268" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="L268" s="2" t="inlineStr">
+        <is>
+          <t>18706_0_Решение о выпуске БО-02.pdf</t>
+        </is>
+      </c>
+      <c r="M268" s="2" t="inlineStr">
+        <is>
+          <t>промежуточной бухгалтерской (финансовой) отчетности, составленной в соответствии с Российскими стандартами бухгалтерского учета, за отчетный период, состоящий из 3, 6 и 9 месяцев отчетного года, в срок не позднее 3 дней, следующих за датой ее составления, но не позднее 60 (Шестидесяти) дней после даты окончания отчетного периода, за который составлена отчетность. Моментом наступления указанного События является рабочий день, следующий за днем истечения срока для раскрытия промежуточной бухгалтер</t>
+        </is>
+      </c>
+      <c r="N268" s="3" t="inlineStr">
+        <is>
+          <t>https://st.finam.ru/ipo/genconditions/18706_0_Решение о выпуске БО-02.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="2" t="inlineStr"/>
+      <c r="B269" s="2" t="inlineStr"/>
+      <c r="C269" s="2" t="inlineStr"/>
+      <c r="D269" s="2" t="inlineStr"/>
+      <c r="E269" s="2" t="inlineStr"/>
+      <c r="F269" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G269" s="2" t="inlineStr">
+        <is>
+          <t>Утрата контроля</t>
+        </is>
+      </c>
+      <c r="H269" s="2" t="inlineStr">
+        <is>
+          <t>Утрата контролирующей доли в Эмитенте Кирсановым Евгением Александровичем (ИНН: 772670780515)</t>
+        </is>
+      </c>
+      <c r="I269" s="2" t="inlineStr">
+        <is>
+          <t>Решение о выпуске</t>
+        </is>
+      </c>
+      <c r="J269" s="2" t="inlineStr">
+        <is>
+          <t>п. 5.6.1, 3</t>
+        </is>
+      </c>
+      <c r="K269" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="L269" s="2" t="inlineStr">
+        <is>
+          <t>18706_0_Решение о выпуске БО-02.pdf</t>
+        </is>
+      </c>
+      <c r="M269" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Утрата контролирующей доли в Эмитенте Кирсановым Евгением Александровичем (ИНН: 772670780515). Под Утратой контролирующей доли в Эмитенте для целей настоящего подпункта понимается снижение доли Кирсанова Е.А. в Эмитенте как его участника до 50% и менее, в том числе полная утрата такой доли. Моментом наступления указанного События является дата, в которую Эмитент узнал или должен был узнать об Утрате контролирующей доли в Эмитенте – Кирсановым Е.А. На дату подписания настоящего Решения о выпуске </t>
+        </is>
+      </c>
+      <c r="N269" s="3" t="inlineStr">
+        <is>
+          <t>https://st.finam.ru/ipo/genconditions/18706_0_Решение о выпуске БО-02.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="2" t="inlineStr">
+        <is>
+          <t>АЙДИ КОЛЛЕКТ-001Р-09</t>
+        </is>
+      </c>
+      <c r="B270" s="2" t="inlineStr"/>
+      <c r="C270" s="2" t="inlineStr">
+        <is>
+          <t>RU000A10FZS6</t>
+        </is>
+      </c>
+      <c r="D270" s="2" t="inlineStr"/>
+      <c r="E270" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F270" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G270" s="2" t="inlineStr">
+        <is>
+          <t>Положения о досрочном погашении</t>
+        </is>
+      </c>
+      <c r="H270" s="2" t="inlineStr">
+        <is>
+          <t>Put-опция у владельцев отсутствует</t>
+        </is>
+      </c>
+      <c r="I270" s="2" t="inlineStr">
+        <is>
+          <t>Решение о выпуске</t>
+        </is>
+      </c>
+      <c r="J270" s="2" t="inlineStr"/>
+      <c r="K270" s="2" t="inlineStr"/>
+      <c r="L270" s="2" t="inlineStr">
+        <is>
+          <t>18679_0_Решение о выпуске 001Р-09.pdf</t>
+        </is>
+      </c>
+      <c r="M270" s="2" t="inlineStr"/>
+      <c r="N270" s="3" t="inlineStr">
+        <is>
+          <t>https://st.finam.ru/ipo/genconditions/18679_0_Решение о выпуске 001Р-09.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="2" t="inlineStr">
+        <is>
+          <t>СЛУЖБА ЗАЩИТЫ АКТИВОВ-БО-08</t>
+        </is>
+      </c>
+      <c r="B271" s="2" t="inlineStr"/>
+      <c r="C271" s="2" t="inlineStr">
+        <is>
+          <t>RU000A10FZQ0</t>
+        </is>
+      </c>
+      <c r="D271" s="2" t="inlineStr"/>
+      <c r="E271" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F271" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G271" s="2" t="inlineStr">
+        <is>
+          <t>Раскрытие отчётности</t>
+        </is>
+      </c>
+      <c r="H271" s="2" t="inlineStr">
+        <is>
+          <t>5.6.1.</t>
+        </is>
+      </c>
+      <c r="I271" s="2" t="inlineStr">
+        <is>
+          <t>Решение о выпуске</t>
+        </is>
+      </c>
+      <c r="J271" s="2" t="inlineStr">
+        <is>
+          <t>п. 5.6.1, 1</t>
+        </is>
+      </c>
+      <c r="K271" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="L271" s="2" t="inlineStr">
+        <is>
+          <t>18686_0_РоВ_БО-08.pdf</t>
+        </is>
+      </c>
+      <c r="M271" s="2" t="inlineStr">
+        <is>
+          <t>5.6.1. Досрочное погашение облигаций по требованию их владельцев Событием досрочного погашения по требованию владельцев Биржевых облигаций является нераскрытие Эмитентом на Странице в сети Интернет промежуточной бухгалтерской (финансовой) отчетности Эмитента, составленной в соответствии с Федеральным законом от</t>
+        </is>
+      </c>
+      <c r="N271" s="3" t="inlineStr">
+        <is>
+          <t>https://st.finam.ru/ipo/genconditions/18686_0_РоВ_БО-08.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="9" t="inlineStr">
         <is>
           <t>ИТОГ</t>
         </is>
       </c>
-      <c r="B263" t="inlineStr">
-        <is>
-          <t>ISIN: 192</t>
-        </is>
-      </c>
-    </row>
-    <row r="264">
-      <c r="A264" s="9" t="inlineStr">
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>ISIN: 202</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="9" t="inlineStr">
         <is>
           <t>С ковенантами:</t>
         </is>
       </c>
-      <c r="B264" t="n">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="265">
-      <c r="A265" s="9" t="inlineStr">
+      <c r="B274" t="n">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="9" t="inlineStr">
         <is>
           <t>Без ковенантов:</t>
         </is>
       </c>
-      <c r="B265" t="n">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="266">
-      <c r="A266" s="9" t="inlineStr">
+      <c r="B275" t="n">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="9" t="inlineStr">
         <is>
           <t>Требует ручной проверки:</t>
         </is>
       </c>
-      <c r="B266" t="n">
+      <c r="B276" t="n">
         <v>12</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N261"/>
+  <autoFilter ref="A1:N271"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N3" r:id="rId2"/>
@@ -14408,7 +14812,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N170" r:id="rId169"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N171" r:id="rId170"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N172" r:id="rId171"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N174" r:id="rId172"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N175" r:id="rId173"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N176" r:id="rId174"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N177" r:id="rId175"/>
@@ -14496,6 +14900,16 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N259" r:id="rId257"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N260" r:id="rId258"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N261" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N262" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N263" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N264" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N265" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N266" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N267" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N268" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N269" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N270" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N271" r:id="rId269"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
